--- a/research/traditional_assets/database/data/austria/austria_air_transport.xlsx
+++ b/research/traditional_assets/database/data/austria/austria_air_transport.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="wbag_flu" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.161</v>
+        <v>-0.0326</v>
+      </c>
+      <c r="E2">
+        <v>-0.009519999999999999</v>
       </c>
       <c r="G2">
-        <v>0.163681045751634</v>
+        <v>0.1229162046570569</v>
       </c>
       <c r="H2">
-        <v>0.1618300653594771</v>
+        <v>0.1213369238080152</v>
       </c>
       <c r="I2">
-        <v>-0.1432679738562092</v>
+        <v>0.1264058292412482</v>
       </c>
       <c r="J2">
-        <v>-0.1432679738562092</v>
+        <v>0.09179951096141702</v>
       </c>
       <c r="K2">
-        <v>-39.6</v>
+        <v>101.1</v>
       </c>
       <c r="L2">
-        <v>-0.1035294117647059</v>
+        <v>0.1601457310312054</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +629,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>89.5</v>
+        <v>57.9</v>
       </c>
       <c r="V2">
-        <v>0.03543010965519972</v>
+        <v>0.01996689426857024</v>
       </c>
       <c r="W2">
-        <v>-0.02726521619388598</v>
+        <v>0.0724783138576242</v>
       </c>
       <c r="X2">
-        <v>0.06114178353713383</v>
+        <v>0.09316194118462383</v>
       </c>
       <c r="Y2">
-        <v>-0.08840699973101981</v>
+        <v>-0.02068362732699963</v>
       </c>
       <c r="Z2">
-        <v>0.2066338933607044</v>
+        <v>0.3737935934632008</v>
       </c>
       <c r="AA2">
-        <v>-0.02960401923180811</v>
+        <v>0.03431406908043257</v>
       </c>
       <c r="AB2">
-        <v>0.05572471763727517</v>
+        <v>0.08929275080723009</v>
       </c>
       <c r="AC2">
-        <v>-0.08532873686908328</v>
+        <v>-0.05497868172679753</v>
       </c>
       <c r="AD2">
-        <v>383.5</v>
+        <v>274.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>383.5</v>
+        <v>274.4</v>
       </c>
       <c r="AG2">
-        <v>294</v>
+        <v>216.5</v>
       </c>
       <c r="AH2">
-        <v>0.1318050591146549</v>
+        <v>0.08644697876630331</v>
       </c>
       <c r="AI2">
-        <v>0.2020760881020129</v>
+        <v>0.1635085210344417</v>
       </c>
       <c r="AJ2">
-        <v>0.1042516222828978</v>
+        <v>0.06947341398453293</v>
       </c>
       <c r="AK2">
-        <v>0.1625836420947852</v>
+        <v>0.1336172313769055</v>
       </c>
       <c r="AL2">
-        <v>15.5</v>
+        <v>13.8</v>
       </c>
       <c r="AM2">
-        <v>12.73</v>
+        <v>9.18</v>
       </c>
       <c r="AN2">
-        <v>3.974093264248705</v>
+        <v>1.319230769230769</v>
       </c>
       <c r="AO2">
-        <v>-3.535483870967742</v>
+        <v>5.782608695652174</v>
       </c>
       <c r="AP2">
-        <v>3.046632124352332</v>
+        <v>1.040865384615385</v>
       </c>
       <c r="AQ2">
-        <v>-4.304791830322073</v>
+        <v>8.692810457516339</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +721,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.161</v>
+        <v>-0.0326</v>
+      </c>
+      <c r="E3">
+        <v>-0.009519999999999999</v>
       </c>
       <c r="G3">
-        <v>0.163681045751634</v>
+        <v>0.1229162046570569</v>
       </c>
       <c r="H3">
-        <v>0.1618300653594771</v>
+        <v>0.1213369238080152</v>
       </c>
       <c r="I3">
-        <v>-0.1432679738562092</v>
+        <v>0.1264058292412482</v>
       </c>
       <c r="J3">
-        <v>-0.1432679738562092</v>
+        <v>0.09179951096141702</v>
       </c>
       <c r="K3">
-        <v>-39.6</v>
+        <v>101.1</v>
       </c>
       <c r="L3">
-        <v>-0.1035294117647059</v>
+        <v>0.1601457310312054</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,7 +751,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +760,8791 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>89.5</v>
+        <v>57.9</v>
       </c>
       <c r="V3">
-        <v>0.03543010965519972</v>
+        <v>0.01996689426857024</v>
       </c>
       <c r="W3">
-        <v>-0.02726521619388598</v>
+        <v>0.0724783138576242</v>
       </c>
       <c r="X3">
-        <v>0.06114178353713383</v>
+        <v>0.09316194118462383</v>
       </c>
       <c r="Y3">
-        <v>-0.08840699973101981</v>
+        <v>-0.02068362732699963</v>
       </c>
       <c r="Z3">
-        <v>0.2066338933607044</v>
+        <v>0.3737935934632008</v>
       </c>
       <c r="AA3">
-        <v>-0.02960401923180811</v>
+        <v>0.03431406908043257</v>
       </c>
       <c r="AB3">
-        <v>0.05572471763727517</v>
+        <v>0.08929275080723009</v>
       </c>
       <c r="AC3">
-        <v>-0.08532873686908328</v>
+        <v>-0.05497868172679753</v>
       </c>
       <c r="AD3">
-        <v>383.5</v>
+        <v>274.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>383.5</v>
+        <v>274.4</v>
       </c>
       <c r="AG3">
-        <v>294</v>
+        <v>216.5</v>
       </c>
       <c r="AH3">
-        <v>0.1318050591146549</v>
+        <v>0.08644697876630331</v>
       </c>
       <c r="AI3">
-        <v>0.2020760881020129</v>
+        <v>0.1635085210344417</v>
       </c>
       <c r="AJ3">
-        <v>0.1042516222828978</v>
+        <v>0.06947341398453293</v>
       </c>
       <c r="AK3">
-        <v>0.1625836420947852</v>
+        <v>0.1336172313769055</v>
       </c>
       <c r="AL3">
-        <v>15.5</v>
+        <v>13.8</v>
       </c>
       <c r="AM3">
-        <v>12.73</v>
+        <v>9.18</v>
       </c>
       <c r="AN3">
-        <v>3.974093264248705</v>
+        <v>1.319230769230769</v>
       </c>
       <c r="AO3">
-        <v>-3.535483870967742</v>
+        <v>5.782608695652174</v>
       </c>
       <c r="AP3">
-        <v>3.046632124352332</v>
+        <v>1.040865384615385</v>
       </c>
       <c r="AQ3">
-        <v>-4.304791830322073</v>
+        <v>8.692810457516339</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Flughafen Wien Aktiengesellschaft (WBAG:FLU)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>WBAG:FLU</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Air Transport</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.08644697876630331</v>
+      </c>
+      <c r="F2">
+        <v>0.09</v>
+      </c>
+      <c r="G2">
+        <v>2899.8</v>
+      </c>
+      <c r="H2">
+        <v>2926.21803238963</v>
+      </c>
+      <c r="I2">
+        <v>3116.3</v>
+      </c>
+      <c r="J2">
+        <v>3153.99603238963</v>
+      </c>
+      <c r="K2">
+        <v>274.4</v>
+      </c>
+      <c r="L2">
+        <v>285.678</v>
+      </c>
+      <c r="M2">
+        <v>0.08929275080723011</v>
+      </c>
+      <c r="N2">
+        <v>0.08868926990543941</v>
+      </c>
+      <c r="O2">
+        <v>0.0484039816513761</v>
+      </c>
+      <c r="P2">
+        <v>0.0418</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.0931619411846238</v>
+      </c>
+      <c r="T2">
+        <v>0.09332667022575759</v>
+      </c>
+      <c r="U2">
+        <v>0.823172110371055</v>
+      </c>
+      <c r="V2">
+        <v>0.825666509016037</v>
+      </c>
+      <c r="W2">
+        <v>4.868800155801605</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>2899.8</v>
+      </c>
+      <c r="AB2">
+        <v>0.0660395809086869</v>
+      </c>
+      <c r="AC2">
+        <v>0.0636894495412844</v>
+      </c>
+      <c r="AD2">
+        <v>0.24</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>208</v>
+      </c>
+      <c r="AH2">
+        <v>131.5</v>
+      </c>
+      <c r="AI2">
+        <v>55.40000000000001</v>
+      </c>
+      <c r="AJ2">
+        <v>274.4</v>
+      </c>
+      <c r="AK2">
+        <v>274.4</v>
+      </c>
+      <c r="AL2">
+        <v>13.8</v>
+      </c>
+      <c r="AM2">
+        <v>274.4</v>
+      </c>
+      <c r="AN2">
+        <v>57.9</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.08951470758936983</v>
+      </c>
+      <c r="C2">
+        <v>3160.561275593216</v>
+      </c>
+      <c r="D2">
+        <v>3102.661275593216</v>
+      </c>
+      <c r="E2">
+        <v>-274.4</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>57.9</v>
+      </c>
+      <c r="H2">
+        <v>2899.8</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>208</v>
+      </c>
+      <c r="K2">
+        <v>131.5</v>
+      </c>
+      <c r="L2">
+        <v>76.5</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>76.5</v>
+      </c>
+      <c r="O2">
+        <v>18.36</v>
+      </c>
+      <c r="P2">
+        <v>58.14</v>
+      </c>
+      <c r="Q2">
+        <v>189.64</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.08951470758936983</v>
+      </c>
+      <c r="T2">
+        <v>0.7679441161126261</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.24</v>
+      </c>
+      <c r="W2">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.08935231229115534</v>
+      </c>
+      <c r="C3">
+        <v>3138.786329131866</v>
+      </c>
+      <c r="D3">
+        <v>3112.628329131866</v>
+      </c>
+      <c r="E3">
+        <v>-242.658</v>
+      </c>
+      <c r="F3">
+        <v>31.742</v>
+      </c>
+      <c r="G3">
+        <v>57.9</v>
+      </c>
+      <c r="H3">
+        <v>2899.8</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>208</v>
+      </c>
+      <c r="K3">
+        <v>131.5</v>
+      </c>
+      <c r="L3">
+        <v>76.5</v>
+      </c>
+      <c r="M3">
+        <v>1.4506094</v>
+      </c>
+      <c r="N3">
+        <v>75.0493906</v>
+      </c>
+      <c r="O3">
+        <v>18.011853744</v>
+      </c>
+      <c r="P3">
+        <v>57.037536856</v>
+      </c>
+      <c r="Q3">
+        <v>188.537536856</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.08990403261732863</v>
+      </c>
+      <c r="T3">
+        <v>0.7738394446807635</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.24</v>
+      </c>
+      <c r="W3">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>52.73645682979856</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.08918991699294085</v>
+      </c>
+      <c r="C4">
+        <v>3117.075625786136</v>
+      </c>
+      <c r="D4">
+        <v>3122.659625786136</v>
+      </c>
+      <c r="E4">
+        <v>-210.916</v>
+      </c>
+      <c r="F4">
+        <v>63.48400000000001</v>
+      </c>
+      <c r="G4">
+        <v>57.9</v>
+      </c>
+      <c r="H4">
+        <v>2899.8</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>208</v>
+      </c>
+      <c r="K4">
+        <v>131.5</v>
+      </c>
+      <c r="L4">
+        <v>76.5</v>
+      </c>
+      <c r="M4">
+        <v>2.901218800000001</v>
+      </c>
+      <c r="N4">
+        <v>73.5987812</v>
+      </c>
+      <c r="O4">
+        <v>17.663707488</v>
+      </c>
+      <c r="P4">
+        <v>55.935073712</v>
+      </c>
+      <c r="Q4">
+        <v>187.435073712</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.09030130305402127</v>
+      </c>
+      <c r="T4">
+        <v>0.779855086076822</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.24</v>
+      </c>
+      <c r="W4">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>26.36822841489928</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.08902752169472637</v>
+      </c>
+      <c r="C5">
+        <v>3095.429788687303</v>
+      </c>
+      <c r="D5">
+        <v>3132.755788687303</v>
+      </c>
+      <c r="E5">
+        <v>-179.174</v>
+      </c>
+      <c r="F5">
+        <v>95.226</v>
+      </c>
+      <c r="G5">
+        <v>57.9</v>
+      </c>
+      <c r="H5">
+        <v>2899.8</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>208</v>
+      </c>
+      <c r="K5">
+        <v>131.5</v>
+      </c>
+      <c r="L5">
+        <v>76.5</v>
+      </c>
+      <c r="M5">
+        <v>4.351828200000001</v>
+      </c>
+      <c r="N5">
+        <v>72.1481718</v>
+      </c>
+      <c r="O5">
+        <v>17.315561232</v>
+      </c>
+      <c r="P5">
+        <v>54.832610568</v>
+      </c>
+      <c r="Q5">
+        <v>186.332610568</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.09070676463373853</v>
+      </c>
+      <c r="T5">
+        <v>0.7859947613160982</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.24</v>
+      </c>
+      <c r="W5">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>17.57881894326619</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.08886512639651187</v>
+      </c>
+      <c r="C6">
+        <v>3073.849449051603</v>
+      </c>
+      <c r="D6">
+        <v>3142.917449051603</v>
+      </c>
+      <c r="E6">
+        <v>-147.432</v>
+      </c>
+      <c r="F6">
+        <v>126.968</v>
+      </c>
+      <c r="G6">
+        <v>57.9</v>
+      </c>
+      <c r="H6">
+        <v>2899.8</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>208</v>
+      </c>
+      <c r="K6">
+        <v>131.5</v>
+      </c>
+      <c r="L6">
+        <v>76.5</v>
+      </c>
+      <c r="M6">
+        <v>5.802437600000001</v>
+      </c>
+      <c r="N6">
+        <v>70.6975624</v>
+      </c>
+      <c r="O6">
+        <v>16.967414976</v>
+      </c>
+      <c r="P6">
+        <v>53.73014742399999</v>
+      </c>
+      <c r="Q6">
+        <v>185.230147424</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.09112067332969986</v>
+      </c>
+      <c r="T6">
+        <v>0.7922623464561926</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.24</v>
+      </c>
+      <c r="W6">
+        <v>0.03473200000000001</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>13.18411420744964</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.08890793109829738</v>
+      </c>
+      <c r="C7">
+        <v>3039.422611717584</v>
+      </c>
+      <c r="D7">
+        <v>3140.232611717584</v>
+      </c>
+      <c r="E7">
+        <v>-115.6899999999999</v>
+      </c>
+      <c r="F7">
+        <v>158.71</v>
+      </c>
+      <c r="G7">
+        <v>57.9</v>
+      </c>
+      <c r="H7">
+        <v>2899.8</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>208</v>
+      </c>
+      <c r="K7">
+        <v>131.5</v>
+      </c>
+      <c r="L7">
+        <v>76.5</v>
+      </c>
+      <c r="M7">
+        <v>8.110081000000001</v>
+      </c>
+      <c r="N7">
+        <v>68.38991899999999</v>
+      </c>
+      <c r="O7">
+        <v>16.41358056</v>
+      </c>
+      <c r="P7">
+        <v>51.97633843999999</v>
+      </c>
+      <c r="Q7">
+        <v>183.47633844</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.09154329589294462</v>
+      </c>
+      <c r="T7">
+        <v>0.7986618807571312</v>
+      </c>
+      <c r="U7">
+        <v>0.0511</v>
+      </c>
+      <c r="V7">
+        <v>0.24</v>
+      </c>
+      <c r="W7">
+        <v>0.038836</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>9.432704802825025</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.0887865758000829</v>
+      </c>
+      <c r="C8">
+        <v>3015.304335866683</v>
+      </c>
+      <c r="D8">
+        <v>3147.856335866682</v>
+      </c>
+      <c r="E8">
+        <v>-83.94799999999998</v>
+      </c>
+      <c r="F8">
+        <v>190.452</v>
+      </c>
+      <c r="G8">
+        <v>57.9</v>
+      </c>
+      <c r="H8">
+        <v>2899.8</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>208</v>
+      </c>
+      <c r="K8">
+        <v>131.5</v>
+      </c>
+      <c r="L8">
+        <v>76.5</v>
+      </c>
+      <c r="M8">
+        <v>9.7320972</v>
+      </c>
+      <c r="N8">
+        <v>66.7679028</v>
+      </c>
+      <c r="O8">
+        <v>16.024296672</v>
+      </c>
+      <c r="P8">
+        <v>50.743606128</v>
+      </c>
+      <c r="Q8">
+        <v>182.243606128</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.09197491042562012</v>
+      </c>
+      <c r="T8">
+        <v>0.805197575362345</v>
+      </c>
+      <c r="U8">
+        <v>0.0511</v>
+      </c>
+      <c r="V8">
+        <v>0.24</v>
+      </c>
+      <c r="W8">
+        <v>0.038836</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>7.860587335687523</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.08876630050186841</v>
+      </c>
+      <c r="C9">
+        <v>2984.839671296863</v>
+      </c>
+      <c r="D9">
+        <v>3149.133671296863</v>
+      </c>
+      <c r="E9">
+        <v>-52.20599999999993</v>
+      </c>
+      <c r="F9">
+        <v>222.194</v>
+      </c>
+      <c r="G9">
+        <v>57.9</v>
+      </c>
+      <c r="H9">
+        <v>2899.8</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>208</v>
+      </c>
+      <c r="K9">
+        <v>131.5</v>
+      </c>
+      <c r="L9">
+        <v>76.5</v>
+      </c>
+      <c r="M9">
+        <v>11.776282</v>
+      </c>
+      <c r="N9">
+        <v>64.72371799999999</v>
+      </c>
+      <c r="O9">
+        <v>15.53369232</v>
+      </c>
+      <c r="P9">
+        <v>49.19002567999999</v>
+      </c>
+      <c r="Q9">
+        <v>180.69002568</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.09241580699125636</v>
+      </c>
+      <c r="T9">
+        <v>0.811873822539714</v>
+      </c>
+      <c r="U9">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V9">
+        <v>0.24</v>
+      </c>
+      <c r="W9">
+        <v>0.04028</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>6.496108024587045</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.08878098520365393</v>
+      </c>
+      <c r="C10">
+        <v>2952.172437657363</v>
+      </c>
+      <c r="D10">
+        <v>3148.208437657363</v>
+      </c>
+      <c r="E10">
+        <v>-20.46399999999994</v>
+      </c>
+      <c r="F10">
+        <v>253.936</v>
+      </c>
+      <c r="G10">
+        <v>57.9</v>
+      </c>
+      <c r="H10">
+        <v>2899.8</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>208</v>
+      </c>
+      <c r="K10">
+        <v>131.5</v>
+      </c>
+      <c r="L10">
+        <v>76.5</v>
+      </c>
+      <c r="M10">
+        <v>13.96648</v>
+      </c>
+      <c r="N10">
+        <v>62.53352</v>
+      </c>
+      <c r="O10">
+        <v>15.0080448</v>
+      </c>
+      <c r="P10">
+        <v>47.5254752</v>
+      </c>
+      <c r="Q10">
+        <v>179.0254752</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.09286628826484122</v>
+      </c>
+      <c r="T10">
+        <v>0.8186952055252865</v>
+      </c>
+      <c r="U10">
+        <v>0.055</v>
+      </c>
+      <c r="V10">
+        <v>0.24</v>
+      </c>
+      <c r="W10">
+        <v>0.0418</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>5.477400175276805</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.08868926990543943</v>
+      </c>
+      <c r="C11">
+        <v>2926.218032389626</v>
+      </c>
+      <c r="D11">
+        <v>3153.996032389626</v>
+      </c>
+      <c r="E11">
+        <v>11.27800000000002</v>
+      </c>
+      <c r="F11">
+        <v>285.678</v>
+      </c>
+      <c r="G11">
+        <v>57.9</v>
+      </c>
+      <c r="H11">
+        <v>2899.8</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>208</v>
+      </c>
+      <c r="K11">
+        <v>131.5</v>
+      </c>
+      <c r="L11">
+        <v>76.5</v>
+      </c>
+      <c r="M11">
+        <v>15.71229</v>
+      </c>
+      <c r="N11">
+        <v>60.78771</v>
+      </c>
+      <c r="O11">
+        <v>14.5890504</v>
+      </c>
+      <c r="P11">
+        <v>46.19865960000001</v>
+      </c>
+      <c r="Q11">
+        <v>177.6986596</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.09332667022575762</v>
+      </c>
+      <c r="T11">
+        <v>0.8256665090160367</v>
+      </c>
+      <c r="U11">
+        <v>0.055</v>
+      </c>
+      <c r="V11">
+        <v>0.24</v>
+      </c>
+      <c r="W11">
+        <v>0.0418</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>4.868800155801605</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.08888635460722494</v>
+      </c>
+      <c r="C12">
+        <v>2882.065379381421</v>
+      </c>
+      <c r="D12">
+        <v>3141.585379381421</v>
+      </c>
+      <c r="E12">
+        <v>43.0200000000001</v>
+      </c>
+      <c r="F12">
+        <v>317.4200000000001</v>
+      </c>
+      <c r="G12">
+        <v>57.9</v>
+      </c>
+      <c r="H12">
+        <v>2899.8</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>208</v>
+      </c>
+      <c r="K12">
+        <v>131.5</v>
+      </c>
+      <c r="L12">
+        <v>76.5</v>
+      </c>
+      <c r="M12">
+        <v>18.66429600000001</v>
+      </c>
+      <c r="N12">
+        <v>57.83570399999999</v>
+      </c>
+      <c r="O12">
+        <v>13.88056896</v>
+      </c>
+      <c r="P12">
+        <v>43.95513503999999</v>
+      </c>
+      <c r="Q12">
+        <v>175.45513504</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.09379728289691661</v>
+      </c>
+      <c r="T12">
+        <v>0.8327927303621369</v>
+      </c>
+      <c r="U12">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V12">
+        <v>0.24</v>
+      </c>
+      <c r="W12">
+        <v>0.04468800000000001</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>4.098734825037064</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.08976819930901046</v>
+      </c>
+      <c r="C13">
+        <v>2795.968105709341</v>
+      </c>
+      <c r="D13">
+        <v>3087.230105709341</v>
+      </c>
+      <c r="E13">
+        <v>74.76200000000006</v>
+      </c>
+      <c r="F13">
+        <v>349.162</v>
+      </c>
+      <c r="G13">
+        <v>57.9</v>
+      </c>
+      <c r="H13">
+        <v>2899.8</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>208</v>
+      </c>
+      <c r="K13">
+        <v>131.5</v>
+      </c>
+      <c r="L13">
+        <v>76.5</v>
+      </c>
+      <c r="M13">
+        <v>24.4762562</v>
+      </c>
+      <c r="N13">
+        <v>52.0237438</v>
+      </c>
+      <c r="O13">
+        <v>12.485698512</v>
+      </c>
+      <c r="P13">
+        <v>39.538045288</v>
+      </c>
+      <c r="Q13">
+        <v>171.038045288</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.09427847113371962</v>
+      </c>
+      <c r="T13">
+        <v>0.8400790915137673</v>
+      </c>
+      <c r="U13">
+        <v>0.0701</v>
+      </c>
+      <c r="V13">
+        <v>0.24</v>
+      </c>
+      <c r="W13">
+        <v>0.053276</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>3.125477988745681</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.09173380401079596</v>
+      </c>
+      <c r="C14">
+        <v>2649.587187825442</v>
+      </c>
+      <c r="D14">
+        <v>2972.591187825442</v>
+      </c>
+      <c r="E14">
+        <v>106.504</v>
+      </c>
+      <c r="F14">
+        <v>380.904</v>
+      </c>
+      <c r="G14">
+        <v>57.9</v>
+      </c>
+      <c r="H14">
+        <v>2899.8</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>208</v>
+      </c>
+      <c r="K14">
+        <v>131.5</v>
+      </c>
+      <c r="L14">
+        <v>76.5</v>
+      </c>
+      <c r="M14">
+        <v>34.81462560000001</v>
+      </c>
+      <c r="N14">
+        <v>41.68537439999999</v>
+      </c>
+      <c r="O14">
+        <v>10.004489856</v>
+      </c>
+      <c r="P14">
+        <v>31.68088454399999</v>
+      </c>
+      <c r="Q14">
+        <v>163.180884544</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.0947705954668136</v>
+      </c>
+      <c r="T14">
+        <v>0.84753105178248</v>
+      </c>
+      <c r="U14">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V14">
+        <v>0.24</v>
+      </c>
+      <c r="W14">
+        <v>0.06946400000000001</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>2.197352367908273</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.09191872871258147</v>
+      </c>
+      <c r="C15">
+        <v>2607.496567813973</v>
+      </c>
+      <c r="D15">
+        <v>2962.242567813973</v>
+      </c>
+      <c r="E15">
+        <v>138.2460000000001</v>
+      </c>
+      <c r="F15">
+        <v>412.6460000000001</v>
+      </c>
+      <c r="G15">
+        <v>57.9</v>
+      </c>
+      <c r="H15">
+        <v>2899.8</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>208</v>
+      </c>
+      <c r="K15">
+        <v>131.5</v>
+      </c>
+      <c r="L15">
+        <v>76.5</v>
+      </c>
+      <c r="M15">
+        <v>37.71584440000001</v>
+      </c>
+      <c r="N15">
+        <v>38.78415559999999</v>
+      </c>
+      <c r="O15">
+        <v>9.308197343999998</v>
+      </c>
+      <c r="P15">
+        <v>29.47595825599999</v>
+      </c>
+      <c r="Q15">
+        <v>160.975958256</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.09527403300296722</v>
+      </c>
+      <c r="T15">
+        <v>0.8551543214826577</v>
+      </c>
+      <c r="U15">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V15">
+        <v>0.24</v>
+      </c>
+      <c r="W15">
+        <v>0.06946400000000001</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>2.02832526268456</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.094348693414367</v>
+      </c>
+      <c r="C16">
+        <v>2446.171954156084</v>
+      </c>
+      <c r="D16">
+        <v>2832.659954156084</v>
+      </c>
+      <c r="E16">
+        <v>169.9880000000001</v>
+      </c>
+      <c r="F16">
+        <v>444.3880000000001</v>
+      </c>
+      <c r="G16">
+        <v>57.9</v>
+      </c>
+      <c r="H16">
+        <v>2899.8</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>208</v>
+      </c>
+      <c r="K16">
+        <v>131.5</v>
+      </c>
+      <c r="L16">
+        <v>76.5</v>
+      </c>
+      <c r="M16">
+        <v>49.99365000000001</v>
+      </c>
+      <c r="N16">
+        <v>26.50634999999999</v>
+      </c>
+      <c r="O16">
+        <v>6.361523999999998</v>
+      </c>
+      <c r="P16">
+        <v>20.14482599999999</v>
+      </c>
+      <c r="Q16">
+        <v>151.644826</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.09578917838879883</v>
+      </c>
+      <c r="T16">
+        <v>0.8629548765246999</v>
+      </c>
+      <c r="U16">
+        <v>0.1125</v>
+      </c>
+      <c r="V16">
+        <v>0.24</v>
+      </c>
+      <c r="W16">
+        <v>0.08550000000000001</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>1.530194334680504</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1059085043667367</v>
+      </c>
+      <c r="C17">
+        <v>1926.488613913323</v>
+      </c>
+      <c r="D17">
+        <v>2344.718613913323</v>
+      </c>
+      <c r="E17">
+        <v>201.73</v>
+      </c>
+      <c r="F17">
+        <v>476.13</v>
+      </c>
+      <c r="G17">
+        <v>57.9</v>
+      </c>
+      <c r="H17">
+        <v>2899.8</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>208</v>
+      </c>
+      <c r="K17">
+        <v>131.5</v>
+      </c>
+      <c r="L17">
+        <v>76.5</v>
+      </c>
+      <c r="M17">
+        <v>93.607158</v>
+      </c>
+      <c r="N17">
+        <v>-17.107158</v>
+      </c>
+      <c r="O17">
+        <v>-4.105717919999999</v>
+      </c>
+      <c r="P17">
+        <v>-13.00144008</v>
+      </c>
+      <c r="Q17">
+        <v>118.49855992</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.09670898700215182</v>
+      </c>
+      <c r="T17">
+        <v>0.8768830178105267</v>
+      </c>
+      <c r="U17">
+        <v>0.1966</v>
+      </c>
+      <c r="V17">
+        <v>0.1961388465612854</v>
+      </c>
+      <c r="W17">
+        <v>0.1580391027660513</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>0.8172451940053559</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1103585398230777</v>
+      </c>
+      <c r="C18">
+        <v>1748.934793369551</v>
+      </c>
+      <c r="D18">
+        <v>2198.906793369551</v>
+      </c>
+      <c r="E18">
+        <v>233.4720000000001</v>
+      </c>
+      <c r="F18">
+        <v>507.8720000000001</v>
+      </c>
+      <c r="G18">
+        <v>57.9</v>
+      </c>
+      <c r="H18">
+        <v>2899.8</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>208</v>
+      </c>
+      <c r="K18">
+        <v>131.5</v>
+      </c>
+      <c r="L18">
+        <v>76.5</v>
+      </c>
+      <c r="M18">
+        <v>108.5830336</v>
+      </c>
+      <c r="N18">
+        <v>-32.08303360000001</v>
+      </c>
+      <c r="O18">
+        <v>-7.699928064000002</v>
+      </c>
+      <c r="P18">
+        <v>-24.38310553600001</v>
+      </c>
+      <c r="Q18">
+        <v>107.116894464</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.09754127905734528</v>
+      </c>
+      <c r="T18">
+        <v>0.8894859453842837</v>
+      </c>
+      <c r="U18">
+        <v>0.2138</v>
+      </c>
+      <c r="V18">
+        <v>0.1690871896951679</v>
+      </c>
+      <c r="W18">
+        <v>0.1776491588431731</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>0.7045299570632</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1121085398230777</v>
+      </c>
+      <c r="C19">
+        <v>1664.701134175634</v>
+      </c>
+      <c r="D19">
+        <v>2146.415134175634</v>
+      </c>
+      <c r="E19">
+        <v>265.2140000000001</v>
+      </c>
+      <c r="F19">
+        <v>539.614</v>
+      </c>
+      <c r="G19">
+        <v>57.9</v>
+      </c>
+      <c r="H19">
+        <v>2899.8</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>208</v>
+      </c>
+      <c r="K19">
+        <v>131.5</v>
+      </c>
+      <c r="L19">
+        <v>76.5</v>
+      </c>
+      <c r="M19">
+        <v>115.3694732</v>
+      </c>
+      <c r="N19">
+        <v>-38.8694732</v>
+      </c>
+      <c r="O19">
+        <v>-9.328673567999999</v>
+      </c>
+      <c r="P19">
+        <v>-29.540799632</v>
+      </c>
+      <c r="Q19">
+        <v>101.959200368</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.09824900531104822</v>
+      </c>
+      <c r="T19">
+        <v>0.9002026435214437</v>
+      </c>
+      <c r="U19">
+        <v>0.2138</v>
+      </c>
+      <c r="V19">
+        <v>0.1591408844189816</v>
+      </c>
+      <c r="W19">
+        <v>0.1797756789112217</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>0.6630870184124236</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1138585398230777</v>
+      </c>
+      <c r="C20">
+        <v>1582.915175238233</v>
+      </c>
+      <c r="D20">
+        <v>2096.371175238233</v>
+      </c>
+      <c r="E20">
+        <v>296.956</v>
+      </c>
+      <c r="F20">
+        <v>571.356</v>
+      </c>
+      <c r="G20">
+        <v>57.9</v>
+      </c>
+      <c r="H20">
+        <v>2899.8</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>208</v>
+      </c>
+      <c r="K20">
+        <v>131.5</v>
+      </c>
+      <c r="L20">
+        <v>76.5</v>
+      </c>
+      <c r="M20">
+        <v>122.1559128</v>
+      </c>
+      <c r="N20">
+        <v>-45.6559128</v>
+      </c>
+      <c r="O20">
+        <v>-10.957419072</v>
+      </c>
+      <c r="P20">
+        <v>-34.698493728</v>
+      </c>
+      <c r="Q20">
+        <v>96.80150627200001</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.09897399318069516</v>
+      </c>
+      <c r="T20">
+        <v>0.911180724539998</v>
+      </c>
+      <c r="U20">
+        <v>0.2138</v>
+      </c>
+      <c r="V20">
+        <v>0.1502997241734827</v>
+      </c>
+      <c r="W20">
+        <v>0.1816659189717094</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>0.6262488507228444</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1156085398230777</v>
+      </c>
+      <c r="C21">
+        <v>1503.40961190117</v>
+      </c>
+      <c r="D21">
+        <v>2048.60761190117</v>
+      </c>
+      <c r="E21">
+        <v>328.6980000000001</v>
+      </c>
+      <c r="F21">
+        <v>603.0980000000001</v>
+      </c>
+      <c r="G21">
+        <v>57.9</v>
+      </c>
+      <c r="H21">
+        <v>2899.8</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>208</v>
+      </c>
+      <c r="K21">
+        <v>131.5</v>
+      </c>
+      <c r="L21">
+        <v>76.5</v>
+      </c>
+      <c r="M21">
+        <v>128.9423524</v>
+      </c>
+      <c r="N21">
+        <v>-52.4423524</v>
+      </c>
+      <c r="O21">
+        <v>-12.586164576</v>
+      </c>
+      <c r="P21">
+        <v>-39.856187824</v>
+      </c>
+      <c r="Q21">
+        <v>91.643812176</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.09971688198539509</v>
+      </c>
+      <c r="T21">
+        <v>0.9224298692874053</v>
+      </c>
+      <c r="U21">
+        <v>0.2138</v>
+      </c>
+      <c r="V21">
+        <v>0.1423892123748783</v>
+      </c>
+      <c r="W21">
+        <v>0.183357186394251</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>0.5932883848953263</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1173585398230777</v>
+      </c>
+      <c r="C22">
+        <v>1426.032047277628</v>
+      </c>
+      <c r="D22">
+        <v>2002.972047277629</v>
+      </c>
+      <c r="E22">
+        <v>360.4400000000002</v>
+      </c>
+      <c r="F22">
+        <v>634.8400000000001</v>
+      </c>
+      <c r="G22">
+        <v>57.9</v>
+      </c>
+      <c r="H22">
+        <v>2899.8</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>208</v>
+      </c>
+      <c r="K22">
+        <v>131.5</v>
+      </c>
+      <c r="L22">
+        <v>76.5</v>
+      </c>
+      <c r="M22">
+        <v>135.728792</v>
+      </c>
+      <c r="N22">
+        <v>-59.22879200000003</v>
+      </c>
+      <c r="O22">
+        <v>-14.21491008000001</v>
+      </c>
+      <c r="P22">
+        <v>-45.01388192000002</v>
+      </c>
+      <c r="Q22">
+        <v>86.48611807999998</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1004783430102126</v>
+      </c>
+      <c r="T22">
+        <v>0.9339602426534981</v>
+      </c>
+      <c r="U22">
+        <v>0.2138</v>
+      </c>
+      <c r="V22">
+        <v>0.1352697517561343</v>
+      </c>
+      <c r="W22">
+        <v>0.1848793270745385</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>0.5636239656505599</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1191085398230777</v>
+      </c>
+      <c r="C23">
+        <v>1350.643367977297</v>
+      </c>
+      <c r="D23">
+        <v>1959.325367977297</v>
+      </c>
+      <c r="E23">
+        <v>392.182</v>
+      </c>
+      <c r="F23">
+        <v>666.582</v>
+      </c>
+      <c r="G23">
+        <v>57.9</v>
+      </c>
+      <c r="H23">
+        <v>2899.8</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>208</v>
+      </c>
+      <c r="K23">
+        <v>131.5</v>
+      </c>
+      <c r="L23">
+        <v>76.5</v>
+      </c>
+      <c r="M23">
+        <v>142.5152316</v>
+      </c>
+      <c r="N23">
+        <v>-66.01523159999999</v>
+      </c>
+      <c r="O23">
+        <v>-15.843655584</v>
+      </c>
+      <c r="P23">
+        <v>-50.171576016</v>
+      </c>
+      <c r="Q23">
+        <v>81.32842398400001</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1012590815293291</v>
+      </c>
+      <c r="T23">
+        <v>0.9457825242060738</v>
+      </c>
+      <c r="U23">
+        <v>0.2138</v>
+      </c>
+      <c r="V23">
+        <v>0.1288283350058423</v>
+      </c>
+      <c r="W23">
+        <v>0.1862565019757509</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>0.5367847291910095</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1208585398230777</v>
+      </c>
+      <c r="C24">
+        <v>1277.116327671279</v>
+      </c>
+      <c r="D24">
+        <v>1917.540327671279</v>
+      </c>
+      <c r="E24">
+        <v>423.9240000000001</v>
+      </c>
+      <c r="F24">
+        <v>698.3240000000001</v>
+      </c>
+      <c r="G24">
+        <v>57.9</v>
+      </c>
+      <c r="H24">
+        <v>2899.8</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>208</v>
+      </c>
+      <c r="K24">
+        <v>131.5</v>
+      </c>
+      <c r="L24">
+        <v>76.5</v>
+      </c>
+      <c r="M24">
+        <v>149.3016712</v>
+      </c>
+      <c r="N24">
+        <v>-72.80167120000002</v>
+      </c>
+      <c r="O24">
+        <v>-17.472401088</v>
+      </c>
+      <c r="P24">
+        <v>-55.32927011200002</v>
+      </c>
+      <c r="Q24">
+        <v>76.17072988799998</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1020598389848334</v>
+      </c>
+      <c r="T24">
+        <v>0.9579079411830749</v>
+      </c>
+      <c r="U24">
+        <v>0.2138</v>
+      </c>
+      <c r="V24">
+        <v>0.1229725015964858</v>
+      </c>
+      <c r="W24">
+        <v>0.1875084791586713</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>0.5123854233186909</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1285021781376924</v>
+      </c>
+      <c r="C25">
+        <v>1081.978242729967</v>
+      </c>
+      <c r="D25">
+        <v>1754.144242729968</v>
+      </c>
+      <c r="E25">
+        <v>455.6660000000002</v>
+      </c>
+      <c r="F25">
+        <v>730.0660000000001</v>
+      </c>
+      <c r="G25">
+        <v>57.9</v>
+      </c>
+      <c r="H25">
+        <v>2899.8</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>208</v>
+      </c>
+      <c r="K25">
+        <v>131.5</v>
+      </c>
+      <c r="L25">
+        <v>76.5</v>
+      </c>
+      <c r="M25">
+        <v>174.3397608000001</v>
+      </c>
+      <c r="N25">
+        <v>-97.83976080000005</v>
+      </c>
+      <c r="O25">
+        <v>-23.48154259200001</v>
+      </c>
+      <c r="P25">
+        <v>-74.35821820800004</v>
+      </c>
+      <c r="Q25">
+        <v>57.14178179199996</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1030679386010191</v>
+      </c>
+      <c r="T25">
+        <v>0.9731730231583782</v>
+      </c>
+      <c r="U25">
+        <v>0.2388</v>
+      </c>
+      <c r="V25">
+        <v>0.1053116048556606</v>
+      </c>
+      <c r="W25">
+        <v>0.2136515887604682</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>0.4387983535652527</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1305021781376924</v>
+      </c>
+      <c r="C26">
+        <v>1011.978825548533</v>
+      </c>
+      <c r="D26">
+        <v>1715.886825548533</v>
+      </c>
+      <c r="E26">
+        <v>487.408</v>
+      </c>
+      <c r="F26">
+        <v>761.808</v>
+      </c>
+      <c r="G26">
+        <v>57.9</v>
+      </c>
+      <c r="H26">
+        <v>2899.8</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>208</v>
+      </c>
+      <c r="K26">
+        <v>131.5</v>
+      </c>
+      <c r="L26">
+        <v>76.5</v>
+      </c>
+      <c r="M26">
+        <v>181.9197504</v>
+      </c>
+      <c r="N26">
+        <v>-105.4197504</v>
+      </c>
+      <c r="O26">
+        <v>-25.300740096</v>
+      </c>
+      <c r="P26">
+        <v>-80.119010304</v>
+      </c>
+      <c r="Q26">
+        <v>51.380989696</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1039135693720852</v>
+      </c>
+      <c r="T26">
+        <v>0.9859779313578305</v>
+      </c>
+      <c r="U26">
+        <v>0.2388</v>
+      </c>
+      <c r="V26">
+        <v>0.1009236213200081</v>
+      </c>
+      <c r="W26">
+        <v>0.2146994392287821</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.4205150888333673</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1325021781376924</v>
+      </c>
+      <c r="C27">
+        <v>943.6125579028634</v>
+      </c>
+      <c r="D27">
+        <v>1679.262557902863</v>
+      </c>
+      <c r="E27">
+        <v>519.1500000000001</v>
+      </c>
+      <c r="F27">
+        <v>793.5500000000001</v>
+      </c>
+      <c r="G27">
+        <v>57.9</v>
+      </c>
+      <c r="H27">
+        <v>2899.8</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>208</v>
+      </c>
+      <c r="K27">
+        <v>131.5</v>
+      </c>
+      <c r="L27">
+        <v>76.5</v>
+      </c>
+      <c r="M27">
+        <v>189.49974</v>
+      </c>
+      <c r="N27">
+        <v>-112.99974</v>
+      </c>
+      <c r="O27">
+        <v>-27.11993760000001</v>
+      </c>
+      <c r="P27">
+        <v>-85.87980240000002</v>
+      </c>
+      <c r="Q27">
+        <v>45.62019759999998</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1047817502970463</v>
+      </c>
+      <c r="T27">
+        <v>0.9991243037759349</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>0.09688667646720779</v>
+      </c>
+      <c r="W27">
+        <v>0.2156634616596308</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.4036944852800325</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1345021781376924</v>
+      </c>
+      <c r="C28">
+        <v>876.7770503029251</v>
+      </c>
+      <c r="D28">
+        <v>1644.169050302925</v>
+      </c>
+      <c r="E28">
+        <v>550.8920000000002</v>
+      </c>
+      <c r="F28">
+        <v>825.2920000000001</v>
+      </c>
+      <c r="G28">
+        <v>57.9</v>
+      </c>
+      <c r="H28">
+        <v>2899.8</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>208</v>
+      </c>
+      <c r="K28">
+        <v>131.5</v>
+      </c>
+      <c r="L28">
+        <v>76.5</v>
+      </c>
+      <c r="M28">
+        <v>197.0797296</v>
+      </c>
+      <c r="N28">
+        <v>-120.5797296</v>
+      </c>
+      <c r="O28">
+        <v>-28.93913510400001</v>
+      </c>
+      <c r="P28">
+        <v>-91.64059449600003</v>
+      </c>
+      <c r="Q28">
+        <v>39.85940550399997</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1056733955713307</v>
+      </c>
+      <c r="T28">
+        <v>1.012625983556691</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>0.09316026583385364</v>
+      </c>
+      <c r="W28">
+        <v>0.2165533285188758</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.3881677743077235</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1365021781376924</v>
+      </c>
+      <c r="C29">
+        <v>811.3782970627715</v>
+      </c>
+      <c r="D29">
+        <v>1610.512297062771</v>
+      </c>
+      <c r="E29">
+        <v>582.6340000000001</v>
+      </c>
+      <c r="F29">
+        <v>857.0340000000001</v>
+      </c>
+      <c r="G29">
+        <v>57.9</v>
+      </c>
+      <c r="H29">
+        <v>2899.8</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>208</v>
+      </c>
+      <c r="K29">
+        <v>131.5</v>
+      </c>
+      <c r="L29">
+        <v>76.5</v>
+      </c>
+      <c r="M29">
+        <v>204.6597192</v>
+      </c>
+      <c r="N29">
+        <v>-128.1597192</v>
+      </c>
+      <c r="O29">
+        <v>-30.75833260800001</v>
+      </c>
+      <c r="P29">
+        <v>-97.40138659200004</v>
+      </c>
+      <c r="Q29">
+        <v>34.09861340799996</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1065894694832668</v>
+      </c>
+      <c r="T29">
+        <v>1.026497572372536</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>0.08970988561778499</v>
+      </c>
+      <c r="W29">
+        <v>0.217377279314473</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.3737911900741041</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1385021781376924</v>
+      </c>
+      <c r="C30">
+        <v>747.3298354157931</v>
+      </c>
+      <c r="D30">
+        <v>1578.205835415793</v>
+      </c>
+      <c r="E30">
+        <v>614.3760000000002</v>
+      </c>
+      <c r="F30">
+        <v>888.7760000000002</v>
+      </c>
+      <c r="G30">
+        <v>57.9</v>
+      </c>
+      <c r="H30">
+        <v>2899.8</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>208</v>
+      </c>
+      <c r="K30">
+        <v>131.5</v>
+      </c>
+      <c r="L30">
+        <v>76.5</v>
+      </c>
+      <c r="M30">
+        <v>212.2397088</v>
+      </c>
+      <c r="N30">
+        <v>-135.7397088</v>
+      </c>
+      <c r="O30">
+        <v>-32.57753011200001</v>
+      </c>
+      <c r="P30">
+        <v>-103.162178688</v>
+      </c>
+      <c r="Q30">
+        <v>28.33782131199996</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1075309898927566</v>
+      </c>
+      <c r="T30">
+        <v>1.040754483099932</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>0.08650596113143554</v>
+      </c>
+      <c r="W30">
+        <v>0.2181423764818132</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.3604415047143147</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1405021781376924</v>
+      </c>
+      <c r="C31">
+        <v>684.5520038472878</v>
+      </c>
+      <c r="D31">
+        <v>1547.170003847288</v>
+      </c>
+      <c r="E31">
+        <v>646.1180000000001</v>
+      </c>
+      <c r="F31">
+        <v>920.518</v>
+      </c>
+      <c r="G31">
+        <v>57.9</v>
+      </c>
+      <c r="H31">
+        <v>2899.8</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>208</v>
+      </c>
+      <c r="K31">
+        <v>131.5</v>
+      </c>
+      <c r="L31">
+        <v>76.5</v>
+      </c>
+      <c r="M31">
+        <v>219.8196984</v>
+      </c>
+      <c r="N31">
+        <v>-143.3196984</v>
+      </c>
+      <c r="O31">
+        <v>-34.39672761600001</v>
+      </c>
+      <c r="P31">
+        <v>-108.922970784</v>
+      </c>
+      <c r="Q31">
+        <v>22.57702921599999</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1084990320039222</v>
+      </c>
+      <c r="T31">
+        <v>1.05541299694641</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>0.08352299695448949</v>
+      </c>
+      <c r="W31">
+        <v>0.2188547083272679</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.3480124873103728</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1425021781376924</v>
+      </c>
+      <c r="C32">
+        <v>622.9712862498038</v>
+      </c>
+      <c r="D32">
+        <v>1517.331286249804</v>
+      </c>
+      <c r="E32">
+        <v>677.86</v>
+      </c>
+      <c r="F32">
+        <v>952.26</v>
+      </c>
+      <c r="G32">
+        <v>57.9</v>
+      </c>
+      <c r="H32">
+        <v>2899.8</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>208</v>
+      </c>
+      <c r="K32">
+        <v>131.5</v>
+      </c>
+      <c r="L32">
+        <v>76.5</v>
+      </c>
+      <c r="M32">
+        <v>227.399688</v>
+      </c>
+      <c r="N32">
+        <v>-150.899688</v>
+      </c>
+      <c r="O32">
+        <v>-36.21592512</v>
+      </c>
+      <c r="P32">
+        <v>-114.68376288</v>
+      </c>
+      <c r="Q32">
+        <v>16.81623712000001</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1094947324611211</v>
+      </c>
+      <c r="T32">
+        <v>1.070490325474216</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>0.08073889705600651</v>
+      </c>
+      <c r="W32">
+        <v>0.2195195513830256</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.3364120710666938</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1445021781376924</v>
+      </c>
+      <c r="C33">
+        <v>562.5197305342487</v>
+      </c>
+      <c r="D33">
+        <v>1488.621730534249</v>
+      </c>
+      <c r="E33">
+        <v>709.6020000000001</v>
+      </c>
+      <c r="F33">
+        <v>984.0020000000001</v>
+      </c>
+      <c r="G33">
+        <v>57.9</v>
+      </c>
+      <c r="H33">
+        <v>2899.8</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>208</v>
+      </c>
+      <c r="K33">
+        <v>131.5</v>
+      </c>
+      <c r="L33">
+        <v>76.5</v>
+      </c>
+      <c r="M33">
+        <v>234.9796776</v>
+      </c>
+      <c r="N33">
+        <v>-158.4796776</v>
+      </c>
+      <c r="O33">
+        <v>-38.035122624</v>
+      </c>
+      <c r="P33">
+        <v>-120.444554976</v>
+      </c>
+      <c r="Q33">
+        <v>11.05544502399997</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1105192938011373</v>
+      </c>
+      <c r="T33">
+        <v>1.08600467801732</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>0.07813441650581275</v>
+      </c>
+      <c r="W33">
+        <v>0.2201415013384119</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.3255600687742197</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1465021781376925</v>
+      </c>
+      <c r="C34">
+        <v>503.1344320183891</v>
+      </c>
+      <c r="D34">
+        <v>1460.978432018389</v>
+      </c>
+      <c r="E34">
+        <v>741.3440000000002</v>
+      </c>
+      <c r="F34">
+        <v>1015.744</v>
+      </c>
+      <c r="G34">
+        <v>57.9</v>
+      </c>
+      <c r="H34">
+        <v>2899.8</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>208</v>
+      </c>
+      <c r="K34">
+        <v>131.5</v>
+      </c>
+      <c r="L34">
+        <v>76.5</v>
+      </c>
+      <c r="M34">
+        <v>242.5596672</v>
+      </c>
+      <c r="N34">
+        <v>-166.0596672</v>
+      </c>
+      <c r="O34">
+        <v>-39.854320128</v>
+      </c>
+      <c r="P34">
+        <v>-126.205347072</v>
+      </c>
+      <c r="Q34">
+        <v>5.294652927999977</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1115739892982129</v>
+      </c>
+      <c r="T34">
+        <v>1.101975335046987</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>0.0756927159900061</v>
+      </c>
+      <c r="W34">
+        <v>0.2207245794215866</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.3153863166250254</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1485021781376925</v>
+      </c>
+      <c r="C35">
+        <v>444.7570733259729</v>
+      </c>
+      <c r="D35">
+        <v>1434.343073325973</v>
+      </c>
+      <c r="E35">
+        <v>773.0860000000001</v>
+      </c>
+      <c r="F35">
+        <v>1047.486</v>
+      </c>
+      <c r="G35">
+        <v>57.9</v>
+      </c>
+      <c r="H35">
+        <v>2899.8</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>208</v>
+      </c>
+      <c r="K35">
+        <v>131.5</v>
+      </c>
+      <c r="L35">
+        <v>76.5</v>
+      </c>
+      <c r="M35">
+        <v>250.1396568</v>
+      </c>
+      <c r="N35">
+        <v>-173.6396568</v>
+      </c>
+      <c r="O35">
+        <v>-41.67351763200001</v>
+      </c>
+      <c r="P35">
+        <v>-131.966139168</v>
+      </c>
+      <c r="Q35">
+        <v>-0.4661391680000406</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1126601682429623</v>
+      </c>
+      <c r="T35">
+        <v>1.11842272810739</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>0.07339899732364227</v>
+      </c>
+      <c r="W35">
+        <v>0.2212723194391142</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.3058291555151762</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1505021781376925</v>
+      </c>
+      <c r="C36">
+        <v>387.3335137138067</v>
+      </c>
+      <c r="D36">
+        <v>1408.661513713807</v>
+      </c>
+      <c r="E36">
+        <v>804.8280000000001</v>
+      </c>
+      <c r="F36">
+        <v>1079.228</v>
+      </c>
+      <c r="G36">
+        <v>57.9</v>
+      </c>
+      <c r="H36">
+        <v>2899.8</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>208</v>
+      </c>
+      <c r="K36">
+        <v>131.5</v>
+      </c>
+      <c r="L36">
+        <v>76.5</v>
+      </c>
+      <c r="M36">
+        <v>257.7196464</v>
+      </c>
+      <c r="N36">
+        <v>-181.2196464</v>
+      </c>
+      <c r="O36">
+        <v>-43.49271513600001</v>
+      </c>
+      <c r="P36">
+        <v>-137.726931264</v>
+      </c>
+      <c r="Q36">
+        <v>-6.226931264000029</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.113779261701189</v>
+      </c>
+      <c r="T36">
+        <v>1.135368527018108</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>0.0712402032847116</v>
+      </c>
+      <c r="W36">
+        <v>0.2217878394556109</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.296834180352965</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1525021781376925</v>
+      </c>
+      <c r="C37">
+        <v>330.813421740794</v>
+      </c>
+      <c r="D37">
+        <v>1383.883421740794</v>
+      </c>
+      <c r="E37">
+        <v>836.5700000000003</v>
+      </c>
+      <c r="F37">
+        <v>1110.97</v>
+      </c>
+      <c r="G37">
+        <v>57.9</v>
+      </c>
+      <c r="H37">
+        <v>2899.8</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>208</v>
+      </c>
+      <c r="K37">
+        <v>131.5</v>
+      </c>
+      <c r="L37">
+        <v>76.5</v>
+      </c>
+      <c r="M37">
+        <v>265.2996360000001</v>
+      </c>
+      <c r="N37">
+        <v>-188.7996360000001</v>
+      </c>
+      <c r="O37">
+        <v>-45.31191264000002</v>
+      </c>
+      <c r="P37">
+        <v>-143.4877233600001</v>
+      </c>
+      <c r="Q37">
+        <v>-11.98772336000007</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1149327888042842</v>
+      </c>
+      <c r="T37">
+        <v>1.152835735126079</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>0.06920476890514841</v>
+      </c>
+      <c r="W37">
+        <v>0.2222739011854506</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.2883532037714518</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1545021781376924</v>
+      </c>
+      <c r="C38">
+        <v>275.1499460345397</v>
+      </c>
+      <c r="D38">
+        <v>1359.96194603454</v>
+      </c>
+      <c r="E38">
+        <v>868.312</v>
+      </c>
+      <c r="F38">
+        <v>1142.712</v>
+      </c>
+      <c r="G38">
+        <v>57.9</v>
+      </c>
+      <c r="H38">
+        <v>2899.8</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>208</v>
+      </c>
+      <c r="K38">
+        <v>131.5</v>
+      </c>
+      <c r="L38">
+        <v>76.5</v>
+      </c>
+      <c r="M38">
+        <v>272.8796256</v>
+      </c>
+      <c r="N38">
+        <v>-196.3796256</v>
+      </c>
+      <c r="O38">
+        <v>-47.131110144</v>
+      </c>
+      <c r="P38">
+        <v>-149.248515456</v>
+      </c>
+      <c r="Q38">
+        <v>-17.74851545600001</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1161223636293512</v>
+      </c>
+      <c r="T38">
+        <v>1.170848793487424</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>0.06728241421333876</v>
+      </c>
+      <c r="W38">
+        <v>0.2227329594858547</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.2803433925555782</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1565021781376925</v>
+      </c>
+      <c r="C39">
+        <v>220.299419624032</v>
+      </c>
+      <c r="D39">
+        <v>1336.853419624032</v>
+      </c>
+      <c r="E39">
+        <v>900.0540000000002</v>
+      </c>
+      <c r="F39">
+        <v>1174.454</v>
+      </c>
+      <c r="G39">
+        <v>57.9</v>
+      </c>
+      <c r="H39">
+        <v>2899.8</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>208</v>
+      </c>
+      <c r="K39">
+        <v>131.5</v>
+      </c>
+      <c r="L39">
+        <v>76.5</v>
+      </c>
+      <c r="M39">
+        <v>280.4596152</v>
+      </c>
+      <c r="N39">
+        <v>-203.9596152</v>
+      </c>
+      <c r="O39">
+        <v>-48.95030764800001</v>
+      </c>
+      <c r="P39">
+        <v>-155.009307552</v>
+      </c>
+      <c r="Q39">
+        <v>-23.50930755200002</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.117349702734579</v>
+      </c>
+      <c r="T39">
+        <v>1.189433694971351</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0.06546397058595123</v>
+      </c>
+      <c r="W39">
+        <v>0.2231672038240749</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.2727665441081301</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1585021781376925</v>
+      </c>
+      <c r="C40">
+        <v>166.2210939126273</v>
+      </c>
+      <c r="D40">
+        <v>1314.517093912627</v>
+      </c>
+      <c r="E40">
+        <v>931.7960000000002</v>
+      </c>
+      <c r="F40">
+        <v>1206.196</v>
+      </c>
+      <c r="G40">
+        <v>57.9</v>
+      </c>
+      <c r="H40">
+        <v>2899.8</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>208</v>
+      </c>
+      <c r="K40">
+        <v>131.5</v>
+      </c>
+      <c r="L40">
+        <v>76.5</v>
+      </c>
+      <c r="M40">
+        <v>288.0396048000001</v>
+      </c>
+      <c r="N40">
+        <v>-211.5396048000001</v>
+      </c>
+      <c r="O40">
+        <v>-50.76950515200001</v>
+      </c>
+      <c r="P40">
+        <v>-160.770099648</v>
+      </c>
+      <c r="Q40">
+        <v>-29.27009964800004</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1186166334238464</v>
+      </c>
+      <c r="T40">
+        <v>1.208618109406373</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0.06374123451789987</v>
+      </c>
+      <c r="W40">
+        <v>0.2235785931971255</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.2655884771579161</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1605021781376925</v>
+      </c>
+      <c r="C41">
+        <v>112.8768988816496</v>
+      </c>
+      <c r="D41">
+        <v>1292.91489888165</v>
+      </c>
+      <c r="E41">
+        <v>963.5380000000001</v>
+      </c>
+      <c r="F41">
+        <v>1237.938</v>
+      </c>
+      <c r="G41">
+        <v>57.9</v>
+      </c>
+      <c r="H41">
+        <v>2899.8</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>208</v>
+      </c>
+      <c r="K41">
+        <v>131.5</v>
+      </c>
+      <c r="L41">
+        <v>76.5</v>
+      </c>
+      <c r="M41">
+        <v>295.6195944</v>
+      </c>
+      <c r="N41">
+        <v>-219.1195944</v>
+      </c>
+      <c r="O41">
+        <v>-52.58870265600001</v>
+      </c>
+      <c r="P41">
+        <v>-166.530891744</v>
+      </c>
+      <c r="Q41">
+        <v>-35.03089174400003</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1199251028242373</v>
+      </c>
+      <c r="T41">
+        <v>1.228431521035986</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0.06210684388923578</v>
+      </c>
+      <c r="W41">
+        <v>0.2239688856792505</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.258778516205149</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1625021781376924</v>
+      </c>
+      <c r="C42">
+        <v>60.23122655596899</v>
+      </c>
+      <c r="D42">
+        <v>1272.011226555969</v>
+      </c>
+      <c r="E42">
+        <v>995.2800000000003</v>
+      </c>
+      <c r="F42">
+        <v>1269.68</v>
+      </c>
+      <c r="G42">
+        <v>57.9</v>
+      </c>
+      <c r="H42">
+        <v>2899.8</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>208</v>
+      </c>
+      <c r="K42">
+        <v>131.5</v>
+      </c>
+      <c r="L42">
+        <v>76.5</v>
+      </c>
+      <c r="M42">
+        <v>303.1995840000001</v>
+      </c>
+      <c r="N42">
+        <v>-226.6995840000001</v>
+      </c>
+      <c r="O42">
+        <v>-54.40790016000002</v>
+      </c>
+      <c r="P42">
+        <v>-172.29168384</v>
+      </c>
+      <c r="Q42">
+        <v>-40.79168384000005</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1212771878713079</v>
+      </c>
+      <c r="T42">
+        <v>1.248905379719919</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.06055417279200487</v>
+      </c>
+      <c r="W42">
+        <v>0.2243396635372692</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.2523090533000203</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1645021781376925</v>
+      </c>
+      <c r="C43">
+        <v>8.25073514076621</v>
+      </c>
+      <c r="D43">
+        <v>1251.772735140766</v>
+      </c>
+      <c r="E43">
+        <v>1027.022</v>
+      </c>
+      <c r="F43">
+        <v>1301.422</v>
+      </c>
+      <c r="G43">
+        <v>57.9</v>
+      </c>
+      <c r="H43">
+        <v>2899.8</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>208</v>
+      </c>
+      <c r="K43">
+        <v>131.5</v>
+      </c>
+      <c r="L43">
+        <v>76.5</v>
+      </c>
+      <c r="M43">
+        <v>310.7795736</v>
+      </c>
+      <c r="N43">
+        <v>-234.2795736</v>
+      </c>
+      <c r="O43">
+        <v>-56.22709766400001</v>
+      </c>
+      <c r="P43">
+        <v>-178.052475936</v>
+      </c>
+      <c r="Q43">
+        <v>-46.55247593600004</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1226751063098047</v>
+      </c>
+      <c r="T43">
+        <v>1.270073267511782</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.05907724174829744</v>
+      </c>
+      <c r="W43">
+        <v>0.2246923546705066</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.2461551739512393</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1665021781376924</v>
+      </c>
+      <c r="C44">
+        <v>-43.09582843670137</v>
+      </c>
+      <c r="D44">
+        <v>1232.168171563299</v>
+      </c>
+      <c r="E44">
+        <v>1058.764</v>
+      </c>
+      <c r="F44">
+        <v>1333.164</v>
+      </c>
+      <c r="G44">
+        <v>57.9</v>
+      </c>
+      <c r="H44">
+        <v>2899.8</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>208</v>
+      </c>
+      <c r="K44">
+        <v>131.5</v>
+      </c>
+      <c r="L44">
+        <v>76.5</v>
+      </c>
+      <c r="M44">
+        <v>318.3595632</v>
+      </c>
+      <c r="N44">
+        <v>-241.8595632</v>
+      </c>
+      <c r="O44">
+        <v>-58.046295168</v>
+      </c>
+      <c r="P44">
+        <v>-183.813268032</v>
+      </c>
+      <c r="Q44">
+        <v>-52.31326803200002</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1241212288323875</v>
+      </c>
+      <c r="T44">
+        <v>1.291971082468881</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.05767064075429036</v>
+      </c>
+      <c r="W44">
+        <v>0.2250282509878755</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.2402943364762099</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1685021781376924</v>
+      </c>
+      <c r="C45">
+        <v>-93.83778956696437</v>
+      </c>
+      <c r="D45">
+        <v>1213.168210433036</v>
+      </c>
+      <c r="E45">
+        <v>1090.506</v>
+      </c>
+      <c r="F45">
+        <v>1364.906</v>
+      </c>
+      <c r="G45">
+        <v>57.9</v>
+      </c>
+      <c r="H45">
+        <v>2899.8</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>208</v>
+      </c>
+      <c r="K45">
+        <v>131.5</v>
+      </c>
+      <c r="L45">
+        <v>76.5</v>
+      </c>
+      <c r="M45">
+        <v>325.9395528000001</v>
+      </c>
+      <c r="N45">
+        <v>-249.4395528000001</v>
+      </c>
+      <c r="O45">
+        <v>-59.86549267200001</v>
+      </c>
+      <c r="P45">
+        <v>-189.574060128</v>
+      </c>
+      <c r="Q45">
+        <v>-58.07406012800004</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1256180924961136</v>
+      </c>
+      <c r="T45">
+        <v>1.314637241810441</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.05632946306233012</v>
+      </c>
+      <c r="W45">
+        <v>0.2253485242207156</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.2347060960930422</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1705021781376924</v>
+      </c>
+      <c r="C46">
+        <v>-144.0026923251053</v>
+      </c>
+      <c r="D46">
+        <v>1194.745307674895</v>
+      </c>
+      <c r="E46">
+        <v>1122.248</v>
+      </c>
+      <c r="F46">
+        <v>1396.648</v>
+      </c>
+      <c r="G46">
+        <v>57.9</v>
+      </c>
+      <c r="H46">
+        <v>2899.8</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>208</v>
+      </c>
+      <c r="K46">
+        <v>131.5</v>
+      </c>
+      <c r="L46">
+        <v>76.5</v>
+      </c>
+      <c r="M46">
+        <v>333.5195424</v>
+      </c>
+      <c r="N46">
+        <v>-257.0195424</v>
+      </c>
+      <c r="O46">
+        <v>-61.684690176</v>
+      </c>
+      <c r="P46">
+        <v>-195.334852224</v>
+      </c>
+      <c r="Q46">
+        <v>-63.83485222400003</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1271684155764013</v>
+      </c>
+      <c r="T46">
+        <v>1.33811290684277</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.0550492479927317</v>
+      </c>
+      <c r="W46">
+        <v>0.2256542395793357</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.2293718666363821</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1725021781376924</v>
+      </c>
+      <c r="C47">
+        <v>-193.6164327008603</v>
+      </c>
+      <c r="D47">
+        <v>1176.87356729914</v>
+      </c>
+      <c r="E47">
+        <v>1153.99</v>
+      </c>
+      <c r="F47">
+        <v>1428.39</v>
+      </c>
+      <c r="G47">
+        <v>57.9</v>
+      </c>
+      <c r="H47">
+        <v>2899.8</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>208</v>
+      </c>
+      <c r="K47">
+        <v>131.5</v>
+      </c>
+      <c r="L47">
+        <v>76.5</v>
+      </c>
+      <c r="M47">
+        <v>341.0995320000001</v>
+      </c>
+      <c r="N47">
+        <v>-264.5995320000001</v>
+      </c>
+      <c r="O47">
+        <v>-63.50388768000001</v>
+      </c>
+      <c r="P47">
+        <v>-201.09564432</v>
+      </c>
+      <c r="Q47">
+        <v>-69.59564432000005</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1287751140414268</v>
+      </c>
+      <c r="T47">
+        <v>1.362442232421729</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.053825931370671</v>
+      </c>
+      <c r="W47">
+        <v>0.2259463675886838</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.2242747140444625</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1745021781376925</v>
+      </c>
+      <c r="C48">
+        <v>-242.7033800473214</v>
+      </c>
+      <c r="D48">
+        <v>1159.528619952679</v>
+      </c>
+      <c r="E48">
+        <v>1185.732</v>
+      </c>
+      <c r="F48">
+        <v>1460.132</v>
+      </c>
+      <c r="G48">
+        <v>57.9</v>
+      </c>
+      <c r="H48">
+        <v>2899.8</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>208</v>
+      </c>
+      <c r="K48">
+        <v>131.5</v>
+      </c>
+      <c r="L48">
+        <v>76.5</v>
+      </c>
+      <c r="M48">
+        <v>348.6795216000001</v>
+      </c>
+      <c r="N48">
+        <v>-272.1795216000001</v>
+      </c>
+      <c r="O48">
+        <v>-65.32308518400002</v>
+      </c>
+      <c r="P48">
+        <v>-206.8564364160001</v>
+      </c>
+      <c r="Q48">
+        <v>-75.35643641600007</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1304413198570088</v>
+      </c>
+      <c r="T48">
+        <v>1.387672644133243</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.05265580242783031</v>
+      </c>
+      <c r="W48">
+        <v>0.2262257943802341</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.2193991767826263</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1765021781376925</v>
+      </c>
+      <c r="C49">
+        <v>-291.2864879460392</v>
+      </c>
+      <c r="D49">
+        <v>1142.687512053961</v>
+      </c>
+      <c r="E49">
+        <v>1217.474</v>
+      </c>
+      <c r="F49">
+        <v>1491.874</v>
+      </c>
+      <c r="G49">
+        <v>57.9</v>
+      </c>
+      <c r="H49">
+        <v>2899.8</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>208</v>
+      </c>
+      <c r="K49">
+        <v>131.5</v>
+      </c>
+      <c r="L49">
+        <v>76.5</v>
+      </c>
+      <c r="M49">
+        <v>356.2595112000001</v>
+      </c>
+      <c r="N49">
+        <v>-279.7595112000001</v>
+      </c>
+      <c r="O49">
+        <v>-67.14228268800002</v>
+      </c>
+      <c r="P49">
+        <v>-212.6172285120001</v>
+      </c>
+      <c r="Q49">
+        <v>-81.11722851200005</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1321704013637448</v>
+      </c>
+      <c r="T49">
+        <v>1.413855146852738</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.05153546620596159</v>
+      </c>
+      <c r="W49">
+        <v>0.2264933306700164</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.2147311091915066</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1785021781376924</v>
+      </c>
+      <c r="C50">
+        <v>-339.3873955491499</v>
+      </c>
+      <c r="D50">
+        <v>1126.32860445085</v>
+      </c>
+      <c r="E50">
+        <v>1249.216</v>
+      </c>
+      <c r="F50">
+        <v>1523.616</v>
+      </c>
+      <c r="G50">
+        <v>57.9</v>
+      </c>
+      <c r="H50">
+        <v>2899.8</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>208</v>
+      </c>
+      <c r="K50">
+        <v>131.5</v>
+      </c>
+      <c r="L50">
+        <v>76.5</v>
+      </c>
+      <c r="M50">
+        <v>363.8395008</v>
+      </c>
+      <c r="N50">
+        <v>-287.3395008</v>
+      </c>
+      <c r="O50">
+        <v>-68.961480192</v>
+      </c>
+      <c r="P50">
+        <v>-218.378020608</v>
+      </c>
+      <c r="Q50">
+        <v>-86.87802060799999</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1339659860053553</v>
+      </c>
+      <c r="T50">
+        <v>1.441044668907598</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.05046181066000407</v>
+      </c>
+      <c r="W50">
+        <v>0.226749719614391</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.2102575444166837</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1805021781376925</v>
+      </c>
+      <c r="C51">
+        <v>-387.0265203393762</v>
+      </c>
+      <c r="D51">
+        <v>1110.431479660624</v>
+      </c>
+      <c r="E51">
+        <v>1280.958</v>
+      </c>
+      <c r="F51">
+        <v>1555.358</v>
+      </c>
+      <c r="G51">
+        <v>57.9</v>
+      </c>
+      <c r="H51">
+        <v>2899.8</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>208</v>
+      </c>
+      <c r="K51">
+        <v>131.5</v>
+      </c>
+      <c r="L51">
+        <v>76.5</v>
+      </c>
+      <c r="M51">
+        <v>371.4194904000001</v>
+      </c>
+      <c r="N51">
+        <v>-294.9194904000001</v>
+      </c>
+      <c r="O51">
+        <v>-70.78067769600001</v>
+      </c>
+      <c r="P51">
+        <v>-224.1388127040001</v>
+      </c>
+      <c r="Q51">
+        <v>-92.63881270400009</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1358319857309505</v>
+      </c>
+      <c r="T51">
+        <v>1.469300446729316</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.04943197778939173</v>
+      </c>
+      <c r="W51">
+        <v>0.2269956437038933</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.2059665741224656</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1825021781376925</v>
+      </c>
+      <c r="C52">
+        <v>-434.2231431440025</v>
+      </c>
+      <c r="D52">
+        <v>1094.976856855998</v>
+      </c>
+      <c r="E52">
+        <v>1312.7</v>
+      </c>
+      <c r="F52">
+        <v>1587.1</v>
+      </c>
+      <c r="G52">
+        <v>57.9</v>
+      </c>
+      <c r="H52">
+        <v>2899.8</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>208</v>
+      </c>
+      <c r="K52">
+        <v>131.5</v>
+      </c>
+      <c r="L52">
+        <v>76.5</v>
+      </c>
+      <c r="M52">
+        <v>378.9994800000001</v>
+      </c>
+      <c r="N52">
+        <v>-302.4994800000001</v>
+      </c>
+      <c r="O52">
+        <v>-72.59987520000001</v>
+      </c>
+      <c r="P52">
+        <v>-229.8996048</v>
+      </c>
+      <c r="Q52">
+        <v>-98.39960480000005</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1377726254455695</v>
+      </c>
+      <c r="T52">
+        <v>1.498686455663902</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.0484433382336039</v>
+      </c>
+      <c r="W52">
+        <v>0.2272317308298154</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.2018472426400163</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1845021781376924</v>
+      </c>
+      <c r="C53">
+        <v>-480.9954861471276</v>
+      </c>
+      <c r="D53">
+        <v>1079.946513852872</v>
+      </c>
+      <c r="E53">
+        <v>1344.442</v>
+      </c>
+      <c r="F53">
+        <v>1618.842</v>
+      </c>
+      <c r="G53">
+        <v>57.9</v>
+      </c>
+      <c r="H53">
+        <v>2899.8</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>208</v>
+      </c>
+      <c r="K53">
+        <v>131.5</v>
+      </c>
+      <c r="L53">
+        <v>76.5</v>
+      </c>
+      <c r="M53">
+        <v>386.5794696</v>
+      </c>
+      <c r="N53">
+        <v>-310.0794696</v>
+      </c>
+      <c r="O53">
+        <v>-74.419072704</v>
+      </c>
+      <c r="P53">
+        <v>-235.660396896</v>
+      </c>
+      <c r="Q53">
+        <v>-104.160396896</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1397924749444587</v>
+      </c>
+      <c r="T53">
+        <v>1.529271893534594</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.04749346885647442</v>
+      </c>
+      <c r="W53">
+        <v>0.2274585596370739</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.1978894535686434</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1865021781376925</v>
+      </c>
+      <c r="C54">
+        <v>-527.3607845638394</v>
+      </c>
+      <c r="D54">
+        <v>1065.323215436161</v>
+      </c>
+      <c r="E54">
+        <v>1376.184</v>
+      </c>
+      <c r="F54">
+        <v>1650.584</v>
+      </c>
+      <c r="G54">
+        <v>57.9</v>
+      </c>
+      <c r="H54">
+        <v>2899.8</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>208</v>
+      </c>
+      <c r="K54">
+        <v>131.5</v>
+      </c>
+      <c r="L54">
+        <v>76.5</v>
+      </c>
+      <c r="M54">
+        <v>394.1594592000001</v>
+      </c>
+      <c r="N54">
+        <v>-317.6594592000001</v>
+      </c>
+      <c r="O54">
+        <v>-76.23827020800002</v>
+      </c>
+      <c r="P54">
+        <v>-241.4211889920001</v>
+      </c>
+      <c r="Q54">
+        <v>-109.9211889920001</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1418964848391349</v>
+      </c>
+      <c r="T54">
+        <v>1.561131724649899</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.04658013291692682</v>
+      </c>
+      <c r="W54">
+        <v>0.2276766642594379</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.1940838871538618</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1885021781376925</v>
+      </c>
+      <c r="C55">
+        <v>-573.3353525690463</v>
+      </c>
+      <c r="D55">
+        <v>1051.090647430954</v>
+      </c>
+      <c r="E55">
+        <v>1407.926</v>
+      </c>
+      <c r="F55">
+        <v>1682.326</v>
+      </c>
+      <c r="G55">
+        <v>57.9</v>
+      </c>
+      <c r="H55">
+        <v>2899.8</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>208</v>
+      </c>
+      <c r="K55">
+        <v>131.5</v>
+      </c>
+      <c r="L55">
+        <v>76.5</v>
+      </c>
+      <c r="M55">
+        <v>401.7394488000001</v>
+      </c>
+      <c r="N55">
+        <v>-325.2394488000001</v>
+      </c>
+      <c r="O55">
+        <v>-78.05746771200002</v>
+      </c>
+      <c r="P55">
+        <v>-247.1819810880001</v>
+      </c>
+      <c r="Q55">
+        <v>-115.6819810880001</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1440900270697548</v>
+      </c>
+      <c r="T55">
+        <v>1.594347293259471</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.04570126248453198</v>
+      </c>
+      <c r="W55">
+        <v>0.2278865385186938</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.1904219270188833</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1905021781376925</v>
+      </c>
+      <c r="C56">
+        <v>-618.9346440111892</v>
+      </c>
+      <c r="D56">
+        <v>1037.233355988811</v>
+      </c>
+      <c r="E56">
+        <v>1439.668</v>
+      </c>
+      <c r="F56">
+        <v>1714.068</v>
+      </c>
+      <c r="G56">
+        <v>57.9</v>
+      </c>
+      <c r="H56">
+        <v>2899.8</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>208</v>
+      </c>
+      <c r="K56">
+        <v>131.5</v>
+      </c>
+      <c r="L56">
+        <v>76.5</v>
+      </c>
+      <c r="M56">
+        <v>409.3194384000001</v>
+      </c>
+      <c r="N56">
+        <v>-332.8194384000001</v>
+      </c>
+      <c r="O56">
+        <v>-79.87666521600002</v>
+      </c>
+      <c r="P56">
+        <v>-252.9427731840001</v>
+      </c>
+      <c r="Q56">
+        <v>-121.4427731840001</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.146378940701706</v>
+      </c>
+      <c r="T56">
+        <v>1.629007017025981</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.0448549428088925</v>
+      </c>
+      <c r="W56">
+        <v>0.2280886396572365</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.1868955950370521</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1925021781376924</v>
+      </c>
+      <c r="C57">
+        <v>-664.1733083858428</v>
+      </c>
+      <c r="D57">
+        <v>1023.736691614158</v>
+      </c>
+      <c r="E57">
+        <v>1471.41</v>
+      </c>
+      <c r="F57">
+        <v>1745.81</v>
+      </c>
+      <c r="G57">
+        <v>57.9</v>
+      </c>
+      <c r="H57">
+        <v>2899.8</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>208</v>
+      </c>
+      <c r="K57">
+        <v>131.5</v>
+      </c>
+      <c r="L57">
+        <v>76.5</v>
+      </c>
+      <c r="M57">
+        <v>416.8994280000001</v>
+      </c>
+      <c r="N57">
+        <v>-340.3994280000001</v>
+      </c>
+      <c r="O57">
+        <v>-81.69586272000002</v>
+      </c>
+      <c r="P57">
+        <v>-258.7035652800001</v>
+      </c>
+      <c r="Q57">
+        <v>-127.2035652800001</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1487695838284105</v>
+      </c>
+      <c r="T57">
+        <v>1.665207172959892</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.04403939839418536</v>
+      </c>
+      <c r="W57">
+        <v>0.2282833916634686</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.1834974933091057</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1945021781376924</v>
+      </c>
+      <c r="C58">
+        <v>-709.0652424954201</v>
+      </c>
+      <c r="D58">
+        <v>1010.58675750458</v>
+      </c>
+      <c r="E58">
+        <v>1503.152</v>
+      </c>
+      <c r="F58">
+        <v>1777.552</v>
+      </c>
+      <c r="G58">
+        <v>57.9</v>
+      </c>
+      <c r="H58">
+        <v>2899.8</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>208</v>
+      </c>
+      <c r="K58">
+        <v>131.5</v>
+      </c>
+      <c r="L58">
+        <v>76.5</v>
+      </c>
+      <c r="M58">
+        <v>424.4794176000001</v>
+      </c>
+      <c r="N58">
+        <v>-347.9794176000001</v>
+      </c>
+      <c r="O58">
+        <v>-83.51506022400002</v>
+      </c>
+      <c r="P58">
+        <v>-264.4643573760001</v>
+      </c>
+      <c r="Q58">
+        <v>-132.9643573760001</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1512688925517835</v>
+      </c>
+      <c r="T58">
+        <v>1.703052790527162</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.04325298056571777</v>
+      </c>
+      <c r="W58">
+        <v>0.2284711882409066</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.1802207523571574</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1965021781376924</v>
+      </c>
+      <c r="C59">
+        <v>-753.6236381779481</v>
+      </c>
+      <c r="D59">
+        <v>997.7703618220522</v>
+      </c>
+      <c r="E59">
+        <v>1534.894</v>
+      </c>
+      <c r="F59">
+        <v>1809.294</v>
+      </c>
+      <c r="G59">
+        <v>57.9</v>
+      </c>
+      <c r="H59">
+        <v>2899.8</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>208</v>
+      </c>
+      <c r="K59">
+        <v>131.5</v>
+      </c>
+      <c r="L59">
+        <v>76.5</v>
+      </c>
+      <c r="M59">
+        <v>432.0594072000001</v>
+      </c>
+      <c r="N59">
+        <v>-355.5594072000001</v>
+      </c>
+      <c r="O59">
+        <v>-85.33425772800003</v>
+      </c>
+      <c r="P59">
+        <v>-270.2251494720001</v>
+      </c>
+      <c r="Q59">
+        <v>-138.7251494720001</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1538844481925227</v>
+      </c>
+      <c r="T59">
+        <v>1.742658669376631</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.04249415634526658</v>
+      </c>
+      <c r="W59">
+        <v>0.2286523954647504</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.177058984771944</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1985021781376924</v>
+      </c>
+      <c r="C60">
+        <v>-797.8610264495064</v>
+      </c>
+      <c r="D60">
+        <v>985.2749735504937</v>
+      </c>
+      <c r="E60">
+        <v>1566.636</v>
+      </c>
+      <c r="F60">
+        <v>1841.036</v>
+      </c>
+      <c r="G60">
+        <v>57.9</v>
+      </c>
+      <c r="H60">
+        <v>2899.8</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>208</v>
+      </c>
+      <c r="K60">
+        <v>131.5</v>
+      </c>
+      <c r="L60">
+        <v>76.5</v>
+      </c>
+      <c r="M60">
+        <v>439.6393968</v>
+      </c>
+      <c r="N60">
+        <v>-363.1393968</v>
+      </c>
+      <c r="O60">
+        <v>-87.15345523200001</v>
+      </c>
+      <c r="P60">
+        <v>-275.985941568</v>
+      </c>
+      <c r="Q60">
+        <v>-144.485941568</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1566245541018684</v>
+      </c>
+      <c r="T60">
+        <v>1.784150542457026</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.04176149847724474</v>
+      </c>
+      <c r="W60">
+        <v>0.228827354163634</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.1740062436551865</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2005021781376924</v>
+      </c>
+      <c r="C61">
+        <v>-841.7893183708375</v>
+      </c>
+      <c r="D61">
+        <v>973.0886816291625</v>
+      </c>
+      <c r="E61">
+        <v>1598.378</v>
+      </c>
+      <c r="F61">
+        <v>1872.778</v>
+      </c>
+      <c r="G61">
+        <v>57.9</v>
+      </c>
+      <c r="H61">
+        <v>2899.8</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>208</v>
+      </c>
+      <c r="K61">
+        <v>131.5</v>
+      </c>
+      <c r="L61">
+        <v>76.5</v>
+      </c>
+      <c r="M61">
+        <v>447.2193864</v>
+      </c>
+      <c r="N61">
+        <v>-370.7193864</v>
+      </c>
+      <c r="O61">
+        <v>-88.972652736</v>
+      </c>
+      <c r="P61">
+        <v>-281.746733664</v>
+      </c>
+      <c r="Q61">
+        <v>-150.246733664</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1594983237141091</v>
+      </c>
+      <c r="T61">
+        <v>1.827666409346222</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.04105367646915585</v>
+      </c>
+      <c r="W61">
+        <v>0.2289963820591656</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.1710569852881494</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2025021781376924</v>
+      </c>
+      <c r="C62">
+        <v>-885.4198429182711</v>
+      </c>
+      <c r="D62">
+        <v>961.2001570817289</v>
+      </c>
+      <c r="E62">
+        <v>1630.12</v>
+      </c>
+      <c r="F62">
+        <v>1904.52</v>
+      </c>
+      <c r="G62">
+        <v>57.9</v>
+      </c>
+      <c r="H62">
+        <v>2899.8</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>208</v>
+      </c>
+      <c r="K62">
+        <v>131.5</v>
+      </c>
+      <c r="L62">
+        <v>76.5</v>
+      </c>
+      <c r="M62">
+        <v>454.799376</v>
+      </c>
+      <c r="N62">
+        <v>-378.299376</v>
+      </c>
+      <c r="O62">
+        <v>-90.79185024</v>
+      </c>
+      <c r="P62">
+        <v>-287.50752576</v>
+      </c>
+      <c r="Q62">
+        <v>-156.00752576</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1625157818069618</v>
+      </c>
+      <c r="T62">
+        <v>1.873358069579877</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.04036944852800325</v>
+      </c>
+      <c r="W62">
+        <v>0.2291597756915128</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.1682060355333469</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2045021781376924</v>
+      </c>
+      <c r="C63">
+        <v>-928.7633821120772</v>
+      </c>
+      <c r="D63">
+        <v>949.598617887923</v>
+      </c>
+      <c r="E63">
+        <v>1661.862</v>
+      </c>
+      <c r="F63">
+        <v>1936.262</v>
+      </c>
+      <c r="G63">
+        <v>57.9</v>
+      </c>
+      <c r="H63">
+        <v>2899.8</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>208</v>
+      </c>
+      <c r="K63">
+        <v>131.5</v>
+      </c>
+      <c r="L63">
+        <v>76.5</v>
+      </c>
+      <c r="M63">
+        <v>462.3793656000001</v>
+      </c>
+      <c r="N63">
+        <v>-385.8793656000001</v>
+      </c>
+      <c r="O63">
+        <v>-92.61104774400002</v>
+      </c>
+      <c r="P63">
+        <v>-293.2683178560001</v>
+      </c>
+      <c r="Q63">
+        <v>-161.7683178560001</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1656879813404737</v>
+      </c>
+      <c r="T63">
+        <v>1.921392891876798</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.03970765428983927</v>
+      </c>
+      <c r="W63">
+        <v>0.2293178121555864</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.1654485595409969</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2065021781376924</v>
+      </c>
+      <c r="C64">
+        <v>-971.8302036311901</v>
+      </c>
+      <c r="D64">
+        <v>938.2737963688101</v>
+      </c>
+      <c r="E64">
+        <v>1693.604</v>
+      </c>
+      <c r="F64">
+        <v>1968.004</v>
+      </c>
+      <c r="G64">
+        <v>57.9</v>
+      </c>
+      <c r="H64">
+        <v>2899.8</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>208</v>
+      </c>
+      <c r="K64">
+        <v>131.5</v>
+      </c>
+      <c r="L64">
+        <v>76.5</v>
+      </c>
+      <c r="M64">
+        <v>469.9593552000001</v>
+      </c>
+      <c r="N64">
+        <v>-393.4593552000001</v>
+      </c>
+      <c r="O64">
+        <v>-94.43024524800001</v>
+      </c>
+      <c r="P64">
+        <v>-299.0291099520001</v>
+      </c>
+      <c r="Q64">
+        <v>-167.5291099520001</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1690271387441704</v>
+      </c>
+      <c r="T64">
+        <v>1.971955862715661</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.03906720825290638</v>
+      </c>
+      <c r="W64">
+        <v>0.229470750669206</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.1627800343871099</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2085021781376924</v>
+      </c>
+      <c r="C65">
+        <v>-1014.63009112168</v>
+      </c>
+      <c r="D65">
+        <v>927.2159088783204</v>
+      </c>
+      <c r="E65">
+        <v>1725.346</v>
+      </c>
+      <c r="F65">
+        <v>1999.746</v>
+      </c>
+      <c r="G65">
+        <v>57.9</v>
+      </c>
+      <c r="H65">
+        <v>2899.8</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>208</v>
+      </c>
+      <c r="K65">
+        <v>131.5</v>
+      </c>
+      <c r="L65">
+        <v>76.5</v>
+      </c>
+      <c r="M65">
+        <v>477.5393448</v>
+      </c>
+      <c r="N65">
+        <v>-401.0393448</v>
+      </c>
+      <c r="O65">
+        <v>-96.24944275200001</v>
+      </c>
+      <c r="P65">
+        <v>-304.789902048</v>
+      </c>
+      <c r="Q65">
+        <v>-173.289902048</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1725467911426614</v>
+      </c>
+      <c r="T65">
+        <v>2.025251967113381</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.03844709383619357</v>
+      </c>
+      <c r="W65">
+        <v>0.229618833991917</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.1601962243174733</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2105021781376925</v>
+      </c>
+      <c r="C66">
+        <v>-1057.172372387009</v>
+      </c>
+      <c r="D66">
+        <v>916.4156276129917</v>
+      </c>
+      <c r="E66">
+        <v>1757.088</v>
+      </c>
+      <c r="F66">
+        <v>2031.488</v>
+      </c>
+      <c r="G66">
+        <v>57.9</v>
+      </c>
+      <c r="H66">
+        <v>2899.8</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>208</v>
+      </c>
+      <c r="K66">
+        <v>131.5</v>
+      </c>
+      <c r="L66">
+        <v>76.5</v>
+      </c>
+      <c r="M66">
+        <v>485.1193344000001</v>
+      </c>
+      <c r="N66">
+        <v>-408.6193344000001</v>
+      </c>
+      <c r="O66">
+        <v>-98.06864025600001</v>
+      </c>
+      <c r="P66">
+        <v>-310.5506941440001</v>
+      </c>
+      <c r="Q66">
+        <v>-179.0506941440001</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1762619797855132</v>
+      </c>
+      <c r="T66">
+        <v>2.081508966199864</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.03784635799500305</v>
+      </c>
+      <c r="W66">
+        <v>0.2297622897107933</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.1576931583125127</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2125021781376925</v>
+      </c>
+      <c r="C67">
+        <v>-1099.4659456308</v>
+      </c>
+      <c r="D67">
+        <v>905.8640543692003</v>
+      </c>
+      <c r="E67">
+        <v>1788.83</v>
+      </c>
+      <c r="F67">
+        <v>2063.23</v>
+      </c>
+      <c r="G67">
+        <v>57.9</v>
+      </c>
+      <c r="H67">
+        <v>2899.8</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>208</v>
+      </c>
+      <c r="K67">
+        <v>131.5</v>
+      </c>
+      <c r="L67">
+        <v>76.5</v>
+      </c>
+      <c r="M67">
+        <v>492.6993240000002</v>
+      </c>
+      <c r="N67">
+        <v>-416.1993240000002</v>
+      </c>
+      <c r="O67">
+        <v>-99.88783776000004</v>
+      </c>
+      <c r="P67">
+        <v>-316.3114862400001</v>
+      </c>
+      <c r="Q67">
+        <v>-184.8114862400001</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1801894649222422</v>
+      </c>
+      <c r="T67">
+        <v>2.140980650948432</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.03726410633354146</v>
+      </c>
+      <c r="W67">
+        <v>0.2299013314075503</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.1552671097230894</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2145021781376925</v>
+      </c>
+      <c r="C68">
+        <v>-1141.519303907296</v>
+      </c>
+      <c r="D68">
+        <v>895.5526960927047</v>
+      </c>
+      <c r="E68">
+        <v>1820.572</v>
+      </c>
+      <c r="F68">
+        <v>2094.972</v>
+      </c>
+      <c r="G68">
+        <v>57.9</v>
+      </c>
+      <c r="H68">
+        <v>2899.8</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>208</v>
+      </c>
+      <c r="K68">
+        <v>131.5</v>
+      </c>
+      <c r="L68">
+        <v>76.5</v>
+      </c>
+      <c r="M68">
+        <v>500.2793136000001</v>
+      </c>
+      <c r="N68">
+        <v>-423.7793136000001</v>
+      </c>
+      <c r="O68">
+        <v>-101.707035264</v>
+      </c>
+      <c r="P68">
+        <v>-322.0722783360001</v>
+      </c>
+      <c r="Q68">
+        <v>-190.5722783360001</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1843479785964257</v>
+      </c>
+      <c r="T68">
+        <v>2.203950670093974</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.03669949866182114</v>
+      </c>
+      <c r="W68">
+        <v>0.2300361597195571</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.1529145777575881</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2165021781376925</v>
+      </c>
+      <c r="C69">
+        <v>-1183.340557920702</v>
+      </c>
+      <c r="D69">
+        <v>885.473442079298</v>
+      </c>
+      <c r="E69">
+        <v>1852.314</v>
+      </c>
+      <c r="F69">
+        <v>2126.714</v>
+      </c>
+      <c r="G69">
+        <v>57.9</v>
+      </c>
+      <c r="H69">
+        <v>2899.8</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>208</v>
+      </c>
+      <c r="K69">
+        <v>131.5</v>
+      </c>
+      <c r="L69">
+        <v>76.5</v>
+      </c>
+      <c r="M69">
+        <v>507.8593032000001</v>
+      </c>
+      <c r="N69">
+        <v>-431.3593032000001</v>
+      </c>
+      <c r="O69">
+        <v>-103.526232768</v>
+      </c>
+      <c r="P69">
+        <v>-327.8330704320001</v>
+      </c>
+      <c r="Q69">
+        <v>-196.3330704320001</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.188758523402378</v>
+      </c>
+      <c r="T69">
+        <v>2.270737054036216</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.03615174495045067</v>
+      </c>
+      <c r="W69">
+        <v>0.2301669633058324</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.1506322706268778</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2185021781376925</v>
+      </c>
+      <c r="C70">
+        <v>-1224.937457302064</v>
+      </c>
+      <c r="D70">
+        <v>875.618542697936</v>
+      </c>
+      <c r="E70">
+        <v>1884.056</v>
+      </c>
+      <c r="F70">
+        <v>2158.456</v>
+      </c>
+      <c r="G70">
+        <v>57.9</v>
+      </c>
+      <c r="H70">
+        <v>2899.8</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>208</v>
+      </c>
+      <c r="K70">
+        <v>131.5</v>
+      </c>
+      <c r="L70">
+        <v>76.5</v>
+      </c>
+      <c r="M70">
+        <v>515.4392928000001</v>
+      </c>
+      <c r="N70">
+        <v>-438.9392928000001</v>
+      </c>
+      <c r="O70">
+        <v>-105.345430272</v>
+      </c>
+      <c r="P70">
+        <v>-333.593862528</v>
+      </c>
+      <c r="Q70">
+        <v>-202.093862528</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1934447272587023</v>
+      </c>
+      <c r="T70">
+        <v>2.341697586974848</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.0356201016423558</v>
+      </c>
+      <c r="W70">
+        <v>0.2302939197278054</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.1484170901764825</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2205021781376924</v>
+      </c>
+      <c r="C71">
+        <v>-1266.317410480968</v>
+      </c>
+      <c r="D71">
+        <v>865.9805895190323</v>
+      </c>
+      <c r="E71">
+        <v>1915.798</v>
+      </c>
+      <c r="F71">
+        <v>2190.198</v>
+      </c>
+      <c r="G71">
+        <v>57.9</v>
+      </c>
+      <c r="H71">
+        <v>2899.8</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>208</v>
+      </c>
+      <c r="K71">
+        <v>131.5</v>
+      </c>
+      <c r="L71">
+        <v>76.5</v>
+      </c>
+      <c r="M71">
+        <v>523.0192824000001</v>
+      </c>
+      <c r="N71">
+        <v>-446.5192824000001</v>
+      </c>
+      <c r="O71">
+        <v>-107.164627776</v>
+      </c>
+      <c r="P71">
+        <v>-339.354654624</v>
+      </c>
+      <c r="Q71">
+        <v>-207.854654624</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.1984332668476927</v>
+      </c>
+      <c r="T71">
+        <v>2.417236218812746</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.03510386828522022</v>
+      </c>
+      <c r="W71">
+        <v>0.2304171962534894</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.1462661178550843</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2225021781376924</v>
+      </c>
+      <c r="C72">
+        <v>-1307.48750325916</v>
+      </c>
+      <c r="D72">
+        <v>856.5524967408406</v>
+      </c>
+      <c r="E72">
+        <v>1947.54</v>
+      </c>
+      <c r="F72">
+        <v>2221.940000000001</v>
+      </c>
+      <c r="G72">
+        <v>57.9</v>
+      </c>
+      <c r="H72">
+        <v>2899.8</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>208</v>
+      </c>
+      <c r="K72">
+        <v>131.5</v>
+      </c>
+      <c r="L72">
+        <v>76.5</v>
+      </c>
+      <c r="M72">
+        <v>530.5992720000002</v>
+      </c>
+      <c r="N72">
+        <v>-454.0992720000002</v>
+      </c>
+      <c r="O72">
+        <v>-108.98382528</v>
+      </c>
+      <c r="P72">
+        <v>-345.1154467200001</v>
+      </c>
+      <c r="Q72">
+        <v>-213.6154467200001</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2037543757426158</v>
+      </c>
+      <c r="T72">
+        <v>2.497810759439838</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.03460238445257421</v>
+      </c>
+      <c r="W72">
+        <v>0.2305369505927253</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.1441766018857259</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2245021781376924</v>
+      </c>
+      <c r="C73">
+        <v>-1348.454516183948</v>
+      </c>
+      <c r="D73">
+        <v>847.3274838160518</v>
+      </c>
+      <c r="E73">
+        <v>1979.282</v>
+      </c>
+      <c r="F73">
+        <v>2253.682</v>
+      </c>
+      <c r="G73">
+        <v>57.9</v>
+      </c>
+      <c r="H73">
+        <v>2899.8</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>208</v>
+      </c>
+      <c r="K73">
+        <v>131.5</v>
+      </c>
+      <c r="L73">
+        <v>76.5</v>
+      </c>
+      <c r="M73">
+        <v>538.1792616000001</v>
+      </c>
+      <c r="N73">
+        <v>-461.6792616000001</v>
+      </c>
+      <c r="O73">
+        <v>-110.803022784</v>
+      </c>
+      <c r="P73">
+        <v>-350.8762388160001</v>
+      </c>
+      <c r="Q73">
+        <v>-219.3762388160001</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.209442457664775</v>
+      </c>
+      <c r="T73">
+        <v>2.583942164937763</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.03411502692507316</v>
+      </c>
+      <c r="W73">
+        <v>0.2306533315702925</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.1421459455211382</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2265021781376924</v>
+      </c>
+      <c r="C74">
+        <v>-1389.224940810907</v>
+      </c>
+      <c r="D74">
+        <v>838.2990591890932</v>
+      </c>
+      <c r="E74">
+        <v>2011.024</v>
+      </c>
+      <c r="F74">
+        <v>2285.424</v>
+      </c>
+      <c r="G74">
+        <v>57.9</v>
+      </c>
+      <c r="H74">
+        <v>2899.8</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>208</v>
+      </c>
+      <c r="K74">
+        <v>131.5</v>
+      </c>
+      <c r="L74">
+        <v>76.5</v>
+      </c>
+      <c r="M74">
+        <v>545.7592512</v>
+      </c>
+      <c r="N74">
+        <v>-469.2592512</v>
+      </c>
+      <c r="O74">
+        <v>-112.622220288</v>
+      </c>
+      <c r="P74">
+        <v>-356.637030912</v>
+      </c>
+      <c r="Q74">
+        <v>-225.137030912</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2155368311528026</v>
+      </c>
+      <c r="T74">
+        <v>2.676225813685539</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.03364120710666938</v>
+      </c>
+      <c r="W74">
+        <v>0.2307664797429274</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.1401716962777891</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2285021781376924</v>
+      </c>
+      <c r="C75">
+        <v>-1429.804994937841</v>
+      </c>
+      <c r="D75">
+        <v>829.4610050621592</v>
+      </c>
+      <c r="E75">
+        <v>2042.766</v>
+      </c>
+      <c r="F75">
+        <v>2317.166</v>
+      </c>
+      <c r="G75">
+        <v>57.9</v>
+      </c>
+      <c r="H75">
+        <v>2899.8</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>208</v>
+      </c>
+      <c r="K75">
+        <v>131.5</v>
+      </c>
+      <c r="L75">
+        <v>76.5</v>
+      </c>
+      <c r="M75">
+        <v>553.3392408000001</v>
+      </c>
+      <c r="N75">
+        <v>-476.8392408000001</v>
+      </c>
+      <c r="O75">
+        <v>-114.441417792</v>
+      </c>
+      <c r="P75">
+        <v>-362.397823008</v>
+      </c>
+      <c r="Q75">
+        <v>-230.897823008</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2220826397140175</v>
+      </c>
+      <c r="T75">
+        <v>2.775345288266486</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.03318036865315336</v>
+      </c>
+      <c r="W75">
+        <v>0.230876527965627</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.1382515360548057</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2305021781376924</v>
+      </c>
+      <c r="C76">
+        <v>-1470.200636885158</v>
+      </c>
+      <c r="D76">
+        <v>820.8073631148425</v>
+      </c>
+      <c r="E76">
+        <v>2074.508</v>
+      </c>
+      <c r="F76">
+        <v>2348.908</v>
+      </c>
+      <c r="G76">
+        <v>57.9</v>
+      </c>
+      <c r="H76">
+        <v>2899.8</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>208</v>
+      </c>
+      <c r="K76">
+        <v>131.5</v>
+      </c>
+      <c r="L76">
+        <v>76.5</v>
+      </c>
+      <c r="M76">
+        <v>560.9192304000001</v>
+      </c>
+      <c r="N76">
+        <v>-484.4192304000001</v>
+      </c>
+      <c r="O76">
+        <v>-116.260615296</v>
+      </c>
+      <c r="P76">
+        <v>-368.158615104</v>
+      </c>
+      <c r="Q76">
+        <v>-236.658615104</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2291319720107105</v>
+      </c>
+      <c r="T76">
+        <v>2.882089337815196</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.03273198529297561</v>
+      </c>
+      <c r="W76">
+        <v>0.2309836019120374</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.1363832720540651</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2325021781376924</v>
+      </c>
+      <c r="C77">
+        <v>-1510.417578891554</v>
+      </c>
+      <c r="D77">
+        <v>812.3324211084458</v>
+      </c>
+      <c r="E77">
+        <v>2106.25</v>
+      </c>
+      <c r="F77">
+        <v>2380.65</v>
+      </c>
+      <c r="G77">
+        <v>57.9</v>
+      </c>
+      <c r="H77">
+        <v>2899.8</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>208</v>
+      </c>
+      <c r="K77">
+        <v>131.5</v>
+      </c>
+      <c r="L77">
+        <v>76.5</v>
+      </c>
+      <c r="M77">
+        <v>568.49922</v>
+      </c>
+      <c r="N77">
+        <v>-491.99922</v>
+      </c>
+      <c r="O77">
+        <v>-118.0798128</v>
+      </c>
+      <c r="P77">
+        <v>-373.9194072</v>
+      </c>
+      <c r="Q77">
+        <v>-242.4194072</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.236745250891139</v>
+      </c>
+      <c r="T77">
+        <v>2.997372911327805</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.03229555882240261</v>
+      </c>
+      <c r="W77">
+        <v>0.2310878205532103</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.1345648284266775</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2345021781376925</v>
+      </c>
+      <c r="C78">
+        <v>-1550.461299688315</v>
+      </c>
+      <c r="D78">
+        <v>804.0307003116856</v>
+      </c>
+      <c r="E78">
+        <v>2137.992</v>
+      </c>
+      <c r="F78">
+        <v>2412.392</v>
+      </c>
+      <c r="G78">
+        <v>57.9</v>
+      </c>
+      <c r="H78">
+        <v>2899.8</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>208</v>
+      </c>
+      <c r="K78">
+        <v>131.5</v>
+      </c>
+      <c r="L78">
+        <v>76.5</v>
+      </c>
+      <c r="M78">
+        <v>576.0792096000001</v>
+      </c>
+      <c r="N78">
+        <v>-499.5792096000001</v>
+      </c>
+      <c r="O78">
+        <v>-119.899010304</v>
+      </c>
+      <c r="P78">
+        <v>-379.6801992960001</v>
+      </c>
+      <c r="Q78">
+        <v>-248.1801992960001</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2449929696782698</v>
+      </c>
+      <c r="T78">
+        <v>3.122263449299797</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.03187061725894993</v>
+      </c>
+      <c r="W78">
+        <v>0.2311892965985628</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.132794238578958</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2365021781376924</v>
+      </c>
+      <c r="C79">
+        <v>-1590.337056310376</v>
+      </c>
+      <c r="D79">
+        <v>795.8969436896247</v>
+      </c>
+      <c r="E79">
+        <v>2169.734</v>
+      </c>
+      <c r="F79">
+        <v>2444.134</v>
+      </c>
+      <c r="G79">
+        <v>57.9</v>
+      </c>
+      <c r="H79">
+        <v>2899.8</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>208</v>
+      </c>
+      <c r="K79">
+        <v>131.5</v>
+      </c>
+      <c r="L79">
+        <v>76.5</v>
+      </c>
+      <c r="M79">
+        <v>583.6591992000001</v>
+      </c>
+      <c r="N79">
+        <v>-507.1591992000001</v>
+      </c>
+      <c r="O79">
+        <v>-121.718207808</v>
+      </c>
+      <c r="P79">
+        <v>-385.4409913920001</v>
+      </c>
+      <c r="Q79">
+        <v>-253.9409913920001</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2539578814034119</v>
+      </c>
+      <c r="T79">
+        <v>3.258014034051962</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.03145671313870383</v>
+      </c>
+      <c r="W79">
+        <v>0.2312881369024775</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.1310696380779326</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2385021781376924</v>
+      </c>
+      <c r="C80">
+        <v>-1630.04989519768</v>
+      </c>
+      <c r="D80">
+        <v>787.9261048023207</v>
+      </c>
+      <c r="E80">
+        <v>2201.476</v>
+      </c>
+      <c r="F80">
+        <v>2475.876</v>
+      </c>
+      <c r="G80">
+        <v>57.9</v>
+      </c>
+      <c r="H80">
+        <v>2899.8</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>208</v>
+      </c>
+      <c r="K80">
+        <v>131.5</v>
+      </c>
+      <c r="L80">
+        <v>76.5</v>
+      </c>
+      <c r="M80">
+        <v>591.2391888000001</v>
+      </c>
+      <c r="N80">
+        <v>-514.7391888000001</v>
+      </c>
+      <c r="O80">
+        <v>-123.537405312</v>
+      </c>
+      <c r="P80">
+        <v>-391.201783488</v>
+      </c>
+      <c r="Q80">
+        <v>-259.701783488</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.263737785103567</v>
+      </c>
+      <c r="T80">
+        <v>3.406105581054323</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.03105342194461789</v>
+      </c>
+      <c r="W80">
+        <v>0.2313844428396253</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.1293892581025745</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2405021781376925</v>
+      </c>
+      <c r="C81">
+        <v>-1669.604662636061</v>
+      </c>
+      <c r="D81">
+        <v>780.1133373639398</v>
+      </c>
+      <c r="E81">
+        <v>2233.218</v>
+      </c>
+      <c r="F81">
+        <v>2507.618</v>
+      </c>
+      <c r="G81">
+        <v>57.9</v>
+      </c>
+      <c r="H81">
+        <v>2899.8</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>208</v>
+      </c>
+      <c r="K81">
+        <v>131.5</v>
+      </c>
+      <c r="L81">
+        <v>76.5</v>
+      </c>
+      <c r="M81">
+        <v>598.8191784000002</v>
+      </c>
+      <c r="N81">
+        <v>-522.3191784000002</v>
+      </c>
+      <c r="O81">
+        <v>-125.356602816</v>
+      </c>
+      <c r="P81">
+        <v>-396.9625755840001</v>
+      </c>
+      <c r="Q81">
+        <v>-265.4625755840001</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2744491082037369</v>
+      </c>
+      <c r="T81">
+        <v>3.568301084914054</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.03066034065417968</v>
+      </c>
+      <c r="W81">
+        <v>0.2314783106517819</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.1277514193924153</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2425021781376925</v>
+      </c>
+      <c r="C82">
+        <v>-1709.006014583065</v>
+      </c>
+      <c r="D82">
+        <v>772.4539854169358</v>
+      </c>
+      <c r="E82">
+        <v>2264.96</v>
+      </c>
+      <c r="F82">
+        <v>2539.360000000001</v>
+      </c>
+      <c r="G82">
+        <v>57.9</v>
+      </c>
+      <c r="H82">
+        <v>2899.8</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>208</v>
+      </c>
+      <c r="K82">
+        <v>131.5</v>
+      </c>
+      <c r="L82">
+        <v>76.5</v>
+      </c>
+      <c r="M82">
+        <v>606.3991680000001</v>
+      </c>
+      <c r="N82">
+        <v>-529.8991680000001</v>
+      </c>
+      <c r="O82">
+        <v>-127.17580032</v>
+      </c>
+      <c r="P82">
+        <v>-402.7233676800001</v>
+      </c>
+      <c r="Q82">
+        <v>-271.2233676800001</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.2862315636139238</v>
+      </c>
+      <c r="T82">
+        <v>3.746716139159756</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.03027708639600243</v>
+      </c>
+      <c r="W82">
+        <v>0.2315698317686346</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.1261545266500101</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2445021781376924</v>
+      </c>
+      <c r="C83">
+        <v>-1748.258425920565</v>
+      </c>
+      <c r="D83">
+        <v>764.9435740794353</v>
+      </c>
+      <c r="E83">
+        <v>2296.702</v>
+      </c>
+      <c r="F83">
+        <v>2571.102</v>
+      </c>
+      <c r="G83">
+        <v>57.9</v>
+      </c>
+      <c r="H83">
+        <v>2899.8</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>208</v>
+      </c>
+      <c r="K83">
+        <v>131.5</v>
+      </c>
+      <c r="L83">
+        <v>76.5</v>
+      </c>
+      <c r="M83">
+        <v>613.9791576000001</v>
+      </c>
+      <c r="N83">
+        <v>-537.4791576000001</v>
+      </c>
+      <c r="O83">
+        <v>-128.994997824</v>
+      </c>
+      <c r="P83">
+        <v>-408.4841597760001</v>
+      </c>
+      <c r="Q83">
+        <v>-276.9841597760001</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.2992542774883408</v>
+      </c>
+      <c r="T83">
+        <v>3.943911725431323</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.02990329520592833</v>
+      </c>
+      <c r="W83">
+        <v>0.2316590931048243</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.1245970633580347</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2465021781376925</v>
+      </c>
+      <c r="C84">
+        <v>-1787.366199172807</v>
+      </c>
+      <c r="D84">
+        <v>757.5778008271939</v>
+      </c>
+      <c r="E84">
+        <v>2328.444</v>
+      </c>
+      <c r="F84">
+        <v>2602.844000000001</v>
+      </c>
+      <c r="G84">
+        <v>57.9</v>
+      </c>
+      <c r="H84">
+        <v>2899.8</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>208</v>
+      </c>
+      <c r="K84">
+        <v>131.5</v>
+      </c>
+      <c r="L84">
+        <v>76.5</v>
+      </c>
+      <c r="M84">
+        <v>621.5591472000001</v>
+      </c>
+      <c r="N84">
+        <v>-545.0591472000001</v>
+      </c>
+      <c r="O84">
+        <v>-130.814195328</v>
+      </c>
+      <c r="P84">
+        <v>-414.2449518720001</v>
+      </c>
+      <c r="Q84">
+        <v>-282.7449518720001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.3137239595710264</v>
+      </c>
+      <c r="T84">
+        <v>4.16301793239973</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.02953862087414872</v>
+      </c>
+      <c r="W84">
+        <v>0.2317461773352533</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.1230775869756197</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2485021781376925</v>
+      </c>
+      <c r="C85">
+        <v>-1826.333472725566</v>
+      </c>
+      <c r="D85">
+        <v>750.3525272744342</v>
+      </c>
+      <c r="E85">
+        <v>2360.186</v>
+      </c>
+      <c r="F85">
+        <v>2634.586</v>
+      </c>
+      <c r="G85">
+        <v>57.9</v>
+      </c>
+      <c r="H85">
+        <v>2899.8</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>208</v>
+      </c>
+      <c r="K85">
+        <v>131.5</v>
+      </c>
+      <c r="L85">
+        <v>76.5</v>
+      </c>
+      <c r="M85">
+        <v>629.1391368000001</v>
+      </c>
+      <c r="N85">
+        <v>-552.6391368000001</v>
+      </c>
+      <c r="O85">
+        <v>-132.633392832</v>
+      </c>
+      <c r="P85">
+        <v>-420.005743968</v>
+      </c>
+      <c r="Q85">
+        <v>-288.505743968</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.3298959571928515</v>
+      </c>
+      <c r="T85">
+        <v>4.40790134018795</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.029182733875665</v>
+      </c>
+      <c r="W85">
+        <v>0.2318311631504912</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.1215947244819375</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2505021781376925</v>
+      </c>
+      <c r="C86">
+        <v>-1865.164228579428</v>
+      </c>
+      <c r="D86">
+        <v>743.2637714205724</v>
+      </c>
+      <c r="E86">
+        <v>2391.928</v>
+      </c>
+      <c r="F86">
+        <v>2666.328</v>
+      </c>
+      <c r="G86">
+        <v>57.9</v>
+      </c>
+      <c r="H86">
+        <v>2899.8</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>208</v>
+      </c>
+      <c r="K86">
+        <v>131.5</v>
+      </c>
+      <c r="L86">
+        <v>76.5</v>
+      </c>
+      <c r="M86">
+        <v>636.7191264000001</v>
+      </c>
+      <c r="N86">
+        <v>-560.2191264000001</v>
+      </c>
+      <c r="O86">
+        <v>-134.452590336</v>
+      </c>
+      <c r="P86">
+        <v>-425.766536064</v>
+      </c>
+      <c r="Q86">
+        <v>-294.266536064</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.3480894545174046</v>
+      </c>
+      <c r="T86">
+        <v>4.683395173949695</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.02883532037714518</v>
+      </c>
+      <c r="W86">
+        <v>0.2319141254939378</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.1201471682381049</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2525021781376924</v>
+      </c>
+      <c r="C87">
+        <v>-1903.862299667685</v>
+      </c>
+      <c r="D87">
+        <v>736.3077003323154</v>
+      </c>
+      <c r="E87">
+        <v>2423.67</v>
+      </c>
+      <c r="F87">
+        <v>2698.07</v>
+      </c>
+      <c r="G87">
+        <v>57.9</v>
+      </c>
+      <c r="H87">
+        <v>2899.8</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>208</v>
+      </c>
+      <c r="K87">
+        <v>131.5</v>
+      </c>
+      <c r="L87">
+        <v>76.5</v>
+      </c>
+      <c r="M87">
+        <v>644.299116</v>
+      </c>
+      <c r="N87">
+        <v>-567.799116</v>
+      </c>
+      <c r="O87">
+        <v>-136.27178784</v>
+      </c>
+      <c r="P87">
+        <v>-431.52732816</v>
+      </c>
+      <c r="Q87">
+        <v>-300.02732816</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.3687087514852316</v>
+      </c>
+      <c r="T87">
+        <v>4.995621518879674</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.02849608131388465</v>
+      </c>
+      <c r="W87">
+        <v>0.2319951357822443</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.118733672141186</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2545021781376924</v>
+      </c>
+      <c r="C88">
+        <v>-1942.431376767131</v>
+      </c>
+      <c r="D88">
+        <v>729.4806232328688</v>
+      </c>
+      <c r="E88">
+        <v>2455.412</v>
+      </c>
+      <c r="F88">
+        <v>2729.812</v>
+      </c>
+      <c r="G88">
+        <v>57.9</v>
+      </c>
+      <c r="H88">
+        <v>2899.8</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>208</v>
+      </c>
+      <c r="K88">
+        <v>131.5</v>
+      </c>
+      <c r="L88">
+        <v>76.5</v>
+      </c>
+      <c r="M88">
+        <v>651.8791056000001</v>
+      </c>
+      <c r="N88">
+        <v>-575.3791056000001</v>
+      </c>
+      <c r="O88">
+        <v>-138.090985344</v>
+      </c>
+      <c r="P88">
+        <v>-437.2881202560001</v>
+      </c>
+      <c r="Q88">
+        <v>-305.7881202560001</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.3922736623056052</v>
+      </c>
+      <c r="T88">
+        <v>5.352451627371079</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.02816473153116506</v>
+      </c>
+      <c r="W88">
+        <v>0.2320742621103578</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.117353048046521</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2565021781376924</v>
+      </c>
+      <c r="C89">
+        <v>-1980.875015027925</v>
+      </c>
+      <c r="D89">
+        <v>722.7789849720749</v>
+      </c>
+      <c r="E89">
+        <v>2487.154</v>
+      </c>
+      <c r="F89">
+        <v>2761.554</v>
+      </c>
+      <c r="G89">
+        <v>57.9</v>
+      </c>
+      <c r="H89">
+        <v>2899.8</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>208</v>
+      </c>
+      <c r="K89">
+        <v>131.5</v>
+      </c>
+      <c r="L89">
+        <v>76.5</v>
+      </c>
+      <c r="M89">
+        <v>659.4590952000001</v>
+      </c>
+      <c r="N89">
+        <v>-582.9590952000001</v>
+      </c>
+      <c r="O89">
+        <v>-139.910182848</v>
+      </c>
+      <c r="P89">
+        <v>-443.0489123520001</v>
+      </c>
+      <c r="Q89">
+        <v>-311.5489123520001</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.4194639440214211</v>
+      </c>
+      <c r="T89">
+        <v>5.764178675630393</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.02784099898482983</v>
+      </c>
+      <c r="W89">
+        <v>0.2321515694424227</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.1160041624367909</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2585021781376924</v>
+      </c>
+      <c r="C90">
+        <v>-2019.196640146791</v>
+      </c>
+      <c r="D90">
+        <v>716.1993598532094</v>
+      </c>
+      <c r="E90">
+        <v>2518.896</v>
+      </c>
+      <c r="F90">
+        <v>2793.296</v>
+      </c>
+      <c r="G90">
+        <v>57.9</v>
+      </c>
+      <c r="H90">
+        <v>2899.8</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>208</v>
+      </c>
+      <c r="K90">
+        <v>131.5</v>
+      </c>
+      <c r="L90">
+        <v>76.5</v>
+      </c>
+      <c r="M90">
+        <v>667.0390848000001</v>
+      </c>
+      <c r="N90">
+        <v>-590.5390848000001</v>
+      </c>
+      <c r="O90">
+        <v>-141.729380352</v>
+      </c>
+      <c r="P90">
+        <v>-448.809704448</v>
+      </c>
+      <c r="Q90">
+        <v>-317.309704448</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.4511859393565396</v>
+      </c>
+      <c r="T90">
+        <v>6.244526898599594</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.02752462399636585</v>
+      </c>
+      <c r="W90">
+        <v>0.2322271197896678</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.1146859333181911</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2605021781376924</v>
+      </c>
+      <c r="C91">
+        <v>-2057.399554206087</v>
+      </c>
+      <c r="D91">
+        <v>709.7384457939135</v>
+      </c>
+      <c r="E91">
+        <v>2550.638</v>
+      </c>
+      <c r="F91">
+        <v>2825.038</v>
+      </c>
+      <c r="G91">
+        <v>57.9</v>
+      </c>
+      <c r="H91">
+        <v>2899.8</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>208</v>
+      </c>
+      <c r="K91">
+        <v>131.5</v>
+      </c>
+      <c r="L91">
+        <v>76.5</v>
+      </c>
+      <c r="M91">
+        <v>674.6190744000002</v>
+      </c>
+      <c r="N91">
+        <v>-598.1190744000002</v>
+      </c>
+      <c r="O91">
+        <v>-143.548577856</v>
+      </c>
+      <c r="P91">
+        <v>-454.5704965440001</v>
+      </c>
+      <c r="Q91">
+        <v>-323.0704965440001</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.488675570207134</v>
+      </c>
+      <c r="T91">
+        <v>6.812211162108647</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.02721535855820444</v>
+      </c>
+      <c r="W91">
+        <v>0.2323009723763008</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.1133973273258518</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2625021781376924</v>
+      </c>
+      <c r="C92">
+        <v>-2095.486941199655</v>
+      </c>
+      <c r="D92">
+        <v>703.3930588003449</v>
+      </c>
+      <c r="E92">
+        <v>2582.38</v>
+      </c>
+      <c r="F92">
+        <v>2856.78</v>
+      </c>
+      <c r="G92">
+        <v>57.9</v>
+      </c>
+      <c r="H92">
+        <v>2899.8</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>208</v>
+      </c>
+      <c r="K92">
+        <v>131.5</v>
+      </c>
+      <c r="L92">
+        <v>76.5</v>
+      </c>
+      <c r="M92">
+        <v>682.1990640000001</v>
+      </c>
+      <c r="N92">
+        <v>-605.6990640000001</v>
+      </c>
+      <c r="O92">
+        <v>-145.36777536</v>
+      </c>
+      <c r="P92">
+        <v>-460.3312886400001</v>
+      </c>
+      <c r="Q92">
+        <v>-328.8312886400001</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.5336631272278475</v>
+      </c>
+      <c r="T92">
+        <v>7.493432278319513</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.0269129656853355</v>
+      </c>
+      <c r="W92">
+        <v>0.2323731837943419</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.1121373570222313</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2645021781376924</v>
+      </c>
+      <c r="C93">
+        <v>-2133.461872264868</v>
+      </c>
+      <c r="D93">
+        <v>697.1601277351319</v>
+      </c>
+      <c r="E93">
+        <v>2614.122</v>
+      </c>
+      <c r="F93">
+        <v>2888.522</v>
+      </c>
+      <c r="G93">
+        <v>57.9</v>
+      </c>
+      <c r="H93">
+        <v>2899.8</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>208</v>
+      </c>
+      <c r="K93">
+        <v>131.5</v>
+      </c>
+      <c r="L93">
+        <v>76.5</v>
+      </c>
+      <c r="M93">
+        <v>689.7790536000001</v>
+      </c>
+      <c r="N93">
+        <v>-613.2790536000001</v>
+      </c>
+      <c r="O93">
+        <v>-147.186972864</v>
+      </c>
+      <c r="P93">
+        <v>-466.0920807360001</v>
+      </c>
+      <c r="Q93">
+        <v>-334.5920807360001</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.5886479191420528</v>
+      </c>
+      <c r="T93">
+        <v>8.32603586479946</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.02661721880967247</v>
+      </c>
+      <c r="W93">
+        <v>0.2324438081482502</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.1109050783736353</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2665021781376925</v>
+      </c>
+      <c r="C94">
+        <v>-2171.327310638951</v>
+      </c>
+      <c r="D94">
+        <v>691.0366893610502</v>
+      </c>
+      <c r="E94">
+        <v>2645.864</v>
+      </c>
+      <c r="F94">
+        <v>2920.264000000001</v>
+      </c>
+      <c r="G94">
+        <v>57.9</v>
+      </c>
+      <c r="H94">
+        <v>2899.8</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>208</v>
+      </c>
+      <c r="K94">
+        <v>131.5</v>
+      </c>
+      <c r="L94">
+        <v>76.5</v>
+      </c>
+      <c r="M94">
+        <v>697.3590432000002</v>
+      </c>
+      <c r="N94">
+        <v>-620.8590432000002</v>
+      </c>
+      <c r="O94">
+        <v>-149.0061703680001</v>
+      </c>
+      <c r="P94">
+        <v>-471.8528728320001</v>
+      </c>
+      <c r="Q94">
+        <v>-340.3528728320001</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.6573789090348097</v>
+      </c>
+      <c r="T94">
+        <v>9.366790347899395</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.02632790121391516</v>
+      </c>
+      <c r="W94">
+        <v>0.2325128971901171</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.1096995883913132</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2685021781376925</v>
+      </c>
+      <c r="C95">
+        <v>-2209.086116356367</v>
+      </c>
+      <c r="D95">
+        <v>685.019883643633</v>
+      </c>
+      <c r="E95">
+        <v>2677.606</v>
+      </c>
+      <c r="F95">
+        <v>2952.006</v>
+      </c>
+      <c r="G95">
+        <v>57.9</v>
+      </c>
+      <c r="H95">
+        <v>2899.8</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>208</v>
+      </c>
+      <c r="K95">
+        <v>131.5</v>
+      </c>
+      <c r="L95">
+        <v>76.5</v>
+      </c>
+      <c r="M95">
+        <v>704.9390328000001</v>
+      </c>
+      <c r="N95">
+        <v>-628.4390328000001</v>
+      </c>
+      <c r="O95">
+        <v>-150.825367872</v>
+      </c>
+      <c r="P95">
+        <v>-477.613664928</v>
+      </c>
+      <c r="Q95">
+        <v>-346.113664928</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.7457473246112112</v>
+      </c>
+      <c r="T95">
+        <v>10.70490325474217</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.02604480550193758</v>
+      </c>
+      <c r="W95">
+        <v>0.2325805004461373</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.1085200229247399</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2705021781376925</v>
+      </c>
+      <c r="C96">
+        <v>-2246.741050702945</v>
+      </c>
+      <c r="D96">
+        <v>679.1069492970551</v>
+      </c>
+      <c r="E96">
+        <v>2709.348</v>
+      </c>
+      <c r="F96">
+        <v>2983.748000000001</v>
+      </c>
+      <c r="G96">
+        <v>57.9</v>
+      </c>
+      <c r="H96">
+        <v>2899.8</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>208</v>
+      </c>
+      <c r="K96">
+        <v>131.5</v>
+      </c>
+      <c r="L96">
+        <v>76.5</v>
+      </c>
+      <c r="M96">
+        <v>712.5190224000002</v>
+      </c>
+      <c r="N96">
+        <v>-636.0190224000002</v>
+      </c>
+      <c r="O96">
+        <v>-152.644565376</v>
+      </c>
+      <c r="P96">
+        <v>-483.3744570240001</v>
+      </c>
+      <c r="Q96">
+        <v>-351.8744570240001</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.8635718787130799</v>
+      </c>
+      <c r="T96">
+        <v>12.4890537971992</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.0257677331029808</v>
+      </c>
+      <c r="W96">
+        <v>0.2326466653350082</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.1073655545957534</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2725021781376925</v>
+      </c>
+      <c r="C97">
+        <v>-2284.294780441271</v>
+      </c>
+      <c r="D97">
+        <v>673.2952195587302</v>
+      </c>
+      <c r="E97">
+        <v>2741.090000000001</v>
+      </c>
+      <c r="F97">
+        <v>3015.490000000001</v>
+      </c>
+      <c r="G97">
+        <v>57.9</v>
+      </c>
+      <c r="H97">
+        <v>2899.8</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>208</v>
+      </c>
+      <c r="K97">
+        <v>131.5</v>
+      </c>
+      <c r="L97">
+        <v>76.5</v>
+      </c>
+      <c r="M97">
+        <v>720.0990120000002</v>
+      </c>
+      <c r="N97">
+        <v>-643.5990120000002</v>
+      </c>
+      <c r="O97">
+        <v>-154.46376288</v>
+      </c>
+      <c r="P97">
+        <v>-489.1352491200002</v>
+      </c>
+      <c r="Q97">
+        <v>-357.6352491200002</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.028526254455696</v>
+      </c>
+      <c r="T97">
+        <v>14.98686455663904</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.02549649380715994</v>
+      </c>
+      <c r="W97">
+        <v>0.2327114372788502</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.1062353908631665</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2745021781376925</v>
+      </c>
+      <c r="C98">
+        <v>-2321.749881820973</v>
+      </c>
+      <c r="D98">
+        <v>667.5821181790271</v>
+      </c>
+      <c r="E98">
+        <v>2772.832</v>
+      </c>
+      <c r="F98">
+        <v>3047.232</v>
+      </c>
+      <c r="G98">
+        <v>57.9</v>
+      </c>
+      <c r="H98">
+        <v>2899.8</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>208</v>
+      </c>
+      <c r="K98">
+        <v>131.5</v>
+      </c>
+      <c r="L98">
+        <v>76.5</v>
+      </c>
+      <c r="M98">
+        <v>727.6790016</v>
+      </c>
+      <c r="N98">
+        <v>-651.1790016</v>
+      </c>
+      <c r="O98">
+        <v>-156.282960384</v>
+      </c>
+      <c r="P98">
+        <v>-494.896041216</v>
+      </c>
+      <c r="Q98">
+        <v>-363.396041216</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.275957818069618</v>
+      </c>
+      <c r="T98">
+        <v>18.73358069579876</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.02523090533000203</v>
+      </c>
+      <c r="W98">
+        <v>0.2327748598071955</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.1051287722083418</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2765021781376925</v>
+      </c>
+      <c r="C99">
+        <v>-2359.10884438656</v>
+      </c>
+      <c r="D99">
+        <v>661.9651556134398</v>
+      </c>
+      <c r="E99">
+        <v>2804.574</v>
+      </c>
+      <c r="F99">
+        <v>3078.974</v>
+      </c>
+      <c r="G99">
+        <v>57.9</v>
+      </c>
+      <c r="H99">
+        <v>2899.8</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>208</v>
+      </c>
+      <c r="K99">
+        <v>131.5</v>
+      </c>
+      <c r="L99">
+        <v>76.5</v>
+      </c>
+      <c r="M99">
+        <v>735.2589912000001</v>
+      </c>
+      <c r="N99">
+        <v>-658.7589912000001</v>
+      </c>
+      <c r="O99">
+        <v>-158.102157888</v>
+      </c>
+      <c r="P99">
+        <v>-500.6568333120001</v>
+      </c>
+      <c r="Q99">
+        <v>-369.1568333120001</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.688343757426157</v>
+      </c>
+      <c r="T99">
+        <v>24.97810759439836</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.02497079290391954</v>
+      </c>
+      <c r="W99">
+        <v>0.232836974654544</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.1040449704329981</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2785021781376925</v>
+      </c>
+      <c r="C100">
+        <v>-2396.374074594617</v>
+      </c>
+      <c r="D100">
+        <v>656.4419254053838</v>
+      </c>
+      <c r="E100">
+        <v>2836.316</v>
+      </c>
+      <c r="F100">
+        <v>3110.716</v>
+      </c>
+      <c r="G100">
+        <v>57.9</v>
+      </c>
+      <c r="H100">
+        <v>2899.8</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>208</v>
+      </c>
+      <c r="K100">
+        <v>131.5</v>
+      </c>
+      <c r="L100">
+        <v>76.5</v>
+      </c>
+      <c r="M100">
+        <v>742.8389808000002</v>
+      </c>
+      <c r="N100">
+        <v>-666.3389808000002</v>
+      </c>
+      <c r="O100">
+        <v>-159.921355392</v>
+      </c>
+      <c r="P100">
+        <v>-506.4176254080002</v>
+      </c>
+      <c r="Q100">
+        <v>-374.9176254080002</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.513115636139235</v>
+      </c>
+      <c r="T100">
+        <v>37.46716139159753</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.02471598889469586</v>
+      </c>
+      <c r="W100">
+        <v>0.2328978218519467</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.1029832870612328</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2805021781376925</v>
+      </c>
+      <c r="C101">
+        <v>-2433.547899251417</v>
+      </c>
+      <c r="D101">
+        <v>651.0101007485831</v>
+      </c>
+      <c r="E101">
+        <v>2868.058</v>
+      </c>
+      <c r="F101">
+        <v>3142.458</v>
+      </c>
+      <c r="G101">
+        <v>57.9</v>
+      </c>
+      <c r="H101">
+        <v>2899.8</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>208</v>
+      </c>
+      <c r="K101">
+        <v>131.5</v>
+      </c>
+      <c r="L101">
+        <v>76.5</v>
+      </c>
+      <c r="M101">
+        <v>750.4189704</v>
+      </c>
+      <c r="N101">
+        <v>-673.9189704</v>
+      </c>
+      <c r="O101">
+        <v>-161.740552896</v>
+      </c>
+      <c r="P101">
+        <v>-512.178417504</v>
+      </c>
+      <c r="Q101">
+        <v>-380.678417504</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>4.987431272278471</v>
+      </c>
+      <c r="T101">
+        <v>74.93432278319506</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.02446633244121409</v>
+      </c>
+      <c r="W101">
+        <v>0.2329574398130381</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.101943051838392</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/austria/austria_air_transport.xlsx
+++ b/research/traditional_assets/database/data/austria/austria_air_transport.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08491369717164139</v>
+        <v>0.08474410429842945</v>
       </c>
       <c r="C2">
-        <v>4671.143879926085</v>
+        <v>4640.601956322568</v>
       </c>
       <c r="D2">
-        <v>4646.243879926085</v>
+        <v>4662.517956322568</v>
       </c>
       <c r="E2">
-        <v>-61.9</v>
+        <v>-15.084</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>46.816</v>
       </c>
       <c r="G2">
         <v>24.9</v>
@@ -1451,28 +1451,28 @@
         <v>326.5</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.3548448</v>
       </c>
       <c r="N2">
-        <v>326.5</v>
+        <v>324.1451552</v>
       </c>
       <c r="O2">
-        <v>78.36</v>
+        <v>77.79483724799999</v>
       </c>
       <c r="P2">
-        <v>248.14</v>
+        <v>246.350317952</v>
       </c>
       <c r="Q2">
-        <v>397.34</v>
+        <v>395.550317952</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08491369717164139</v>
+        <v>0.08521396393780753</v>
       </c>
       <c r="T2">
-        <v>0.8042187817285177</v>
+        <v>0.8103925824771406</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>138.6503263399779</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08474410429842945</v>
+        <v>0.08457451142521751</v>
       </c>
       <c r="C3">
-        <v>4640.601956322568</v>
+        <v>4610.174437595884</v>
       </c>
       <c r="D3">
-        <v>4662.517956322568</v>
+        <v>4678.906437595884</v>
       </c>
       <c r="E3">
-        <v>-15.084</v>
+        <v>31.73199999999999</v>
       </c>
       <c r="F3">
-        <v>46.816</v>
+        <v>93.63199999999999</v>
       </c>
       <c r="G3">
         <v>24.9</v>
@@ -1533,28 +1533,28 @@
         <v>326.5</v>
       </c>
       <c r="M3">
-        <v>2.3548448</v>
+        <v>4.709689599999999</v>
       </c>
       <c r="N3">
-        <v>324.1451552</v>
+        <v>321.7903104</v>
       </c>
       <c r="O3">
-        <v>77.79483724799999</v>
+        <v>77.229674496</v>
       </c>
       <c r="P3">
-        <v>246.350317952</v>
+        <v>244.560635904</v>
       </c>
       <c r="Q3">
-        <v>395.550317952</v>
+        <v>393.760635904</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08521396393780753</v>
+        <v>0.08552035859716073</v>
       </c>
       <c r="T3">
-        <v>0.8103925824771406</v>
+        <v>0.816692379159409</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>138.6503263399779</v>
+        <v>69.32516316998897</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08457451142521751</v>
+        <v>0.08440491855200556</v>
       </c>
       <c r="C4">
-        <v>4610.174437595884</v>
+        <v>4579.862534380944</v>
       </c>
       <c r="D4">
-        <v>4678.906437595884</v>
+        <v>4695.410534380944</v>
       </c>
       <c r="E4">
-        <v>31.73199999999999</v>
+        <v>78.54799999999997</v>
       </c>
       <c r="F4">
-        <v>93.63199999999999</v>
+        <v>140.448</v>
       </c>
       <c r="G4">
         <v>24.9</v>
@@ -1615,28 +1615,28 @@
         <v>326.5</v>
       </c>
       <c r="M4">
-        <v>4.709689599999999</v>
+        <v>7.064534399999999</v>
       </c>
       <c r="N4">
-        <v>321.7903104</v>
+        <v>319.4354656</v>
       </c>
       <c r="O4">
-        <v>77.229674496</v>
+        <v>76.664511744</v>
       </c>
       <c r="P4">
-        <v>244.560635904</v>
+        <v>242.770953856</v>
       </c>
       <c r="Q4">
-        <v>393.760635904</v>
+        <v>391.970953856</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08552035859716073</v>
+        <v>0.08583307067217069</v>
       </c>
       <c r="T4">
-        <v>0.816692379159409</v>
+        <v>0.8231220685567757</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>69.32516316998897</v>
+        <v>46.21677544665931</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08440491855200556</v>
+        <v>0.08423532567879363</v>
       </c>
       <c r="C5">
-        <v>4579.862534380944</v>
+        <v>4549.667474454412</v>
       </c>
       <c r="D5">
-        <v>4695.410534380944</v>
+        <v>4712.031474454412</v>
       </c>
       <c r="E5">
-        <v>78.54799999999997</v>
+        <v>125.364</v>
       </c>
       <c r="F5">
-        <v>140.448</v>
+        <v>187.264</v>
       </c>
       <c r="G5">
         <v>24.9</v>
@@ -1697,28 +1697,28 @@
         <v>326.5</v>
       </c>
       <c r="M5">
-        <v>7.064534399999999</v>
+        <v>9.419379199999998</v>
       </c>
       <c r="N5">
-        <v>319.4354656</v>
+        <v>317.0806208</v>
       </c>
       <c r="O5">
-        <v>76.664511744</v>
+        <v>76.099348992</v>
       </c>
       <c r="P5">
-        <v>242.770953856</v>
+        <v>240.981271808</v>
       </c>
       <c r="Q5">
-        <v>391.970953856</v>
+        <v>390.181271808</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08583307067217069</v>
+        <v>0.08615229758207671</v>
       </c>
       <c r="T5">
-        <v>0.8231220685567757</v>
+        <v>0.8296857098165875</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>46.21677544665931</v>
+        <v>34.66258158499448</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08423532567879363</v>
+        <v>0.08406573280558167</v>
       </c>
       <c r="C6">
-        <v>4549.667474454412</v>
+        <v>4519.590503039176</v>
       </c>
       <c r="D6">
-        <v>4712.031474454412</v>
+        <v>4728.770503039176</v>
       </c>
       <c r="E6">
-        <v>125.364</v>
+        <v>172.18</v>
       </c>
       <c r="F6">
-        <v>187.264</v>
+        <v>234.08</v>
       </c>
       <c r="G6">
         <v>24.9</v>
@@ -1779,28 +1779,28 @@
         <v>326.5</v>
       </c>
       <c r="M6">
-        <v>9.419379199999998</v>
+        <v>11.774224</v>
       </c>
       <c r="N6">
-        <v>317.0806208</v>
+        <v>314.725776</v>
       </c>
       <c r="O6">
-        <v>76.099348992</v>
+        <v>75.53418624</v>
       </c>
       <c r="P6">
-        <v>240.981271808</v>
+        <v>239.19158976</v>
       </c>
       <c r="Q6">
-        <v>390.181271808</v>
+        <v>388.39158976</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08615229758207671</v>
+        <v>0.08647824505850704</v>
       </c>
       <c r="T6">
-        <v>0.8296857098165875</v>
+        <v>0.8363875329976584</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>34.66258158499448</v>
+        <v>27.73006526799558</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08406573280558167</v>
+        <v>0.08389613993236976</v>
       </c>
       <c r="C7">
-        <v>4519.590503039176</v>
+        <v>4489.632883115325</v>
       </c>
       <c r="D7">
-        <v>4728.770503039176</v>
+        <v>4745.628883115325</v>
       </c>
       <c r="E7">
-        <v>172.18</v>
+        <v>218.996</v>
       </c>
       <c r="F7">
-        <v>234.08</v>
+        <v>280.896</v>
       </c>
       <c r="G7">
         <v>24.9</v>
@@ -1861,28 +1861,28 @@
         <v>326.5</v>
       </c>
       <c r="M7">
-        <v>11.774224</v>
+        <v>14.1290688</v>
       </c>
       <c r="N7">
-        <v>314.725776</v>
+        <v>312.3709312</v>
       </c>
       <c r="O7">
-        <v>75.53418624</v>
+        <v>74.96902348799999</v>
       </c>
       <c r="P7">
-        <v>239.19158976</v>
+        <v>237.401907712</v>
       </c>
       <c r="Q7">
-        <v>388.39158976</v>
+        <v>386.601907712</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08647824505850704</v>
+        <v>0.08681112758762741</v>
       </c>
       <c r="T7">
-        <v>0.8363875329976584</v>
+        <v>0.8432319481613054</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>27.73006526799558</v>
+        <v>23.10838772332965</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08389613993236976</v>
+        <v>0.08372654705915782</v>
       </c>
       <c r="C8">
-        <v>4489.632883115325</v>
+        <v>4459.795895737831</v>
       </c>
       <c r="D8">
-        <v>4745.628883115325</v>
+        <v>4762.60789573783</v>
       </c>
       <c r="E8">
-        <v>218.996</v>
+        <v>265.812</v>
       </c>
       <c r="F8">
-        <v>280.896</v>
+        <v>327.7119999999999</v>
       </c>
       <c r="G8">
         <v>24.9</v>
@@ -1943,28 +1943,28 @@
         <v>326.5</v>
       </c>
       <c r="M8">
-        <v>14.1290688</v>
+        <v>16.4839136</v>
       </c>
       <c r="N8">
-        <v>312.3709312</v>
+        <v>310.0160864</v>
       </c>
       <c r="O8">
-        <v>74.969023488</v>
+        <v>74.403860736</v>
       </c>
       <c r="P8">
-        <v>237.401907712</v>
+        <v>235.612225664</v>
       </c>
       <c r="Q8">
-        <v>386.601907712</v>
+        <v>384.812225664</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08681112758762741</v>
+        <v>0.08715116888081485</v>
       </c>
       <c r="T8">
-        <v>0.8432319481613054</v>
+        <v>0.8502235550489017</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>23.10838772332966</v>
+        <v>19.8071894771397</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08372654705915782</v>
+        <v>0.08355695418594587</v>
       </c>
       <c r="C9">
-        <v>4459.795895737831</v>
+        <v>4430.080840361024</v>
       </c>
       <c r="D9">
-        <v>4762.60789573783</v>
+        <v>4779.708840361025</v>
       </c>
       <c r="E9">
-        <v>265.812</v>
+        <v>312.628</v>
       </c>
       <c r="F9">
-        <v>327.712</v>
+        <v>374.528</v>
       </c>
       <c r="G9">
         <v>24.9</v>
@@ -2025,28 +2025,28 @@
         <v>326.5</v>
       </c>
       <c r="M9">
-        <v>16.4839136</v>
+        <v>18.8387584</v>
       </c>
       <c r="N9">
-        <v>310.0160864</v>
+        <v>307.6612416</v>
       </c>
       <c r="O9">
-        <v>74.403860736</v>
+        <v>73.83869798399999</v>
       </c>
       <c r="P9">
-        <v>235.612225664</v>
+        <v>233.822543616</v>
       </c>
       <c r="Q9">
-        <v>384.812225664</v>
+        <v>383.022543616</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08715116888081485</v>
+        <v>0.08749860237602812</v>
       </c>
       <c r="T9">
-        <v>0.8502235550489017</v>
+        <v>0.8573671533905761</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>19.8071894771397</v>
+        <v>17.33129079249724</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08355695418594587</v>
+        <v>0.08338736131273394</v>
       </c>
       <c r="C10">
-        <v>4430.080840361024</v>
+        <v>4400.489035170139</v>
       </c>
       <c r="D10">
-        <v>4779.708840361025</v>
+        <v>4796.933035170139</v>
       </c>
       <c r="E10">
-        <v>312.628</v>
+        <v>359.444</v>
       </c>
       <c r="F10">
-        <v>374.528</v>
+        <v>421.3439999999999</v>
       </c>
       <c r="G10">
         <v>24.9</v>
@@ -2107,28 +2107,28 @@
         <v>326.5</v>
       </c>
       <c r="M10">
-        <v>18.8387584</v>
+        <v>21.19360319999999</v>
       </c>
       <c r="N10">
-        <v>307.6612416</v>
+        <v>305.3063968</v>
       </c>
       <c r="O10">
-        <v>73.83869798399999</v>
+        <v>73.273535232</v>
       </c>
       <c r="P10">
-        <v>233.822543616</v>
+        <v>232.032861568</v>
       </c>
       <c r="Q10">
-        <v>383.022543616</v>
+        <v>381.232861568</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08749860237602812</v>
+        <v>0.08785367177223509</v>
       </c>
       <c r="T10">
-        <v>0.8573671533905761</v>
+        <v>0.8646677538936062</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>17.33129079249724</v>
+        <v>15.40559181555311</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08338736131273394</v>
+        <v>0.083217768439522</v>
       </c>
       <c r="C11">
-        <v>4400.489035170139</v>
+        <v>4371.021817420014</v>
       </c>
       <c r="D11">
-        <v>4796.933035170139</v>
+        <v>4814.281817420014</v>
       </c>
       <c r="E11">
-        <v>359.444</v>
+        <v>406.2599999999999</v>
       </c>
       <c r="F11">
-        <v>421.3439999999999</v>
+        <v>468.1599999999999</v>
       </c>
       <c r="G11">
         <v>24.9</v>
@@ -2189,28 +2189,28 @@
         <v>326.5</v>
       </c>
       <c r="M11">
-        <v>21.19360319999999</v>
+        <v>23.54844799999999</v>
       </c>
       <c r="N11">
-        <v>305.3063968</v>
+        <v>302.951552</v>
       </c>
       <c r="O11">
-        <v>73.273535232</v>
+        <v>72.70837247999999</v>
       </c>
       <c r="P11">
-        <v>232.032861568</v>
+        <v>230.24317952</v>
       </c>
       <c r="Q11">
-        <v>381.232861568</v>
+        <v>379.44317952</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08785367177223509</v>
+        <v>0.08821663159946888</v>
       </c>
       <c r="T11">
-        <v>0.8646677538936062</v>
+        <v>0.8721305899633703</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>15.40559181555311</v>
+        <v>13.86503263399779</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.083217768439522</v>
+        <v>0.08317357556631007</v>
       </c>
       <c r="C12">
-        <v>4371.021817420014</v>
+        <v>4328.747230180021</v>
       </c>
       <c r="D12">
-        <v>4814.281817420014</v>
+        <v>4818.823230180021</v>
       </c>
       <c r="E12">
-        <v>406.26</v>
+        <v>453.076</v>
       </c>
       <c r="F12">
-        <v>468.16</v>
+        <v>514.976</v>
       </c>
       <c r="G12">
         <v>24.9</v>
@@ -2271,45 +2271,45 @@
         <v>326.5</v>
       </c>
       <c r="M12">
-        <v>23.548448</v>
+        <v>26.6757568</v>
       </c>
       <c r="N12">
-        <v>302.951552</v>
+        <v>299.8242432</v>
       </c>
       <c r="O12">
-        <v>72.70837247999999</v>
+        <v>71.95781836800001</v>
       </c>
       <c r="P12">
-        <v>230.24317952</v>
+        <v>227.866424832</v>
       </c>
       <c r="Q12">
-        <v>379.44317952</v>
+        <v>377.066424832</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08821663159946888</v>
+        <v>0.08858774782731468</v>
       </c>
       <c r="T12">
-        <v>0.8721305899633703</v>
+        <v>0.8797611302144774</v>
       </c>
       <c r="U12">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V12">
         <v>0.24</v>
       </c>
       <c r="W12">
-        <v>0.038228</v>
+        <v>0.039368</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y12">
-        <v>13.86503263399779</v>
+        <v>12.23957777272883</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08317357556631007</v>
+        <v>0.08301538269309812</v>
       </c>
       <c r="C13">
-        <v>4328.747230180021</v>
+        <v>4298.258144248861</v>
       </c>
       <c r="D13">
-        <v>4818.823230180021</v>
+        <v>4835.150144248861</v>
       </c>
       <c r="E13">
-        <v>453.076</v>
+        <v>499.8919999999999</v>
       </c>
       <c r="F13">
-        <v>514.976</v>
+        <v>561.7919999999999</v>
       </c>
       <c r="G13">
         <v>24.9</v>
@@ -2353,28 +2353,28 @@
         <v>326.5</v>
       </c>
       <c r="M13">
-        <v>26.6757568</v>
+        <v>29.1008256</v>
       </c>
       <c r="N13">
-        <v>299.8242432</v>
+        <v>297.3991744</v>
       </c>
       <c r="O13">
-        <v>71.95781836800001</v>
+        <v>71.375801856</v>
       </c>
       <c r="P13">
-        <v>227.866424832</v>
+        <v>226.023372544</v>
       </c>
       <c r="Q13">
-        <v>377.066424832</v>
+        <v>375.223372544</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08858774782731468</v>
+        <v>0.08896729851488422</v>
       </c>
       <c r="T13">
-        <v>0.8797611302144774</v>
+        <v>0.8875650918349276</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>12.23957777272883</v>
+        <v>11.21961295833476</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08301538269309812</v>
+        <v>0.08285718981988617</v>
       </c>
       <c r="C14">
-        <v>4298.258144248861</v>
+        <v>4267.880070635239</v>
       </c>
       <c r="D14">
-        <v>4835.150144248861</v>
+        <v>4851.58807063524</v>
       </c>
       <c r="E14">
-        <v>499.8919999999999</v>
+        <v>546.708</v>
       </c>
       <c r="F14">
-        <v>561.7919999999999</v>
+        <v>608.6079999999999</v>
       </c>
       <c r="G14">
         <v>24.9</v>
@@ -2435,28 +2435,28 @@
         <v>326.5</v>
       </c>
       <c r="M14">
-        <v>29.1008256</v>
+        <v>31.52589439999999</v>
       </c>
       <c r="N14">
-        <v>297.3991744</v>
+        <v>294.9741056</v>
       </c>
       <c r="O14">
-        <v>71.375801856</v>
+        <v>70.793785344</v>
       </c>
       <c r="P14">
-        <v>226.023372544</v>
+        <v>224.180320256</v>
       </c>
       <c r="Q14">
-        <v>375.223372544</v>
+        <v>373.380320256</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08896729851488422</v>
+        <v>0.08935557450561629</v>
       </c>
       <c r="T14">
-        <v>0.8875650918349276</v>
+        <v>0.8955484548719401</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.21961295833476</v>
+        <v>10.35656580769363</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08285718981988617</v>
+        <v>0.08287987694667424</v>
       </c>
       <c r="C15">
-        <v>4267.880070635239</v>
+        <v>4218.699774477938</v>
       </c>
       <c r="D15">
-        <v>4851.58807063524</v>
+        <v>4849.223774477939</v>
       </c>
       <c r="E15">
-        <v>546.708</v>
+        <v>593.524</v>
       </c>
       <c r="F15">
-        <v>608.6079999999999</v>
+        <v>655.424</v>
       </c>
       <c r="G15">
         <v>24.9</v>
@@ -2517,45 +2517,45 @@
         <v>326.5</v>
       </c>
       <c r="M15">
-        <v>31.52589439999999</v>
+        <v>35.065184</v>
       </c>
       <c r="N15">
-        <v>294.9741056</v>
+        <v>291.434816</v>
       </c>
       <c r="O15">
-        <v>70.793785344</v>
+        <v>69.94435584</v>
       </c>
       <c r="P15">
-        <v>224.180320256</v>
+        <v>221.49046016</v>
       </c>
       <c r="Q15">
-        <v>373.380320256</v>
+        <v>370.69046016</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08935557450561629</v>
+        <v>0.08975288017055144</v>
       </c>
       <c r="T15">
-        <v>0.8955484548719401</v>
+        <v>0.9037174775144645</v>
       </c>
       <c r="U15">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V15">
         <v>0.24</v>
       </c>
       <c r="W15">
-        <v>0.039368</v>
+        <v>0.04066</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>10.35656580769363</v>
+        <v>9.311230193459131</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08287987694667424</v>
+        <v>0.08273460407346231</v>
       </c>
       <c r="C16">
-        <v>4218.699774477938</v>
+        <v>4187.063102343759</v>
       </c>
       <c r="D16">
-        <v>4849.223774477939</v>
+        <v>4864.403102343759</v>
       </c>
       <c r="E16">
-        <v>593.524</v>
+        <v>640.34</v>
       </c>
       <c r="F16">
-        <v>655.424</v>
+        <v>702.24</v>
       </c>
       <c r="G16">
         <v>24.9</v>
@@ -2599,28 +2599,28 @@
         <v>326.5</v>
       </c>
       <c r="M16">
-        <v>35.065184</v>
+        <v>37.56984</v>
       </c>
       <c r="N16">
-        <v>291.434816</v>
+        <v>288.93016</v>
       </c>
       <c r="O16">
-        <v>69.94435584</v>
+        <v>69.3432384</v>
       </c>
       <c r="P16">
-        <v>221.49046016</v>
+        <v>219.5869216</v>
       </c>
       <c r="Q16">
-        <v>370.69046016</v>
+        <v>368.7869216</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08975288017055144</v>
+        <v>0.0901595342040733</v>
       </c>
       <c r="T16">
-        <v>0.9037174775144645</v>
+        <v>0.9120787124544601</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>9.311230193459131</v>
+        <v>8.69048151389519</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08273460407346231</v>
+        <v>0.08258933120025036</v>
       </c>
       <c r="C17">
-        <v>4187.063102343759</v>
+        <v>4155.521759078399</v>
       </c>
       <c r="D17">
-        <v>4864.403102343759</v>
+        <v>4879.677759078399</v>
       </c>
       <c r="E17">
-        <v>640.3399999999999</v>
+        <v>687.1559999999999</v>
       </c>
       <c r="F17">
-        <v>702.2399999999999</v>
+        <v>749.0559999999999</v>
       </c>
       <c r="G17">
         <v>24.9</v>
@@ -2681,28 +2681,28 @@
         <v>326.5</v>
       </c>
       <c r="M17">
-        <v>37.56983999999999</v>
+        <v>40.074496</v>
       </c>
       <c r="N17">
-        <v>288.93016</v>
+        <v>286.425504</v>
       </c>
       <c r="O17">
-        <v>69.3432384</v>
+        <v>68.74212095999999</v>
       </c>
       <c r="P17">
-        <v>219.5869216</v>
+        <v>217.68338304</v>
       </c>
       <c r="Q17">
-        <v>368.7869216</v>
+        <v>366.88338304</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.0901595342040733</v>
+        <v>0.09057587047648853</v>
       </c>
       <c r="T17">
-        <v>0.91207871245446</v>
+        <v>0.9206390244168365</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.69048151389519</v>
+        <v>8.147326419276739</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08258933120025036</v>
+        <v>0.08244405832703842</v>
       </c>
       <c r="C18">
-        <v>4155.521759078399</v>
+        <v>4124.076645533894</v>
       </c>
       <c r="D18">
-        <v>4879.677759078399</v>
+        <v>4895.048645533895</v>
       </c>
       <c r="E18">
-        <v>687.1559999999999</v>
+        <v>733.972</v>
       </c>
       <c r="F18">
-        <v>749.0559999999999</v>
+        <v>795.872</v>
       </c>
       <c r="G18">
         <v>24.9</v>
@@ -2763,28 +2763,28 @@
         <v>326.5</v>
       </c>
       <c r="M18">
-        <v>40.074496</v>
+        <v>42.57915199999999</v>
       </c>
       <c r="N18">
-        <v>286.425504</v>
+        <v>283.920848</v>
       </c>
       <c r="O18">
-        <v>68.74212095999999</v>
+        <v>68.14100352</v>
       </c>
       <c r="P18">
-        <v>217.68338304</v>
+        <v>215.77984448</v>
       </c>
       <c r="Q18">
-        <v>366.88338304</v>
+        <v>364.97984448</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09057587047648853</v>
+        <v>0.09100223894823906</v>
       </c>
       <c r="T18">
-        <v>0.9206390244168365</v>
+        <v>0.9294056089566195</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.147326419276739</v>
+        <v>7.668071924025167</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08244405832703842</v>
+        <v>0.08240822545382648</v>
       </c>
       <c r="C19">
-        <v>4124.076645533894</v>
+        <v>4081.066914337046</v>
       </c>
       <c r="D19">
-        <v>4895.048645533895</v>
+        <v>4898.854914337046</v>
       </c>
       <c r="E19">
-        <v>733.972</v>
+        <v>780.788</v>
       </c>
       <c r="F19">
-        <v>795.872</v>
+        <v>842.688</v>
       </c>
       <c r="G19">
         <v>24.9</v>
@@ -2845,45 +2845,45 @@
         <v>326.5</v>
       </c>
       <c r="M19">
-        <v>42.57915199999999</v>
+        <v>45.7579584</v>
       </c>
       <c r="N19">
-        <v>283.920848</v>
+        <v>280.7420416</v>
       </c>
       <c r="O19">
-        <v>68.14100352</v>
+        <v>67.378089984</v>
       </c>
       <c r="P19">
-        <v>215.77984448</v>
+        <v>213.363951616</v>
       </c>
       <c r="Q19">
-        <v>364.97984448</v>
+        <v>362.563951616</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09100223894823906</v>
+        <v>0.0914390066510079</v>
       </c>
       <c r="T19">
-        <v>0.9294056089566195</v>
+        <v>0.9383860126315193</v>
       </c>
       <c r="U19">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V19">
         <v>0.24</v>
       </c>
       <c r="W19">
-        <v>0.04066</v>
+        <v>0.041268</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y19">
-        <v>7.668071924025167</v>
+        <v>7.135370794864833</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08240822545382649</v>
+        <v>0.08226903258061453</v>
       </c>
       <c r="C20">
-        <v>4081.066914337045</v>
+        <v>4049.09270002042</v>
       </c>
       <c r="D20">
-        <v>4898.854914337046</v>
+        <v>4913.69670002042</v>
       </c>
       <c r="E20">
-        <v>780.7879999999999</v>
+        <v>827.6039999999999</v>
       </c>
       <c r="F20">
-        <v>842.6879999999999</v>
+        <v>889.5039999999999</v>
       </c>
       <c r="G20">
         <v>24.9</v>
@@ -2927,28 +2927,28 @@
         <v>326.5</v>
       </c>
       <c r="M20">
-        <v>45.75795839999999</v>
+        <v>48.30006719999999</v>
       </c>
       <c r="N20">
-        <v>280.7420416</v>
+        <v>278.1999328</v>
       </c>
       <c r="O20">
-        <v>67.378089984</v>
+        <v>66.767983872</v>
       </c>
       <c r="P20">
-        <v>213.363951616</v>
+        <v>211.431948928</v>
       </c>
       <c r="Q20">
-        <v>362.563951616</v>
+        <v>360.631948928</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.0914390066510079</v>
+        <v>0.09188655874149942</v>
       </c>
       <c r="T20">
-        <v>0.9383860126315191</v>
+        <v>0.947588154668762</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.135370794864834</v>
+        <v>6.759824963556159</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08226903258061453</v>
+        <v>0.0821298397074026</v>
       </c>
       <c r="C21">
-        <v>4049.09270002042</v>
+        <v>4017.20868963915</v>
       </c>
       <c r="D21">
-        <v>4913.69670002042</v>
+        <v>4928.62868963915</v>
       </c>
       <c r="E21">
-        <v>827.6039999999999</v>
+        <v>874.42</v>
       </c>
       <c r="F21">
-        <v>889.5039999999999</v>
+        <v>936.3199999999999</v>
       </c>
       <c r="G21">
         <v>24.9</v>
@@ -3009,28 +3009,28 @@
         <v>326.5</v>
       </c>
       <c r="M21">
-        <v>48.30006719999999</v>
+        <v>50.84217599999999</v>
       </c>
       <c r="N21">
-        <v>278.1999328</v>
+        <v>275.657824</v>
       </c>
       <c r="O21">
-        <v>66.767983872</v>
+        <v>66.15787776000001</v>
       </c>
       <c r="P21">
-        <v>211.431948928</v>
+        <v>209.49994624</v>
       </c>
       <c r="Q21">
-        <v>360.631948928</v>
+        <v>358.69994624</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09188655874149942</v>
+        <v>0.09234529963425325</v>
       </c>
       <c r="T21">
-        <v>0.947588154668762</v>
+        <v>0.957020350256936</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.759824963556159</v>
+        <v>6.421833715378351</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0821298397074026</v>
+        <v>0.08199064683419066</v>
       </c>
       <c r="C22">
-        <v>4017.20868963915</v>
+        <v>3985.415708048671</v>
       </c>
       <c r="D22">
-        <v>4928.62868963915</v>
+        <v>4943.651708048671</v>
       </c>
       <c r="E22">
-        <v>874.42</v>
+        <v>921.236</v>
       </c>
       <c r="F22">
-        <v>936.3199999999999</v>
+        <v>983.136</v>
       </c>
       <c r="G22">
         <v>24.9</v>
@@ -3091,28 +3091,28 @@
         <v>326.5</v>
       </c>
       <c r="M22">
-        <v>50.84217599999999</v>
+        <v>53.3842848</v>
       </c>
       <c r="N22">
-        <v>275.657824</v>
+        <v>273.1157152</v>
       </c>
       <c r="O22">
-        <v>66.15787776000001</v>
+        <v>65.54777164799999</v>
       </c>
       <c r="P22">
-        <v>209.49994624</v>
+        <v>207.567943552</v>
       </c>
       <c r="Q22">
-        <v>358.69994624</v>
+        <v>356.767943552</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09234529963425325</v>
+        <v>0.09281565422049451</v>
       </c>
       <c r="T22">
-        <v>0.957020350256936</v>
+        <v>0.966691335606836</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.421833715378351</v>
+        <v>6.116032109884144</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08199064683419066</v>
+        <v>0.08201865396097874</v>
       </c>
       <c r="C23">
-        <v>3985.415708048671</v>
+        <v>3935.56955722667</v>
       </c>
       <c r="D23">
-        <v>4943.651708048671</v>
+        <v>4940.621557226671</v>
       </c>
       <c r="E23">
-        <v>921.2359999999999</v>
+        <v>968.052</v>
       </c>
       <c r="F23">
-        <v>983.1359999999999</v>
+        <v>1029.952</v>
       </c>
       <c r="G23">
         <v>24.9</v>
@@ -3173,45 +3173,45 @@
         <v>326.5</v>
       </c>
       <c r="M23">
-        <v>53.3842848</v>
+        <v>56.9563456</v>
       </c>
       <c r="N23">
-        <v>273.1157152</v>
+        <v>269.5436544</v>
       </c>
       <c r="O23">
-        <v>65.54777164799999</v>
+        <v>64.69047705599999</v>
       </c>
       <c r="P23">
-        <v>207.567943552</v>
+        <v>204.853177344</v>
       </c>
       <c r="Q23">
-        <v>356.767943552</v>
+        <v>354.053177344</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09281565422049451</v>
+        <v>0.09329806918074196</v>
       </c>
       <c r="T23">
-        <v>0.966691335606836</v>
+        <v>0.9766102949400667</v>
       </c>
       <c r="U23">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V23">
         <v>0.24</v>
       </c>
       <c r="W23">
-        <v>0.041268</v>
+        <v>0.042028</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y23">
-        <v>6.116032109884144</v>
+        <v>5.732460475835023</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08201865396097874</v>
+        <v>0.08188706108776679</v>
       </c>
       <c r="C24">
-        <v>3935.56955722667</v>
+        <v>3903.023239969769</v>
       </c>
       <c r="D24">
-        <v>4940.621557226671</v>
+        <v>4954.891239969769</v>
       </c>
       <c r="E24">
-        <v>968.052</v>
+        <v>1014.868</v>
       </c>
       <c r="F24">
-        <v>1029.952</v>
+        <v>1076.768</v>
       </c>
       <c r="G24">
         <v>24.9</v>
@@ -3255,28 +3255,28 @@
         <v>326.5</v>
       </c>
       <c r="M24">
-        <v>56.9563456</v>
+        <v>59.54527040000001</v>
       </c>
       <c r="N24">
-        <v>269.5436544</v>
+        <v>266.9547296</v>
       </c>
       <c r="O24">
-        <v>64.69047705599999</v>
+        <v>64.069135104</v>
       </c>
       <c r="P24">
-        <v>204.853177344</v>
+        <v>202.885594496</v>
       </c>
       <c r="Q24">
-        <v>354.053177344</v>
+        <v>352.085594496</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09329806918074196</v>
+        <v>0.09379301439969713</v>
       </c>
       <c r="T24">
-        <v>0.9766102949400667</v>
+        <v>0.986786889580654</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.732460475835023</v>
+        <v>5.483223063842195</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08188706108776679</v>
+        <v>0.08175546821455486</v>
       </c>
       <c r="C25">
-        <v>3903.023239969769</v>
+        <v>3870.559589907893</v>
       </c>
       <c r="D25">
-        <v>4954.891239969769</v>
+        <v>4969.243589907894</v>
       </c>
       <c r="E25">
-        <v>1014.868</v>
+        <v>1061.684</v>
       </c>
       <c r="F25">
-        <v>1076.768</v>
+        <v>1123.584</v>
       </c>
       <c r="G25">
         <v>24.9</v>
@@ -3337,28 +3337,28 @@
         <v>326.5</v>
       </c>
       <c r="M25">
-        <v>59.54527040000001</v>
+        <v>62.13419520000001</v>
       </c>
       <c r="N25">
-        <v>266.9547296</v>
+        <v>264.3658048</v>
       </c>
       <c r="O25">
-        <v>64.069135104</v>
+        <v>63.447793152</v>
       </c>
       <c r="P25">
-        <v>202.885594496</v>
+        <v>200.918011648</v>
       </c>
       <c r="Q25">
-        <v>352.085594496</v>
+        <v>350.118011648</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09379301439969713</v>
+        <v>0.09430098449283533</v>
       </c>
       <c r="T25">
-        <v>0.986786889580654</v>
+        <v>0.9972312893433619</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.483223063842195</v>
+        <v>5.254755436182103</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08175546821455484</v>
+        <v>0.08162387534134292</v>
       </c>
       <c r="C26">
-        <v>3870.559589907895</v>
+        <v>3838.179327489888</v>
       </c>
       <c r="D26">
-        <v>4969.243589907896</v>
+        <v>4983.679327489888</v>
       </c>
       <c r="E26">
-        <v>1061.684</v>
+        <v>1108.5</v>
       </c>
       <c r="F26">
-        <v>1123.584</v>
+        <v>1170.4</v>
       </c>
       <c r="G26">
         <v>24.9</v>
@@ -3419,28 +3419,28 @@
         <v>326.5</v>
       </c>
       <c r="M26">
-        <v>62.13419519999999</v>
+        <v>64.72311999999999</v>
       </c>
       <c r="N26">
-        <v>264.3658048</v>
+        <v>261.77688</v>
       </c>
       <c r="O26">
-        <v>63.447793152</v>
+        <v>62.8264512</v>
       </c>
       <c r="P26">
-        <v>200.918011648</v>
+        <v>198.9504288</v>
       </c>
       <c r="Q26">
-        <v>350.118011648</v>
+        <v>348.1504288</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09430098449283533</v>
+        <v>0.09482250045512389</v>
       </c>
       <c r="T26">
-        <v>0.9972312893433619</v>
+        <v>1.007954206433076</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.254755436182104</v>
+        <v>5.04456521873482</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08162387534134292</v>
+        <v>0.08149228246813095</v>
       </c>
       <c r="C27">
-        <v>3838.179327489888</v>
+        <v>3805.883181560659</v>
       </c>
       <c r="D27">
-        <v>4983.679327489888</v>
+        <v>4998.199181560659</v>
       </c>
       <c r="E27">
-        <v>1108.5</v>
+        <v>1155.316</v>
       </c>
       <c r="F27">
-        <v>1170.4</v>
+        <v>1217.216</v>
       </c>
       <c r="G27">
         <v>24.9</v>
@@ -3501,28 +3501,28 @@
         <v>326.5</v>
       </c>
       <c r="M27">
-        <v>64.72311999999999</v>
+        <v>67.3120448</v>
       </c>
       <c r="N27">
-        <v>261.77688</v>
+        <v>259.1879552</v>
       </c>
       <c r="O27">
-        <v>62.8264512</v>
+        <v>62.20510924800001</v>
       </c>
       <c r="P27">
-        <v>198.9504288</v>
+        <v>196.982845952</v>
       </c>
       <c r="Q27">
-        <v>348.1504288</v>
+        <v>346.182845952</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09482250045512389</v>
+        <v>0.09535811144342021</v>
       </c>
       <c r="T27">
-        <v>1.007954206433076</v>
+        <v>1.018966932092781</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.04456521873482</v>
+        <v>4.850543479552712</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08149228246813095</v>
+        <v>0.08136068959491903</v>
       </c>
       <c r="C28">
-        <v>3805.883181560659</v>
+        <v>3773.671889483815</v>
       </c>
       <c r="D28">
-        <v>4998.199181560659</v>
+        <v>5012.803889483816</v>
       </c>
       <c r="E28">
-        <v>1155.316</v>
+        <v>1202.132</v>
       </c>
       <c r="F28">
-        <v>1217.216</v>
+        <v>1264.032</v>
       </c>
       <c r="G28">
         <v>24.9</v>
@@ -3583,28 +3583,28 @@
         <v>326.5</v>
       </c>
       <c r="M28">
-        <v>67.3120448</v>
+        <v>69.9009696</v>
       </c>
       <c r="N28">
-        <v>259.1879552</v>
+        <v>256.5990304</v>
       </c>
       <c r="O28">
-        <v>62.20510924800001</v>
+        <v>61.583767296</v>
       </c>
       <c r="P28">
-        <v>196.982845952</v>
+        <v>195.015263104</v>
       </c>
       <c r="Q28">
-        <v>346.182845952</v>
+        <v>344.215263104</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09535811144342021</v>
+        <v>0.09590839670536853</v>
       </c>
       <c r="T28">
-        <v>1.018966932092781</v>
+        <v>1.030281376263712</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.850543479552712</v>
+        <v>4.67089372105076</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08136068959491903</v>
+        <v>0.08122909672170708</v>
       </c>
       <c r="C29">
-        <v>3773.671889483815</v>
+        <v>3741.546197266534</v>
       </c>
       <c r="D29">
-        <v>5012.803889483816</v>
+        <v>5027.494197266535</v>
       </c>
       <c r="E29">
-        <v>1202.132</v>
+        <v>1248.948</v>
       </c>
       <c r="F29">
-        <v>1264.032</v>
+        <v>1310.848</v>
       </c>
       <c r="G29">
         <v>24.9</v>
@@ -3665,28 +3665,28 @@
         <v>326.5</v>
       </c>
       <c r="M29">
-        <v>69.9009696</v>
+        <v>72.4898944</v>
       </c>
       <c r="N29">
-        <v>256.5990304</v>
+        <v>254.0101056</v>
       </c>
       <c r="O29">
-        <v>61.583767296</v>
+        <v>60.962425344</v>
       </c>
       <c r="P29">
-        <v>195.015263104</v>
+        <v>193.047680256</v>
       </c>
       <c r="Q29">
-        <v>344.215263104</v>
+        <v>342.247680256</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09590839670536853</v>
+        <v>0.09647396766903762</v>
       </c>
       <c r="T29">
-        <v>1.030281376263712</v>
+        <v>1.041910110550502</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.67089372105076</v>
+        <v>4.50407608815609</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08122909672170708</v>
+        <v>0.08164850384849515</v>
       </c>
       <c r="C30">
-        <v>3741.546197266534</v>
+        <v>3648.207204137741</v>
       </c>
       <c r="D30">
-        <v>5027.494197266535</v>
+        <v>4980.971204137741</v>
       </c>
       <c r="E30">
-        <v>1248.948</v>
+        <v>1295.764</v>
       </c>
       <c r="F30">
-        <v>1310.848</v>
+        <v>1357.664</v>
       </c>
       <c r="G30">
         <v>24.9</v>
@@ -3747,45 +3747,45 @@
         <v>326.5</v>
       </c>
       <c r="M30">
-        <v>72.4898944</v>
+        <v>78.47297920000001</v>
       </c>
       <c r="N30">
-        <v>254.0101056</v>
+        <v>248.0270208</v>
       </c>
       <c r="O30">
-        <v>60.962425344</v>
+        <v>59.526484992</v>
       </c>
       <c r="P30">
-        <v>193.047680256</v>
+        <v>188.500535808</v>
       </c>
       <c r="Q30">
-        <v>342.247680256</v>
+        <v>337.700535808</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09647396766903762</v>
+        <v>0.09705547020914809</v>
       </c>
       <c r="T30">
-        <v>1.041910110550502</v>
+        <v>1.053866414817201</v>
       </c>
       <c r="U30">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V30">
         <v>0.24</v>
       </c>
       <c r="W30">
-        <v>0.042028</v>
+        <v>0.043928</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y30">
-        <v>4.50407608815609</v>
+        <v>4.160667828958887</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08164850384849515</v>
+        <v>0.0815359109752832</v>
       </c>
       <c r="C31">
-        <v>3648.207204137741</v>
+        <v>3613.795880127808</v>
       </c>
       <c r="D31">
-        <v>4980.971204137741</v>
+        <v>4993.375880127808</v>
       </c>
       <c r="E31">
-        <v>1295.764</v>
+        <v>1342.58</v>
       </c>
       <c r="F31">
-        <v>1357.664</v>
+        <v>1404.48</v>
       </c>
       <c r="G31">
         <v>24.9</v>
@@ -3829,28 +3829,28 @@
         <v>326.5</v>
       </c>
       <c r="M31">
-        <v>78.4729792</v>
+        <v>81.17894399999999</v>
       </c>
       <c r="N31">
-        <v>248.0270208</v>
+        <v>245.321056</v>
       </c>
       <c r="O31">
-        <v>59.526484992</v>
+        <v>58.87705344</v>
       </c>
       <c r="P31">
-        <v>188.500535808</v>
+        <v>186.44400256</v>
       </c>
       <c r="Q31">
-        <v>337.700535808</v>
+        <v>335.64400256</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09705547020914809</v>
+        <v>0.09765358710754744</v>
       </c>
       <c r="T31">
-        <v>1.053866414817201</v>
+        <v>1.066164327777235</v>
       </c>
       <c r="U31">
         <v>0.0578</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.160667828958888</v>
+        <v>4.021978901326926</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0815359109752832</v>
+        <v>0.08224791810207127</v>
       </c>
       <c r="C32">
-        <v>3613.795880127808</v>
+        <v>3489.559942895308</v>
       </c>
       <c r="D32">
-        <v>4993.375880127808</v>
+        <v>4915.955942895308</v>
       </c>
       <c r="E32">
-        <v>1342.58</v>
+        <v>1389.396</v>
       </c>
       <c r="F32">
-        <v>1404.48</v>
+        <v>1451.296</v>
       </c>
       <c r="G32">
         <v>24.9</v>
@@ -3911,45 +3911,45 @@
         <v>326.5</v>
       </c>
       <c r="M32">
-        <v>81.17894399999999</v>
+        <v>88.9644448</v>
       </c>
       <c r="N32">
-        <v>245.321056</v>
+        <v>237.5355552</v>
       </c>
       <c r="O32">
-        <v>58.87705344</v>
+        <v>57.008533248</v>
       </c>
       <c r="P32">
-        <v>186.44400256</v>
+        <v>180.527021952</v>
       </c>
       <c r="Q32">
-        <v>335.64400256</v>
+        <v>329.727021952</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09765358710754744</v>
+        <v>0.09826904072763952</v>
       </c>
       <c r="T32">
-        <v>1.066164327777235</v>
+        <v>1.078818701982487</v>
       </c>
       <c r="U32">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V32">
         <v>0.24</v>
       </c>
       <c r="W32">
-        <v>0.043928</v>
+        <v>0.046588</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y32">
-        <v>4.021978901326926</v>
+        <v>3.670005480661416</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08224791810207127</v>
+        <v>0.08216192522885933</v>
       </c>
       <c r="C33">
-        <v>3489.559942895308</v>
+        <v>3451.966655248163</v>
       </c>
       <c r="D33">
-        <v>4915.955942895308</v>
+        <v>4925.178655248164</v>
       </c>
       <c r="E33">
-        <v>1389.396</v>
+        <v>1436.212</v>
       </c>
       <c r="F33">
-        <v>1451.296</v>
+        <v>1498.112</v>
       </c>
       <c r="G33">
         <v>24.9</v>
@@ -3993,28 +3993,28 @@
         <v>326.5</v>
       </c>
       <c r="M33">
-        <v>88.9644448</v>
+        <v>91.83426559999999</v>
       </c>
       <c r="N33">
-        <v>237.5355552</v>
+        <v>234.6657344</v>
       </c>
       <c r="O33">
-        <v>57.008533248</v>
+        <v>56.319776256</v>
       </c>
       <c r="P33">
-        <v>180.527021952</v>
+        <v>178.345958144</v>
       </c>
       <c r="Q33">
-        <v>329.727021952</v>
+        <v>327.545958144</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09826904072763952</v>
+        <v>0.09890259592479314</v>
       </c>
       <c r="T33">
-        <v>1.078818701982487</v>
+        <v>1.091845263664364</v>
       </c>
       <c r="U33">
         <v>0.0613</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.670005480661416</v>
+        <v>3.555317809390747</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08216192522885933</v>
+        <v>0.08277817235564738</v>
       </c>
       <c r="C34">
-        <v>3451.966655248163</v>
+        <v>3339.812755848329</v>
       </c>
       <c r="D34">
-        <v>4925.178655248164</v>
+        <v>4859.84075584833</v>
       </c>
       <c r="E34">
-        <v>1436.212</v>
+        <v>1483.028</v>
       </c>
       <c r="F34">
-        <v>1498.112</v>
+        <v>1544.928</v>
       </c>
       <c r="G34">
         <v>24.9</v>
@@ -4075,45 +4075,45 @@
         <v>326.5</v>
       </c>
       <c r="M34">
-        <v>91.83426559999999</v>
+        <v>99.0298848</v>
       </c>
       <c r="N34">
-        <v>234.6657344</v>
+        <v>227.4701152</v>
       </c>
       <c r="O34">
-        <v>56.319776256</v>
+        <v>54.592827648</v>
       </c>
       <c r="P34">
-        <v>178.345958144</v>
+        <v>172.877287552</v>
       </c>
       <c r="Q34">
-        <v>327.545958144</v>
+        <v>322.077287552</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09890259592479314</v>
+        <v>0.09955506321738417</v>
       </c>
       <c r="T34">
-        <v>1.091845263664364</v>
+        <v>1.10526067793376</v>
       </c>
       <c r="U34">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V34">
         <v>0.24</v>
       </c>
       <c r="W34">
-        <v>0.046588</v>
+        <v>0.048716</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y34">
-        <v>3.555317809390747</v>
+        <v>3.296984548244168</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08277817235564738</v>
+        <v>0.08271345948243544</v>
       </c>
       <c r="C35">
-        <v>3339.812755848329</v>
+        <v>3299.776392612378</v>
       </c>
       <c r="D35">
-        <v>4859.84075584833</v>
+        <v>4866.620392612378</v>
       </c>
       <c r="E35">
-        <v>1483.028</v>
+        <v>1529.844</v>
       </c>
       <c r="F35">
-        <v>1544.928</v>
+        <v>1591.744</v>
       </c>
       <c r="G35">
         <v>24.9</v>
@@ -4157,28 +4157,28 @@
         <v>326.5</v>
       </c>
       <c r="M35">
-        <v>99.0298848</v>
+        <v>102.0307904</v>
       </c>
       <c r="N35">
-        <v>227.4701152</v>
+        <v>224.4692096</v>
       </c>
       <c r="O35">
-        <v>54.592827648</v>
+        <v>53.872610304</v>
       </c>
       <c r="P35">
-        <v>172.877287552</v>
+        <v>170.596599296</v>
       </c>
       <c r="Q35">
-        <v>322.077287552</v>
+        <v>319.796599296</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09955506321738417</v>
+        <v>0.1002273022461143</v>
       </c>
       <c r="T35">
-        <v>1.10526067793376</v>
+        <v>1.119082619908289</v>
       </c>
       <c r="U35">
         <v>0.0641</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.296984548244168</v>
+        <v>3.200014414472281</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08271345948243544</v>
+        <v>0.08264874660922351</v>
       </c>
       <c r="C36">
-        <v>3299.776392612378</v>
+        <v>3259.758971431148</v>
       </c>
       <c r="D36">
-        <v>4866.620392612378</v>
+        <v>4873.418971431149</v>
       </c>
       <c r="E36">
-        <v>1529.844</v>
+        <v>1576.66</v>
       </c>
       <c r="F36">
-        <v>1591.744</v>
+        <v>1638.56</v>
       </c>
       <c r="G36">
         <v>24.9</v>
@@ -4239,28 +4239,28 @@
         <v>326.5</v>
       </c>
       <c r="M36">
-        <v>102.0307904</v>
+        <v>105.031696</v>
       </c>
       <c r="N36">
-        <v>224.4692096</v>
+        <v>221.468304</v>
       </c>
       <c r="O36">
-        <v>53.872610304</v>
+        <v>53.15239295999999</v>
       </c>
       <c r="P36">
-        <v>170.596599296</v>
+        <v>168.31591104</v>
       </c>
       <c r="Q36">
-        <v>319.796599296</v>
+        <v>317.51591104</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1002273022461143</v>
+        <v>0.1009202255526516</v>
       </c>
       <c r="T36">
-        <v>1.119082619908289</v>
+        <v>1.133329852405111</v>
       </c>
       <c r="U36">
         <v>0.0641</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.200014414472281</v>
+        <v>3.108585431201644</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08264874660922351</v>
+        <v>0.08258403373601157</v>
       </c>
       <c r="C37">
-        <v>3259.758971431148</v>
+        <v>3219.760571800804</v>
       </c>
       <c r="D37">
-        <v>4873.418971431149</v>
+        <v>4880.236571800804</v>
       </c>
       <c r="E37">
-        <v>1576.66</v>
+        <v>1623.476</v>
       </c>
       <c r="F37">
-        <v>1638.56</v>
+        <v>1685.376</v>
       </c>
       <c r="G37">
         <v>24.9</v>
@@ -4321,28 +4321,28 @@
         <v>326.5</v>
       </c>
       <c r="M37">
-        <v>105.031696</v>
+        <v>108.0326016</v>
       </c>
       <c r="N37">
-        <v>221.468304</v>
+        <v>218.4673984</v>
       </c>
       <c r="O37">
-        <v>53.15239295999999</v>
+        <v>52.43217561599999</v>
       </c>
       <c r="P37">
-        <v>168.31591104</v>
+        <v>166.035222784</v>
       </c>
       <c r="Q37">
-        <v>317.51591104</v>
+        <v>315.235222784</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1009202255526516</v>
+        <v>0.1016348027125181</v>
       </c>
       <c r="T37">
-        <v>1.133329852405111</v>
+        <v>1.148022310917459</v>
       </c>
       <c r="U37">
         <v>0.0641</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.108585431201644</v>
+        <v>3.022235835890487</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08258403373601157</v>
+        <v>0.08471268086279965</v>
       </c>
       <c r="C38">
-        <v>3219.760571800804</v>
+        <v>2958.25386574729</v>
       </c>
       <c r="D38">
-        <v>4880.236571800804</v>
+        <v>4665.54586574729</v>
       </c>
       <c r="E38">
-        <v>1623.476</v>
+        <v>1670.292</v>
       </c>
       <c r="F38">
-        <v>1685.376</v>
+        <v>1732.192</v>
       </c>
       <c r="G38">
         <v>24.9</v>
@@ -4403,45 +4403,45 @@
         <v>326.5</v>
       </c>
       <c r="M38">
-        <v>108.0326016</v>
+        <v>124.5446048</v>
       </c>
       <c r="N38">
-        <v>218.4673984</v>
+        <v>201.9553952</v>
       </c>
       <c r="O38">
-        <v>52.432175616</v>
+        <v>48.469294848</v>
       </c>
       <c r="P38">
-        <v>166.035222784</v>
+        <v>153.486100352</v>
       </c>
       <c r="Q38">
-        <v>315.235222784</v>
+        <v>302.686100352</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1016348027125181</v>
+        <v>0.1023720648615867</v>
       </c>
       <c r="T38">
-        <v>1.148022310917459</v>
+        <v>1.163181196684167</v>
       </c>
       <c r="U38">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V38">
         <v>0.24</v>
       </c>
       <c r="W38">
-        <v>0.048716</v>
+        <v>0.05464400000000001</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y38">
-        <v>3.022235835890488</v>
+        <v>2.621550732962782</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08471268086279965</v>
+        <v>0.08470724798958769</v>
       </c>
       <c r="C39">
-        <v>2958.25386574729</v>
+        <v>2911.961767069156</v>
       </c>
       <c r="D39">
-        <v>4665.54586574729</v>
+        <v>4666.069767069156</v>
       </c>
       <c r="E39">
-        <v>1670.292</v>
+        <v>1717.108</v>
       </c>
       <c r="F39">
-        <v>1732.192</v>
+        <v>1779.008</v>
       </c>
       <c r="G39">
         <v>24.9</v>
@@ -4485,28 +4485,28 @@
         <v>326.5</v>
       </c>
       <c r="M39">
-        <v>124.5446048</v>
+        <v>127.9106752</v>
       </c>
       <c r="N39">
-        <v>201.9553952</v>
+        <v>198.5893248</v>
       </c>
       <c r="O39">
-        <v>48.469294848</v>
+        <v>47.66143795199999</v>
       </c>
       <c r="P39">
-        <v>153.486100352</v>
+        <v>150.927886848</v>
       </c>
       <c r="Q39">
-        <v>302.686100352</v>
+        <v>300.127886848</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1023720648615867</v>
+        <v>0.1031331096606253</v>
       </c>
       <c r="T39">
-        <v>1.163181196684167</v>
+        <v>1.17882907876593</v>
       </c>
       <c r="U39">
         <v>0.07190000000000001</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.621550732962782</v>
+        <v>2.55256255577955</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08470724798958769</v>
+        <v>0.08585777511637577</v>
       </c>
       <c r="C40">
-        <v>2911.961767069156</v>
+        <v>2756.763344707381</v>
       </c>
       <c r="D40">
-        <v>4666.069767069156</v>
+        <v>4557.687344707381</v>
       </c>
       <c r="E40">
-        <v>1717.108</v>
+        <v>1763.924</v>
       </c>
       <c r="F40">
-        <v>1779.008</v>
+        <v>1825.824</v>
       </c>
       <c r="G40">
         <v>24.9</v>
@@ -4567,45 +4567,45 @@
         <v>326.5</v>
       </c>
       <c r="M40">
-        <v>127.9106752</v>
+        <v>138.3974592</v>
       </c>
       <c r="N40">
-        <v>198.5893248</v>
+        <v>188.1025408</v>
       </c>
       <c r="O40">
-        <v>47.66143795199999</v>
+        <v>45.144609792</v>
       </c>
       <c r="P40">
-        <v>150.927886848</v>
+        <v>142.957931008</v>
       </c>
       <c r="Q40">
-        <v>300.127886848</v>
+        <v>292.157931008</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1031331096606253</v>
+        <v>0.103919106748157</v>
       </c>
       <c r="T40">
-        <v>1.17882907876593</v>
+        <v>1.19499000616185</v>
       </c>
       <c r="U40">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V40">
         <v>0.24</v>
       </c>
       <c r="W40">
-        <v>0.05464400000000001</v>
+        <v>0.05760800000000001</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y40">
-        <v>2.55256255577955</v>
+        <v>2.359147356369965</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08585777511637577</v>
+        <v>0.08588198224316382</v>
       </c>
       <c r="C41">
-        <v>2756.763344707381</v>
+        <v>2707.721031087383</v>
       </c>
       <c r="D41">
-        <v>4557.687344707381</v>
+        <v>4555.461031087383</v>
       </c>
       <c r="E41">
-        <v>1763.924</v>
+        <v>1810.74</v>
       </c>
       <c r="F41">
-        <v>1825.824</v>
+        <v>1872.64</v>
       </c>
       <c r="G41">
         <v>24.9</v>
@@ -4649,28 +4649,28 @@
         <v>326.5</v>
       </c>
       <c r="M41">
-        <v>138.3974592</v>
+        <v>141.946112</v>
       </c>
       <c r="N41">
-        <v>188.1025408</v>
+        <v>184.553888</v>
       </c>
       <c r="O41">
-        <v>45.144609792</v>
+        <v>44.29293312</v>
       </c>
       <c r="P41">
-        <v>142.957931008</v>
+        <v>140.26095488</v>
       </c>
       <c r="Q41">
-        <v>292.157931008</v>
+        <v>289.46095488</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.103919106748157</v>
+        <v>0.1047313037386064</v>
       </c>
       <c r="T41">
-        <v>1.19499000616185</v>
+        <v>1.211689631137634</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.359147356369965</v>
+        <v>2.300168672460715</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08588198224316382</v>
+        <v>0.08590618936995187</v>
       </c>
       <c r="C42">
-        <v>2707.721031087383</v>
+        <v>2658.680891399922</v>
       </c>
       <c r="D42">
-        <v>4555.461031087383</v>
+        <v>4553.236891399923</v>
       </c>
       <c r="E42">
-        <v>1810.74</v>
+        <v>1857.556</v>
       </c>
       <c r="F42">
-        <v>1872.64</v>
+        <v>1919.456</v>
       </c>
       <c r="G42">
         <v>24.9</v>
@@ -4731,28 +4731,28 @@
         <v>326.5</v>
       </c>
       <c r="M42">
-        <v>141.946112</v>
+        <v>145.4947648</v>
       </c>
       <c r="N42">
-        <v>184.553888</v>
+        <v>181.0052352</v>
       </c>
       <c r="O42">
-        <v>44.29293312</v>
+        <v>43.441256448</v>
       </c>
       <c r="P42">
-        <v>140.26095488</v>
+        <v>137.563978752</v>
       </c>
       <c r="Q42">
-        <v>289.46095488</v>
+        <v>286.763978752</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1047313037386064</v>
+        <v>0.1055710328304269</v>
       </c>
       <c r="T42">
-        <v>1.211689631137634</v>
+        <v>1.228955345095647</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.300168672460715</v>
+        <v>2.244066997522649</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08590618936995187</v>
+        <v>0.08593039649673995</v>
       </c>
       <c r="C43">
-        <v>2658.680891399922</v>
+        <v>2609.642922462374</v>
       </c>
       <c r="D43">
-        <v>4553.236891399923</v>
+        <v>4551.014922462375</v>
       </c>
       <c r="E43">
-        <v>1857.556</v>
+        <v>1904.372</v>
       </c>
       <c r="F43">
-        <v>1919.456</v>
+        <v>1966.272</v>
       </c>
       <c r="G43">
         <v>24.9</v>
@@ -4813,28 +4813,28 @@
         <v>326.5</v>
       </c>
       <c r="M43">
-        <v>145.4947648</v>
+        <v>149.0434176</v>
       </c>
       <c r="N43">
-        <v>181.0052352</v>
+        <v>177.4565824</v>
       </c>
       <c r="O43">
-        <v>43.441256448</v>
+        <v>42.589579776</v>
       </c>
       <c r="P43">
-        <v>137.563978752</v>
+        <v>134.867002624</v>
       </c>
       <c r="Q43">
-        <v>286.763978752</v>
+        <v>284.067002624</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1055710328304269</v>
+        <v>0.1064397180978275</v>
       </c>
       <c r="T43">
-        <v>1.228955345095647</v>
+        <v>1.246816428500488</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.244066997522649</v>
+        <v>2.190636830914967</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08593039649673995</v>
+        <v>0.085954603623528</v>
       </c>
       <c r="C44">
-        <v>2609.642922462374</v>
+        <v>2560.607121098332</v>
       </c>
       <c r="D44">
-        <v>4551.014922462375</v>
+        <v>4548.795121098332</v>
       </c>
       <c r="E44">
-        <v>1904.372</v>
+        <v>1951.188</v>
       </c>
       <c r="F44">
-        <v>1966.272</v>
+        <v>2013.088</v>
       </c>
       <c r="G44">
         <v>24.9</v>
@@ -4895,28 +4895,28 @@
         <v>326.5</v>
       </c>
       <c r="M44">
-        <v>149.0434176</v>
+        <v>152.5920704</v>
       </c>
       <c r="N44">
-        <v>177.4565824</v>
+        <v>173.9079296</v>
       </c>
       <c r="O44">
-        <v>42.589579776</v>
+        <v>41.737903104</v>
       </c>
       <c r="P44">
-        <v>134.867002624</v>
+        <v>132.170026496</v>
       </c>
       <c r="Q44">
-        <v>284.067002624</v>
+        <v>281.370026496</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1064397180978275</v>
+        <v>0.1073388835500491</v>
       </c>
       <c r="T44">
-        <v>1.246816428500488</v>
+        <v>1.265304216586201</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.190636830914967</v>
+        <v>2.139691788335549</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.085954603623528</v>
+        <v>0.08597881075031606</v>
       </c>
       <c r="C45">
-        <v>2560.607121098332</v>
+        <v>2511.573484137572</v>
       </c>
       <c r="D45">
-        <v>4548.795121098332</v>
+        <v>4546.577484137572</v>
       </c>
       <c r="E45">
-        <v>1951.188</v>
+        <v>1998.004</v>
       </c>
       <c r="F45">
-        <v>2013.088</v>
+        <v>2059.904</v>
       </c>
       <c r="G45">
         <v>24.9</v>
@@ -4977,28 +4977,28 @@
         <v>326.5</v>
       </c>
       <c r="M45">
-        <v>152.5920704</v>
+        <v>156.1407232</v>
       </c>
       <c r="N45">
-        <v>173.9079296</v>
+        <v>170.3592768</v>
       </c>
       <c r="O45">
-        <v>41.737903104</v>
+        <v>40.88622643199999</v>
       </c>
       <c r="P45">
-        <v>132.170026496</v>
+        <v>129.473050368</v>
       </c>
       <c r="Q45">
-        <v>281.370026496</v>
+        <v>278.673050368</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1073388835500491</v>
+        <v>0.1082701620541358</v>
       </c>
       <c r="T45">
-        <v>1.265304216586201</v>
+        <v>1.284452282817832</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.139691788335549</v>
+        <v>2.091062429509741</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08597881075031606</v>
+        <v>0.08600301787710413</v>
       </c>
       <c r="C46">
-        <v>2511.573484137572</v>
+        <v>2462.542008416059</v>
       </c>
       <c r="D46">
-        <v>4546.577484137572</v>
+        <v>4544.362008416059</v>
       </c>
       <c r="E46">
-        <v>1998.004</v>
+        <v>2044.82</v>
       </c>
       <c r="F46">
-        <v>2059.904</v>
+        <v>2106.72</v>
       </c>
       <c r="G46">
         <v>24.9</v>
@@ -5059,28 +5059,28 @@
         <v>326.5</v>
       </c>
       <c r="M46">
-        <v>156.1407232</v>
+        <v>159.689376</v>
       </c>
       <c r="N46">
-        <v>170.3592768</v>
+        <v>166.810624</v>
       </c>
       <c r="O46">
-        <v>40.88622643199999</v>
+        <v>40.03454976</v>
       </c>
       <c r="P46">
-        <v>129.473050368</v>
+        <v>126.77607424</v>
       </c>
       <c r="Q46">
-        <v>278.673050368</v>
+        <v>275.97607424</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1082701620541358</v>
+        <v>0.1092353052310984</v>
       </c>
       <c r="T46">
-        <v>1.284452282817832</v>
+        <v>1.304296642366978</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.091062429509741</v>
+        <v>2.044594375520636</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08600301787710413</v>
+        <v>0.08602722500389218</v>
       </c>
       <c r="C47">
-        <v>2462.542008416059</v>
+        <v>2413.512690775917</v>
       </c>
       <c r="D47">
-        <v>4544.362008416059</v>
+        <v>4542.148690775917</v>
       </c>
       <c r="E47">
-        <v>2044.82</v>
+        <v>2091.636</v>
       </c>
       <c r="F47">
-        <v>2106.72</v>
+        <v>2153.536</v>
       </c>
       <c r="G47">
         <v>24.9</v>
@@ -5141,28 +5141,28 @@
         <v>326.5</v>
       </c>
       <c r="M47">
-        <v>159.689376</v>
+        <v>163.2380288</v>
       </c>
       <c r="N47">
-        <v>166.810624</v>
+        <v>163.2619712</v>
       </c>
       <c r="O47">
-        <v>40.03454976</v>
+        <v>39.18287308799999</v>
       </c>
       <c r="P47">
-        <v>126.77607424</v>
+        <v>124.079098112</v>
       </c>
       <c r="Q47">
-        <v>275.97607424</v>
+        <v>273.279098112</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1092353052310984</v>
+        <v>0.1102361944516522</v>
       </c>
       <c r="T47">
-        <v>1.304296642366978</v>
+        <v>1.324875978195721</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.044594375520636</v>
+        <v>2.000146671704969</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08602722500389218</v>
+        <v>0.09112367213068023</v>
       </c>
       <c r="C48">
-        <v>2413.512690775917</v>
+        <v>1944.259710869299</v>
       </c>
       <c r="D48">
-        <v>4542.148690775917</v>
+        <v>4119.711710869299</v>
       </c>
       <c r="E48">
-        <v>2091.636</v>
+        <v>2138.452</v>
       </c>
       <c r="F48">
-        <v>2153.536</v>
+        <v>2200.352</v>
       </c>
       <c r="G48">
         <v>24.9</v>
@@ -5223,45 +5223,45 @@
         <v>326.5</v>
       </c>
       <c r="M48">
-        <v>163.2380288</v>
+        <v>198.03168</v>
       </c>
       <c r="N48">
-        <v>163.2619712</v>
+        <v>128.46832</v>
       </c>
       <c r="O48">
-        <v>39.18287308799999</v>
+        <v>30.8323968</v>
       </c>
       <c r="P48">
-        <v>124.079098112</v>
+        <v>97.63592320000001</v>
       </c>
       <c r="Q48">
-        <v>273.279098112</v>
+        <v>246.8359232</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1102361944516522</v>
+        <v>0.1112748530767552</v>
       </c>
       <c r="T48">
-        <v>1.324875978195721</v>
+        <v>1.346231892734983</v>
       </c>
       <c r="U48">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V48">
         <v>0.24</v>
       </c>
       <c r="W48">
-        <v>0.05760800000000001</v>
+        <v>0.0684</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y48">
-        <v>2.000146671704969</v>
+        <v>1.648726102813449</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09112367213068023</v>
+        <v>0.09125579925746832</v>
       </c>
       <c r="C49">
-        <v>1944.259710869299</v>
+        <v>1887.534342220321</v>
       </c>
       <c r="D49">
-        <v>4119.711710869299</v>
+        <v>4109.802342220321</v>
       </c>
       <c r="E49">
-        <v>2138.452</v>
+        <v>2185.268</v>
       </c>
       <c r="F49">
-        <v>2200.352</v>
+        <v>2247.168</v>
       </c>
       <c r="G49">
         <v>24.9</v>
@@ -5305,28 +5305,28 @@
         <v>326.5</v>
       </c>
       <c r="M49">
-        <v>198.03168</v>
+        <v>202.24512</v>
       </c>
       <c r="N49">
-        <v>128.46832</v>
+        <v>124.25488</v>
       </c>
       <c r="O49">
-        <v>30.8323968</v>
+        <v>29.82117119999999</v>
       </c>
       <c r="P49">
-        <v>97.63592320000001</v>
+        <v>94.43370879999999</v>
       </c>
       <c r="Q49">
-        <v>246.8359232</v>
+        <v>243.6337088</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1112748530767552</v>
+        <v>0.112353460110516</v>
       </c>
       <c r="T49">
-        <v>1.346231892734983</v>
+        <v>1.368409188602678</v>
       </c>
       <c r="U49">
         <v>0.09</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>1.648726102813449</v>
+        <v>1.614377642338169</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09125579925746831</v>
+        <v>0.09138792638425636</v>
       </c>
       <c r="C50">
-        <v>1887.534342220322</v>
+        <v>1830.856530276978</v>
       </c>
       <c r="D50">
-        <v>4109.802342220322</v>
+        <v>4099.940530276978</v>
       </c>
       <c r="E50">
-        <v>2185.268</v>
+        <v>2232.083999999999</v>
       </c>
       <c r="F50">
-        <v>2247.168</v>
+        <v>2293.983999999999</v>
       </c>
       <c r="G50">
         <v>24.9</v>
@@ -5387,28 +5387,28 @@
         <v>326.5</v>
       </c>
       <c r="M50">
-        <v>202.24512</v>
+        <v>206.4585599999999</v>
       </c>
       <c r="N50">
-        <v>124.25488</v>
+        <v>120.0414400000001</v>
       </c>
       <c r="O50">
-        <v>29.82117120000001</v>
+        <v>28.80994560000001</v>
       </c>
       <c r="P50">
-        <v>94.43370880000003</v>
+        <v>91.23149440000005</v>
       </c>
       <c r="Q50">
-        <v>243.6337088</v>
+        <v>240.4314944</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.112353460110516</v>
+        <v>0.1134743654593262</v>
       </c>
       <c r="T50">
-        <v>1.368409188602678</v>
+        <v>1.391456182347537</v>
       </c>
       <c r="U50">
         <v>0.09</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.614377642338169</v>
+        <v>1.581431159841472</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09138792638425636</v>
+        <v>0.09152005351104442</v>
       </c>
       <c r="C51">
-        <v>1830.856530276978</v>
+        <v>1774.22593351</v>
       </c>
       <c r="D51">
-        <v>4099.940530276978</v>
+        <v>4090.12593351</v>
       </c>
       <c r="E51">
-        <v>2232.083999999999</v>
+        <v>2278.9</v>
       </c>
       <c r="F51">
-        <v>2293.983999999999</v>
+        <v>2340.8</v>
       </c>
       <c r="G51">
         <v>24.9</v>
@@ -5469,28 +5469,28 @@
         <v>326.5</v>
       </c>
       <c r="M51">
-        <v>206.4585599999999</v>
+        <v>210.672</v>
       </c>
       <c r="N51">
-        <v>120.0414400000001</v>
+        <v>115.828</v>
       </c>
       <c r="O51">
-        <v>28.80994560000001</v>
+        <v>27.79872000000001</v>
       </c>
       <c r="P51">
-        <v>91.23149440000005</v>
+        <v>88.02928000000003</v>
       </c>
       <c r="Q51">
-        <v>240.4314944</v>
+        <v>237.22928</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1134743654593262</v>
+        <v>0.1146401070220888</v>
       </c>
       <c r="T51">
-        <v>1.391456182347537</v>
+        <v>1.415425055842191</v>
       </c>
       <c r="U51">
         <v>0.09</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.581431159841472</v>
+        <v>1.549802536644642</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09152005351104442</v>
+        <v>0.09165218063783248</v>
       </c>
       <c r="C52">
-        <v>1774.22593351</v>
+        <v>1717.642213652581</v>
       </c>
       <c r="D52">
-        <v>4090.12593351</v>
+        <v>4080.358213652581</v>
       </c>
       <c r="E52">
-        <v>2278.9</v>
+        <v>2325.716</v>
       </c>
       <c r="F52">
-        <v>2340.8</v>
+        <v>2387.616</v>
       </c>
       <c r="G52">
         <v>24.9</v>
@@ -5551,28 +5551,28 @@
         <v>326.5</v>
       </c>
       <c r="M52">
-        <v>210.672</v>
+        <v>214.88544</v>
       </c>
       <c r="N52">
-        <v>115.828</v>
+        <v>111.61456</v>
       </c>
       <c r="O52">
-        <v>27.79872000000001</v>
+        <v>26.7874944</v>
       </c>
       <c r="P52">
-        <v>88.02928000000003</v>
+        <v>84.82706560000001</v>
       </c>
       <c r="Q52">
-        <v>237.22928</v>
+        <v>234.0270656</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1146401070220888</v>
+        <v>0.1158534298731275</v>
       </c>
       <c r="T52">
-        <v>1.415425055842191</v>
+        <v>1.440372250703974</v>
       </c>
       <c r="U52">
         <v>0.09</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.549802536644642</v>
+        <v>1.519414251612394</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09165218063783248</v>
+        <v>0.1162361575918402</v>
       </c>
       <c r="C53">
-        <v>1717.642213652581</v>
+        <v>415.5331437038758</v>
       </c>
       <c r="D53">
-        <v>4080.358213652581</v>
+        <v>2825.065143703875</v>
       </c>
       <c r="E53">
-        <v>2325.716</v>
+        <v>2372.532</v>
       </c>
       <c r="F53">
-        <v>2387.616</v>
+        <v>2434.432</v>
       </c>
       <c r="G53">
         <v>24.9</v>
@@ -5633,45 +5633,45 @@
         <v>326.5</v>
       </c>
       <c r="M53">
-        <v>214.88544</v>
+        <v>357.3746176</v>
       </c>
       <c r="N53">
-        <v>111.61456</v>
+        <v>-30.87461760000002</v>
       </c>
       <c r="O53">
-        <v>26.7874944</v>
+        <v>-7.409908224000005</v>
       </c>
       <c r="P53">
-        <v>84.82706560000001</v>
+        <v>-23.46470937600002</v>
       </c>
       <c r="Q53">
-        <v>234.0270656</v>
+        <v>125.735290624</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1158534298731275</v>
+        <v>0.1179958853908382</v>
       </c>
       <c r="T53">
-        <v>1.440372250703974</v>
+        <v>1.48442339112161</v>
       </c>
       <c r="U53">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.24</v>
+        <v>0.2192657120593446</v>
       </c>
       <c r="W53">
-        <v>0.0684</v>
+        <v>0.1146117934696882</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y53">
-        <v>1.519414251612394</v>
+        <v>0.9136071335806026</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1162361575918402</v>
+        <v>0.1172461575918402</v>
       </c>
       <c r="C54">
-        <v>415.5331437038758</v>
+        <v>333.4565314575584</v>
       </c>
       <c r="D54">
-        <v>2825.065143703875</v>
+        <v>2789.804531457558</v>
       </c>
       <c r="E54">
-        <v>2372.532</v>
+        <v>2419.348</v>
       </c>
       <c r="F54">
-        <v>2434.432</v>
+        <v>2481.248</v>
       </c>
       <c r="G54">
         <v>24.9</v>
@@ -5715,37 +5715,37 @@
         <v>326.5</v>
       </c>
       <c r="M54">
-        <v>357.3746176</v>
+        <v>364.2472064</v>
       </c>
       <c r="N54">
-        <v>-30.87461760000002</v>
+        <v>-37.74720640000004</v>
       </c>
       <c r="O54">
-        <v>-7.409908224000005</v>
+        <v>-9.059329536000009</v>
       </c>
       <c r="P54">
-        <v>-23.46470937600002</v>
+        <v>-28.68787686400003</v>
       </c>
       <c r="Q54">
-        <v>125.735290624</v>
+        <v>120.512123136</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1179958853908382</v>
+        <v>0.1195319680587284</v>
       </c>
       <c r="T54">
-        <v>1.48442339112161</v>
+        <v>1.516006867528452</v>
       </c>
       <c r="U54">
         <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.2192657120593446</v>
+        <v>0.2151286231525645</v>
       </c>
       <c r="W54">
-        <v>0.1146117934696882</v>
+        <v>0.1152191181212035</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.9136071335806026</v>
+        <v>0.8963692631356855</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1172461575918402</v>
+        <v>0.1182561575918402</v>
       </c>
       <c r="C55">
-        <v>333.4565314575584</v>
+        <v>252.2492682868829</v>
       </c>
       <c r="D55">
-        <v>2789.804531457558</v>
+        <v>2755.413268286883</v>
       </c>
       <c r="E55">
-        <v>2419.348</v>
+        <v>2466.164</v>
       </c>
       <c r="F55">
-        <v>2481.248</v>
+        <v>2528.064</v>
       </c>
       <c r="G55">
         <v>24.9</v>
@@ -5797,37 +5797,37 @@
         <v>326.5</v>
       </c>
       <c r="M55">
-        <v>364.2472064</v>
+        <v>371.1197952</v>
       </c>
       <c r="N55">
-        <v>-37.74720640000004</v>
+        <v>-44.6197952</v>
       </c>
       <c r="O55">
-        <v>-9.059329536000009</v>
+        <v>-10.708750848</v>
       </c>
       <c r="P55">
-        <v>-28.68787686400003</v>
+        <v>-33.911044352</v>
       </c>
       <c r="Q55">
-        <v>120.512123136</v>
+        <v>115.288955648</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1195319680587284</v>
+        <v>0.1211348369295703</v>
       </c>
       <c r="T55">
-        <v>1.516006867528452</v>
+        <v>1.54896353856168</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.2151286231525645</v>
+        <v>0.2111447597608504</v>
       </c>
       <c r="W55">
-        <v>0.1152191181212035</v>
+        <v>0.1158039492671072</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.8963692631356855</v>
+        <v>0.8797698323368767</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1182561575918402</v>
+        <v>0.1192661575918403</v>
       </c>
       <c r="C56">
-        <v>252.2492682868829</v>
+        <v>171.879595048692</v>
       </c>
       <c r="D56">
-        <v>2755.413268286883</v>
+        <v>2721.859595048692</v>
       </c>
       <c r="E56">
-        <v>2466.164</v>
+        <v>2512.98</v>
       </c>
       <c r="F56">
-        <v>2528.064</v>
+        <v>2574.88</v>
       </c>
       <c r="G56">
         <v>24.9</v>
@@ -5879,37 +5879,37 @@
         <v>326.5</v>
       </c>
       <c r="M56">
-        <v>371.1197952</v>
+        <v>377.9923840000001</v>
       </c>
       <c r="N56">
-        <v>-44.6197952</v>
+        <v>-51.49238400000007</v>
       </c>
       <c r="O56">
-        <v>-10.708750848</v>
+        <v>-12.35817216000002</v>
       </c>
       <c r="P56">
-        <v>-33.911044352</v>
+        <v>-39.13421184000006</v>
       </c>
       <c r="Q56">
-        <v>115.288955648</v>
+        <v>110.0657881599999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1211348369295703</v>
+        <v>0.1228089444168942</v>
       </c>
       <c r="T56">
-        <v>1.54896353856168</v>
+        <v>1.583384950529717</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.2111447597608504</v>
+        <v>0.2073057641288349</v>
       </c>
       <c r="W56">
-        <v>0.1158039492671072</v>
+        <v>0.1163675138258871</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8797698323368767</v>
+        <v>0.8637740172034787</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1192661575918403</v>
+        <v>0.1202761575918402</v>
       </c>
       <c r="C57">
-        <v>171.879595048692</v>
+        <v>92.31728095916242</v>
       </c>
       <c r="D57">
-        <v>2721.859595048692</v>
+        <v>2689.113280959162</v>
       </c>
       <c r="E57">
-        <v>2512.98</v>
+        <v>2559.796</v>
       </c>
       <c r="F57">
-        <v>2574.88</v>
+        <v>2621.696</v>
       </c>
       <c r="G57">
         <v>24.9</v>
@@ -5961,37 +5961,37 @@
         <v>326.5</v>
       </c>
       <c r="M57">
-        <v>377.9923840000001</v>
+        <v>384.8649728</v>
       </c>
       <c r="N57">
-        <v>-51.49238400000007</v>
+        <v>-58.36497280000003</v>
       </c>
       <c r="O57">
-        <v>-12.35817216000002</v>
+        <v>-14.00759347200001</v>
       </c>
       <c r="P57">
-        <v>-39.13421184000006</v>
+        <v>-44.35737932800002</v>
       </c>
       <c r="Q57">
-        <v>110.0657881599999</v>
+        <v>104.842620672</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1228089444168942</v>
+        <v>0.1245591476990963</v>
       </c>
       <c r="T57">
-        <v>1.583384950529717</v>
+        <v>1.619370972132665</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.2073057641288349</v>
+        <v>0.2036038754836771</v>
       </c>
       <c r="W57">
-        <v>0.1163675138258871</v>
+        <v>0.1169109510789962</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8637740172034787</v>
+        <v>0.8483494811819882</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1202761575918402</v>
+        <v>0.1212861575918402</v>
       </c>
       <c r="C58">
-        <v>92.31728095916242</v>
+        <v>13.53353274934079</v>
       </c>
       <c r="D58">
-        <v>2689.113280959162</v>
+        <v>2657.145532749341</v>
       </c>
       <c r="E58">
-        <v>2559.796</v>
+        <v>2606.612</v>
       </c>
       <c r="F58">
-        <v>2621.696</v>
+        <v>2668.512</v>
       </c>
       <c r="G58">
         <v>24.9</v>
@@ -6043,37 +6043,37 @@
         <v>326.5</v>
       </c>
       <c r="M58">
-        <v>384.8649728</v>
+        <v>391.7375616</v>
       </c>
       <c r="N58">
-        <v>-58.36497280000003</v>
+        <v>-65.23756160000005</v>
       </c>
       <c r="O58">
-        <v>-14.00759347200001</v>
+        <v>-15.65701478400001</v>
       </c>
       <c r="P58">
-        <v>-44.35737932800002</v>
+        <v>-49.58054681600004</v>
       </c>
       <c r="Q58">
-        <v>104.842620672</v>
+        <v>99.61945318399995</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1245591476990963</v>
+        <v>0.1263907557851218</v>
       </c>
       <c r="T58">
-        <v>1.619370972132665</v>
+        <v>1.657030762182262</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.2036038754836771</v>
+        <v>0.200031877668174</v>
       </c>
       <c r="W58">
-        <v>0.1169109510789962</v>
+        <v>0.1174353203583121</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8483494811819882</v>
+        <v>0.8334661569507251</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1212861575918402</v>
+        <v>0.1222961575918402</v>
       </c>
       <c r="C59">
-        <v>13.53353274934079</v>
+        <v>-64.49908977575888</v>
       </c>
       <c r="D59">
-        <v>2657.145532749341</v>
+        <v>2625.928910224241</v>
       </c>
       <c r="E59">
-        <v>2606.612</v>
+        <v>2653.428</v>
       </c>
       <c r="F59">
-        <v>2668.512</v>
+        <v>2715.328</v>
       </c>
       <c r="G59">
         <v>24.9</v>
@@ -6125,37 +6125,37 @@
         <v>326.5</v>
       </c>
       <c r="M59">
-        <v>391.7375616</v>
+        <v>398.6101504</v>
       </c>
       <c r="N59">
-        <v>-65.23756160000005</v>
+        <v>-72.11015040000001</v>
       </c>
       <c r="O59">
-        <v>-15.65701478400001</v>
+        <v>-17.306436096</v>
       </c>
       <c r="P59">
-        <v>-49.58054681600004</v>
+        <v>-54.80371430400001</v>
       </c>
       <c r="Q59">
-        <v>99.61945318399995</v>
+        <v>94.39628569599998</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1263907557851218</v>
+        <v>0.1283095833038151</v>
       </c>
       <c r="T59">
-        <v>1.657030762182262</v>
+        <v>1.696483875567554</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.200031877668174</v>
+        <v>0.1965830521911366</v>
       </c>
       <c r="W59">
-        <v>0.1174353203583121</v>
+        <v>0.1179416079383412</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8334661569507251</v>
+        <v>0.8190960507964024</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1222961575918402</v>
+        <v>0.1233061575918402</v>
       </c>
       <c r="C60">
-        <v>-64.49908977575842</v>
+        <v>-141.8067522950337</v>
       </c>
       <c r="D60">
-        <v>2625.928910224241</v>
+        <v>2595.437247704966</v>
       </c>
       <c r="E60">
-        <v>2653.427999999999</v>
+        <v>2700.243999999999</v>
       </c>
       <c r="F60">
-        <v>2715.328</v>
+        <v>2762.143999999999</v>
       </c>
       <c r="G60">
         <v>24.9</v>
@@ -6207,37 +6207,37 @@
         <v>326.5</v>
       </c>
       <c r="M60">
-        <v>398.6101504</v>
+        <v>405.4827391999999</v>
       </c>
       <c r="N60">
-        <v>-72.11015039999995</v>
+        <v>-78.98273919999991</v>
       </c>
       <c r="O60">
-        <v>-17.30643609599999</v>
+        <v>-18.95585740799998</v>
       </c>
       <c r="P60">
-        <v>-54.80371430399997</v>
+        <v>-60.02688179199993</v>
       </c>
       <c r="Q60">
-        <v>94.39628569600002</v>
+        <v>89.17311820800006</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1283095833038151</v>
+        <v>0.1303220121648838</v>
       </c>
       <c r="T60">
-        <v>1.696483875567554</v>
+        <v>1.737861531069201</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.1965830521911366</v>
+        <v>0.1932511360523038</v>
       </c>
       <c r="W60">
-        <v>0.1179416079383412</v>
+        <v>0.1184307332275218</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8190960507964025</v>
+        <v>0.8052130668845991</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1233061575918402</v>
+        <v>0.1579154718245997</v>
       </c>
       <c r="C61">
-        <v>-141.8067522950337</v>
+        <v>-927.3861630436732</v>
       </c>
       <c r="D61">
-        <v>2595.437247704966</v>
+        <v>1856.673836956326</v>
       </c>
       <c r="E61">
-        <v>2700.243999999999</v>
+        <v>2747.059999999999</v>
       </c>
       <c r="F61">
-        <v>2762.143999999999</v>
+        <v>2808.96</v>
       </c>
       <c r="G61">
         <v>24.9</v>
@@ -6289,45 +6289,45 @@
         <v>326.5</v>
       </c>
       <c r="M61">
-        <v>405.4827391999999</v>
+        <v>564.0391679999999</v>
       </c>
       <c r="N61">
-        <v>-78.98273919999991</v>
+        <v>-237.5391679999999</v>
       </c>
       <c r="O61">
-        <v>-18.95585740799998</v>
+        <v>-57.00940031999998</v>
       </c>
       <c r="P61">
-        <v>-60.02688179199993</v>
+        <v>-180.5297676799999</v>
       </c>
       <c r="Q61">
-        <v>89.17311820800006</v>
+        <v>-31.32976767999995</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1303220121648838</v>
+        <v>0.1354333480509047</v>
       </c>
       <c r="T61">
-        <v>1.737861531069201</v>
+        <v>1.842955976660023</v>
       </c>
       <c r="U61">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.1932511360523038</v>
+        <v>0.1389265222091811</v>
       </c>
       <c r="W61">
-        <v>0.1184307332275218</v>
+        <v>0.1729035543403964</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y61">
-        <v>0.8052130668845991</v>
+        <v>0.578860509204921</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1579154718245997</v>
+        <v>0.1594654718245997</v>
       </c>
       <c r="C62">
-        <v>-927.3861630436732</v>
+        <v>-997.5726563359256</v>
       </c>
       <c r="D62">
-        <v>1856.673836956326</v>
+        <v>1833.303343664074</v>
       </c>
       <c r="E62">
-        <v>2747.059999999999</v>
+        <v>2793.875999999999</v>
       </c>
       <c r="F62">
-        <v>2808.96</v>
+        <v>2855.775999999999</v>
       </c>
       <c r="G62">
         <v>24.9</v>
@@ -6371,37 +6371,37 @@
         <v>326.5</v>
       </c>
       <c r="M62">
-        <v>564.0391679999999</v>
+        <v>573.4398207999999</v>
       </c>
       <c r="N62">
-        <v>-237.5391679999999</v>
+        <v>-246.9398207999999</v>
       </c>
       <c r="O62">
-        <v>-57.00940031999998</v>
+        <v>-59.26555699199997</v>
       </c>
       <c r="P62">
-        <v>-180.5297676799999</v>
+        <v>-187.6742638079999</v>
       </c>
       <c r="Q62">
-        <v>-31.32976767999995</v>
+        <v>-38.47426380799993</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1354333480509047</v>
+        <v>0.1377316390265688</v>
       </c>
       <c r="T62">
-        <v>1.842955976660023</v>
+        <v>1.890211258112844</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.1389265222091811</v>
+        <v>0.1366490382385388</v>
       </c>
       <c r="W62">
-        <v>0.1729035543403964</v>
+        <v>0.1733608731217014</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.578860509204921</v>
+        <v>0.5693709926605781</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1594654718245997</v>
+        <v>0.1610154718245997</v>
       </c>
       <c r="C63">
-        <v>-997.5726563359256</v>
+        <v>-1067.178120821639</v>
       </c>
       <c r="D63">
-        <v>1833.303343664074</v>
+        <v>1810.513879178361</v>
       </c>
       <c r="E63">
-        <v>2793.875999999999</v>
+        <v>2840.692</v>
       </c>
       <c r="F63">
-        <v>2855.775999999999</v>
+        <v>2902.592</v>
       </c>
       <c r="G63">
         <v>24.9</v>
@@ -6453,37 +6453,37 @@
         <v>326.5</v>
       </c>
       <c r="M63">
-        <v>573.4398207999999</v>
+        <v>582.8404736</v>
       </c>
       <c r="N63">
-        <v>-246.9398207999999</v>
+        <v>-256.3404736</v>
       </c>
       <c r="O63">
-        <v>-59.26555699199997</v>
+        <v>-61.521713664</v>
       </c>
       <c r="P63">
-        <v>-187.6742638079999</v>
+        <v>-194.818759936</v>
       </c>
       <c r="Q63">
-        <v>-38.47426380799993</v>
+        <v>-45.618759936</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1377316390265688</v>
+        <v>0.1401508926851628</v>
       </c>
       <c r="T63">
-        <v>1.890211258112844</v>
+        <v>1.939953659642129</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.1366490382385388</v>
+        <v>0.1344450214927559</v>
       </c>
       <c r="W63">
-        <v>0.1733608731217014</v>
+        <v>0.1738034396842546</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5693709926605781</v>
+        <v>0.5601875895531494</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1610154718245997</v>
+        <v>0.1625654718245997</v>
       </c>
       <c r="C64">
-        <v>-1067.178120821639</v>
+        <v>-1136.223958451124</v>
       </c>
       <c r="D64">
-        <v>1810.513879178361</v>
+        <v>1788.284041548876</v>
       </c>
       <c r="E64">
-        <v>2840.692</v>
+        <v>2887.508</v>
       </c>
       <c r="F64">
-        <v>2902.592</v>
+        <v>2949.408</v>
       </c>
       <c r="G64">
         <v>24.9</v>
@@ -6535,37 +6535,37 @@
         <v>326.5</v>
       </c>
       <c r="M64">
-        <v>582.8404736</v>
+        <v>592.2411264</v>
       </c>
       <c r="N64">
-        <v>-256.3404736</v>
+        <v>-265.7411264</v>
       </c>
       <c r="O64">
-        <v>-61.521713664</v>
+        <v>-63.77787033599999</v>
       </c>
       <c r="P64">
-        <v>-194.818759936</v>
+        <v>-201.963256064</v>
       </c>
       <c r="Q64">
-        <v>-45.618759936</v>
+        <v>-52.76325606400002</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1401508926851628</v>
+        <v>0.1427009168117888</v>
       </c>
       <c r="T64">
-        <v>1.939953659642129</v>
+        <v>1.992384839632457</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.1344450214927559</v>
+        <v>0.1323109735325534</v>
       </c>
       <c r="W64">
-        <v>0.1738034396842546</v>
+        <v>0.1742319565146633</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5601875895531494</v>
+        <v>0.5512957230523058</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1625654718245997</v>
+        <v>0.1641154718245997</v>
       </c>
       <c r="C65">
-        <v>-1136.223958451124</v>
+        <v>-1204.730532814827</v>
       </c>
       <c r="D65">
-        <v>1788.284041548876</v>
+        <v>1766.593467185172</v>
       </c>
       <c r="E65">
-        <v>2887.508</v>
+        <v>2934.324</v>
       </c>
       <c r="F65">
-        <v>2949.408</v>
+        <v>2996.224</v>
       </c>
       <c r="G65">
         <v>24.9</v>
@@ -6617,37 +6617,37 @@
         <v>326.5</v>
       </c>
       <c r="M65">
-        <v>592.2411264</v>
+        <v>601.6417792</v>
       </c>
       <c r="N65">
-        <v>-265.7411264</v>
+        <v>-275.1417792</v>
       </c>
       <c r="O65">
-        <v>-63.77787033599999</v>
+        <v>-66.034027008</v>
       </c>
       <c r="P65">
-        <v>-201.963256064</v>
+        <v>-209.107752192</v>
       </c>
       <c r="Q65">
-        <v>-52.76325606400002</v>
+        <v>-59.90775219199998</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1427009168117888</v>
+        <v>0.1453926089454496</v>
       </c>
       <c r="T65">
-        <v>1.992384839632457</v>
+        <v>2.047728862955581</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.1323109735325534</v>
+        <v>0.1302436145711072</v>
       </c>
       <c r="W65">
-        <v>0.1742319565146633</v>
+        <v>0.1746470821941217</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5512957230523058</v>
+        <v>0.5426817273796135</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1641154718245997</v>
+        <v>0.1656654718245997</v>
       </c>
       <c r="C66">
-        <v>-1204.730532814827</v>
+        <v>-1272.717231361389</v>
       </c>
       <c r="D66">
-        <v>1766.593467185172</v>
+        <v>1745.422768638611</v>
       </c>
       <c r="E66">
-        <v>2934.324</v>
+        <v>2981.14</v>
       </c>
       <c r="F66">
-        <v>2996.224</v>
+        <v>3043.04</v>
       </c>
       <c r="G66">
         <v>24.9</v>
@@ -6699,37 +6699,37 @@
         <v>326.5</v>
       </c>
       <c r="M66">
-        <v>601.6417792</v>
+        <v>611.042432</v>
       </c>
       <c r="N66">
-        <v>-275.1417792</v>
+        <v>-284.542432</v>
       </c>
       <c r="O66">
-        <v>-66.034027008</v>
+        <v>-68.29018367999998</v>
       </c>
       <c r="P66">
-        <v>-209.107752192</v>
+        <v>-216.25224832</v>
       </c>
       <c r="Q66">
-        <v>-59.90775219199998</v>
+        <v>-67.05224831999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1453926089454496</v>
+        <v>0.1482381120581767</v>
       </c>
       <c r="T66">
-        <v>2.047728862955581</v>
+        <v>2.10623540189717</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1302436145711072</v>
+        <v>0.1282398666546287</v>
       </c>
       <c r="W66">
-        <v>0.1746470821941217</v>
+        <v>0.1750494347757506</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5426817273796135</v>
+        <v>0.5343327777276194</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1656654718245997</v>
+        <v>0.1672154718245998</v>
       </c>
       <c r="C67">
-        <v>-1272.717231361389</v>
+        <v>-1340.202523194984</v>
       </c>
       <c r="D67">
-        <v>1745.422768638611</v>
+        <v>1724.753476805016</v>
       </c>
       <c r="E67">
-        <v>2981.14</v>
+        <v>3027.956</v>
       </c>
       <c r="F67">
-        <v>3043.04</v>
+        <v>3089.856</v>
       </c>
       <c r="G67">
         <v>24.9</v>
@@ -6781,37 +6781,37 @@
         <v>326.5</v>
       </c>
       <c r="M67">
-        <v>611.042432</v>
+        <v>620.4430848</v>
       </c>
       <c r="N67">
-        <v>-284.542432</v>
+        <v>-293.9430848</v>
       </c>
       <c r="O67">
-        <v>-68.29018367999998</v>
+        <v>-70.54634035199999</v>
       </c>
       <c r="P67">
-        <v>-216.25224832</v>
+        <v>-223.396744448</v>
       </c>
       <c r="Q67">
-        <v>-67.05224831999999</v>
+        <v>-74.19674444799998</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1482381120581767</v>
+        <v>0.1512509977069467</v>
       </c>
       <c r="T67">
-        <v>2.10623540189717</v>
+        <v>2.168183501952968</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1282398666546287</v>
+        <v>0.1262968383719828</v>
       </c>
       <c r="W67">
-        <v>0.1750494347757506</v>
+        <v>0.1754395948549059</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5343327777276194</v>
+        <v>0.5262368265499282</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1672154718245998</v>
+        <v>0.1687654718245997</v>
       </c>
       <c r="C68">
-        <v>-1340.202523194984</v>
+        <v>-1407.204012814114</v>
       </c>
       <c r="D68">
-        <v>1724.753476805016</v>
+        <v>1704.567987185886</v>
       </c>
       <c r="E68">
-        <v>3027.956</v>
+        <v>3074.772</v>
       </c>
       <c r="F68">
-        <v>3089.856</v>
+        <v>3136.672</v>
       </c>
       <c r="G68">
         <v>24.9</v>
@@ -6863,37 +6863,37 @@
         <v>326.5</v>
       </c>
       <c r="M68">
-        <v>620.4430848</v>
+        <v>629.8437376000001</v>
       </c>
       <c r="N68">
-        <v>-293.9430848</v>
+        <v>-303.3437376000001</v>
       </c>
       <c r="O68">
-        <v>-70.54634035199999</v>
+        <v>-72.802497024</v>
       </c>
       <c r="P68">
-        <v>-223.396744448</v>
+        <v>-230.5412405760001</v>
       </c>
       <c r="Q68">
-        <v>-74.19674444799998</v>
+        <v>-81.34124057600008</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1512509977069467</v>
+        <v>0.1544464824859451</v>
       </c>
       <c r="T68">
-        <v>2.168183501952968</v>
+        <v>2.23388603231518</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.1262968383719828</v>
+        <v>0.1244118109335949</v>
       </c>
       <c r="W68">
-        <v>0.1754395948549059</v>
+        <v>0.1758181083645341</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5262368265499282</v>
+        <v>0.5183825455566456</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1687654718245997</v>
+        <v>0.1703154718245997</v>
       </c>
       <c r="C69">
-        <v>-1407.204012814114</v>
+        <v>-1473.738490120488</v>
       </c>
       <c r="D69">
-        <v>1704.567987185886</v>
+        <v>1684.849509879511</v>
       </c>
       <c r="E69">
-        <v>3074.772</v>
+        <v>3121.588</v>
       </c>
       <c r="F69">
-        <v>3136.672</v>
+        <v>3183.488</v>
       </c>
       <c r="G69">
         <v>24.9</v>
@@ -6945,37 +6945,37 @@
         <v>326.5</v>
       </c>
       <c r="M69">
-        <v>629.8437376000001</v>
+        <v>639.2443903999999</v>
       </c>
       <c r="N69">
-        <v>-303.3437376000001</v>
+        <v>-312.7443903999999</v>
       </c>
       <c r="O69">
-        <v>-72.802497024</v>
+        <v>-75.05865369599998</v>
       </c>
       <c r="P69">
-        <v>-230.5412405760001</v>
+        <v>-237.685736704</v>
       </c>
       <c r="Q69">
-        <v>-81.34124057600008</v>
+        <v>-88.48573670399998</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1544464824859451</v>
+        <v>0.1578416850636308</v>
       </c>
       <c r="T69">
-        <v>2.23388603231518</v>
+        <v>2.303694970825029</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.1244118109335949</v>
+        <v>0.1225822254786892</v>
       </c>
       <c r="W69">
-        <v>0.1758181083645341</v>
+        <v>0.1761854891238792</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5183825455566456</v>
+        <v>0.5107592728278716</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1703154718245997</v>
+        <v>0.1718654718245997</v>
       </c>
       <c r="C70">
-        <v>-1473.738490120488</v>
+        <v>-1539.821976996573</v>
       </c>
       <c r="D70">
-        <v>1684.849509879511</v>
+        <v>1665.582023003427</v>
       </c>
       <c r="E70">
-        <v>3121.588</v>
+        <v>3168.404</v>
       </c>
       <c r="F70">
-        <v>3183.488</v>
+        <v>3230.304</v>
       </c>
       <c r="G70">
         <v>24.9</v>
@@ -7027,37 +7027,37 @@
         <v>326.5</v>
       </c>
       <c r="M70">
-        <v>639.2443903999999</v>
+        <v>648.6450432</v>
       </c>
       <c r="N70">
-        <v>-312.7443903999999</v>
+        <v>-322.1450432</v>
       </c>
       <c r="O70">
-        <v>-75.05865369599998</v>
+        <v>-77.31481036800001</v>
       </c>
       <c r="P70">
-        <v>-237.685736704</v>
+        <v>-244.830232832</v>
       </c>
       <c r="Q70">
-        <v>-88.48573670399998</v>
+        <v>-95.63023283200005</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1578416850636308</v>
+        <v>0.1614559329689092</v>
       </c>
       <c r="T70">
-        <v>2.303694970825029</v>
+        <v>2.378007711819385</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.1225822254786892</v>
+        <v>0.1208056714862444</v>
       </c>
       <c r="W70">
-        <v>0.1761854891238792</v>
+        <v>0.1765422211655621</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5107592728278716</v>
+        <v>0.5033569645260183</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1718654718245997</v>
+        <v>0.1983994096036277</v>
       </c>
       <c r="C71">
-        <v>-1539.821976996573</v>
+        <v>-1859.318632276266</v>
       </c>
       <c r="D71">
-        <v>1665.582023003427</v>
+        <v>1392.901367723734</v>
       </c>
       <c r="E71">
-        <v>3168.404</v>
+        <v>3215.22</v>
       </c>
       <c r="F71">
-        <v>3230.304</v>
+        <v>3277.12</v>
       </c>
       <c r="G71">
         <v>24.9</v>
@@ -7109,45 +7109,45 @@
         <v>326.5</v>
       </c>
       <c r="M71">
-        <v>648.6450432</v>
+        <v>772.744896</v>
       </c>
       <c r="N71">
-        <v>-322.1450432</v>
+        <v>-446.244896</v>
       </c>
       <c r="O71">
-        <v>-77.31481036800001</v>
+        <v>-107.09877504</v>
       </c>
       <c r="P71">
-        <v>-244.830232832</v>
+        <v>-339.14612096</v>
       </c>
       <c r="Q71">
-        <v>-95.63023283200005</v>
+        <v>-189.94612096</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1614559329689092</v>
+        <v>0.1669242566646326</v>
       </c>
       <c r="T71">
-        <v>2.378007711819385</v>
+        <v>2.49044220251387</v>
       </c>
       <c r="U71">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.1208056714862444</v>
+        <v>0.1014047461272394</v>
       </c>
       <c r="W71">
-        <v>0.1765422211655621</v>
+        <v>0.211888760863197</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y71">
-        <v>0.5033569645260183</v>
+        <v>0.4225197755301641</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1983994096036277</v>
+        <v>0.2002994096036277</v>
       </c>
       <c r="C72">
-        <v>-1859.318632276266</v>
+        <v>-1922.274461081419</v>
       </c>
       <c r="D72">
-        <v>1392.901367723734</v>
+        <v>1376.761538918581</v>
       </c>
       <c r="E72">
-        <v>3215.22</v>
+        <v>3262.036</v>
       </c>
       <c r="F72">
-        <v>3277.12</v>
+        <v>3323.936</v>
       </c>
       <c r="G72">
         <v>24.9</v>
@@ -7191,37 +7191,37 @@
         <v>326.5</v>
       </c>
       <c r="M72">
-        <v>772.744896</v>
+        <v>783.7841088</v>
       </c>
       <c r="N72">
-        <v>-446.244896</v>
+        <v>-457.2841088</v>
       </c>
       <c r="O72">
-        <v>-107.09877504</v>
+        <v>-109.748186112</v>
       </c>
       <c r="P72">
-        <v>-339.14612096</v>
+        <v>-347.535922688</v>
       </c>
       <c r="Q72">
-        <v>-189.94612096</v>
+        <v>-198.335922688</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1669242566646326</v>
+        <v>0.1711009551703096</v>
       </c>
       <c r="T72">
-        <v>2.49044220251387</v>
+        <v>2.576319519841936</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.1014047461272394</v>
+        <v>0.09997651026629234</v>
       </c>
       <c r="W72">
-        <v>0.211888760863197</v>
+        <v>0.2122255388792083</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4225197755301641</v>
+        <v>0.4165687927762182</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2002994096036276</v>
+        <v>0.2021994096036276</v>
       </c>
       <c r="C73">
-        <v>-1922.274461081418</v>
+        <v>-1984.860543317767</v>
       </c>
       <c r="D73">
-        <v>1376.761538918581</v>
+        <v>1360.991456682232</v>
       </c>
       <c r="E73">
-        <v>3262.035999999999</v>
+        <v>3308.851999999999</v>
       </c>
       <c r="F73">
-        <v>3323.935999999999</v>
+        <v>3370.751999999999</v>
       </c>
       <c r="G73">
         <v>24.9</v>
@@ -7273,37 +7273,37 @@
         <v>326.5</v>
       </c>
       <c r="M73">
-        <v>783.7841087999999</v>
+        <v>794.8233215999999</v>
       </c>
       <c r="N73">
-        <v>-457.2841087999999</v>
+        <v>-468.3233215999999</v>
       </c>
       <c r="O73">
-        <v>-109.748186112</v>
+        <v>-112.397597184</v>
       </c>
       <c r="P73">
-        <v>-347.5359226879999</v>
+        <v>-355.9257244159999</v>
       </c>
       <c r="Q73">
-        <v>-198.3359226879999</v>
+        <v>-206.7257244159999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1711009551703096</v>
+        <v>0.1755759892835349</v>
       </c>
       <c r="T73">
-        <v>2.576319519841934</v>
+        <v>2.66833093126486</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.09997651026629235</v>
+        <v>0.09858794762370496</v>
       </c>
       <c r="W73">
-        <v>0.2122255388792083</v>
+        <v>0.2125529619503304</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.4165687927762182</v>
+        <v>0.4107831150987707</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2021994096036276</v>
+        <v>0.2040994096036277</v>
       </c>
       <c r="C74">
-        <v>-1984.860543317767</v>
+        <v>-2047.089440855453</v>
       </c>
       <c r="D74">
-        <v>1360.991456682232</v>
+        <v>1345.578559144546</v>
       </c>
       <c r="E74">
-        <v>3308.851999999999</v>
+        <v>3355.667999999999</v>
       </c>
       <c r="F74">
-        <v>3370.751999999999</v>
+        <v>3417.567999999999</v>
       </c>
       <c r="G74">
         <v>24.9</v>
@@ -7355,37 +7355,37 @@
         <v>326.5</v>
       </c>
       <c r="M74">
-        <v>794.8233215999999</v>
+        <v>805.8625343999998</v>
       </c>
       <c r="N74">
-        <v>-468.3233215999999</v>
+        <v>-479.3625343999998</v>
       </c>
       <c r="O74">
-        <v>-112.397597184</v>
+        <v>-115.047008256</v>
       </c>
       <c r="P74">
-        <v>-355.9257244159999</v>
+        <v>-364.3155261439999</v>
       </c>
       <c r="Q74">
-        <v>-206.7257244159999</v>
+        <v>-215.1155261439999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1755759892835349</v>
+        <v>0.1803825074051473</v>
       </c>
       <c r="T74">
-        <v>2.66833093126486</v>
+        <v>2.767158002793189</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.09858794762370496</v>
+        <v>0.09723742779324326</v>
       </c>
       <c r="W74">
-        <v>0.2125529619503304</v>
+        <v>0.2128714145263532</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.4107831150987707</v>
+        <v>0.4051559491385136</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2040994096036277</v>
+        <v>0.2059994096036277</v>
       </c>
       <c r="C75">
-        <v>-2047.089440855453</v>
+        <v>-2108.973152896189</v>
       </c>
       <c r="D75">
-        <v>1345.578559144546</v>
+        <v>1330.51084710381</v>
       </c>
       <c r="E75">
-        <v>3355.667999999999</v>
+        <v>3402.483999999999</v>
       </c>
       <c r="F75">
-        <v>3417.567999999999</v>
+        <v>3464.384</v>
       </c>
       <c r="G75">
         <v>24.9</v>
@@ -7437,37 +7437,37 @@
         <v>326.5</v>
       </c>
       <c r="M75">
-        <v>805.8625343999998</v>
+        <v>816.9017471999999</v>
       </c>
       <c r="N75">
-        <v>-479.3625343999998</v>
+        <v>-490.4017471999999</v>
       </c>
       <c r="O75">
-        <v>-115.047008256</v>
+        <v>-117.696419328</v>
       </c>
       <c r="P75">
-        <v>-364.3155261439999</v>
+        <v>-372.7053278719999</v>
       </c>
       <c r="Q75">
-        <v>-215.1155261439999</v>
+        <v>-223.505327872</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1803825074051473</v>
+        <v>0.1855587576899607</v>
       </c>
       <c r="T75">
-        <v>2.767158002793189</v>
+        <v>2.873587156746773</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.09723742779324326</v>
+        <v>0.09592340849873995</v>
       </c>
       <c r="W75">
-        <v>0.2128714145263532</v>
+        <v>0.2131812602759971</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.4051559491385136</v>
+        <v>0.3996808687447498</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2059994096036277</v>
+        <v>0.2078994096036277</v>
       </c>
       <c r="C76">
-        <v>-2108.973152896189</v>
+        <v>-2170.523147128043</v>
       </c>
       <c r="D76">
-        <v>1330.51084710381</v>
+        <v>1315.776852871957</v>
       </c>
       <c r="E76">
-        <v>3402.483999999999</v>
+        <v>3449.3</v>
       </c>
       <c r="F76">
-        <v>3464.384</v>
+        <v>3511.2</v>
       </c>
       <c r="G76">
         <v>24.9</v>
@@ -7519,37 +7519,37 @@
         <v>326.5</v>
       </c>
       <c r="M76">
-        <v>816.9017471999999</v>
+        <v>827.94096</v>
       </c>
       <c r="N76">
-        <v>-490.4017471999999</v>
+        <v>-501.44096</v>
       </c>
       <c r="O76">
-        <v>-117.696419328</v>
+        <v>-120.3458304</v>
       </c>
       <c r="P76">
-        <v>-372.7053278719999</v>
+        <v>-381.0951296</v>
       </c>
       <c r="Q76">
-        <v>-223.505327872</v>
+        <v>-231.8951296</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1855587576899607</v>
+        <v>0.1911491079975591</v>
       </c>
       <c r="T76">
-        <v>2.873587156746773</v>
+        <v>2.988530643016644</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.09592340849873995</v>
+        <v>0.09464442971875675</v>
       </c>
       <c r="W76">
-        <v>0.2131812602759971</v>
+        <v>0.2134828434723172</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3996808687447498</v>
+        <v>0.3943517904948198</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2078994096036277</v>
+        <v>0.2097994096036276</v>
       </c>
       <c r="C77">
-        <v>-2170.523147128043</v>
+        <v>-2231.75038883284</v>
       </c>
       <c r="D77">
-        <v>1315.776852871957</v>
+        <v>1301.365611167159</v>
       </c>
       <c r="E77">
-        <v>3449.3</v>
+        <v>3496.116</v>
       </c>
       <c r="F77">
-        <v>3511.2</v>
+        <v>3558.016</v>
       </c>
       <c r="G77">
         <v>24.9</v>
@@ -7601,37 +7601,37 @@
         <v>326.5</v>
       </c>
       <c r="M77">
-        <v>827.94096</v>
+        <v>838.9801728</v>
       </c>
       <c r="N77">
-        <v>-501.44096</v>
+        <v>-512.4801728</v>
       </c>
       <c r="O77">
-        <v>-120.3458304</v>
+        <v>-122.995241472</v>
       </c>
       <c r="P77">
-        <v>-381.0951296</v>
+        <v>-389.484931328</v>
       </c>
       <c r="Q77">
-        <v>-231.8951296</v>
+        <v>-240.284931328</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1911491079975591</v>
+        <v>0.1972053208307908</v>
       </c>
       <c r="T77">
-        <v>2.988530643016644</v>
+        <v>3.113052753142338</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.09464442971875675</v>
+        <v>0.09339910827508889</v>
       </c>
       <c r="W77">
-        <v>0.2134828434723172</v>
+        <v>0.213776490268734</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3943517904948198</v>
+        <v>0.3891629511462038</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2097994096036276</v>
+        <v>0.2116994096036277</v>
       </c>
       <c r="C78">
-        <v>-2231.75038883284</v>
+        <v>-2292.665368101491</v>
       </c>
       <c r="D78">
-        <v>1301.365611167159</v>
+        <v>1287.266631898509</v>
       </c>
       <c r="E78">
-        <v>3496.116</v>
+        <v>3542.932</v>
       </c>
       <c r="F78">
-        <v>3558.016</v>
+        <v>3604.832</v>
       </c>
       <c r="G78">
         <v>24.9</v>
@@ -7683,37 +7683,37 @@
         <v>326.5</v>
       </c>
       <c r="M78">
-        <v>838.9801728</v>
+        <v>850.0193856</v>
       </c>
       <c r="N78">
-        <v>-512.4801728</v>
+        <v>-523.5193856</v>
       </c>
       <c r="O78">
-        <v>-122.995241472</v>
+        <v>-125.644652544</v>
       </c>
       <c r="P78">
-        <v>-389.484931328</v>
+        <v>-397.874733056</v>
       </c>
       <c r="Q78">
-        <v>-240.284931328</v>
+        <v>-248.674733056</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1972053208307908</v>
+        <v>0.2037881608669121</v>
       </c>
       <c r="T78">
-        <v>3.113052753142338</v>
+        <v>3.248402872844179</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.09339910827508889</v>
+        <v>0.0921861328429449</v>
       </c>
       <c r="W78">
-        <v>0.213776490268734</v>
+        <v>0.2140625098756336</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3891629511462038</v>
+        <v>0.3841088868456037</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2116994096036277</v>
+        <v>0.2135994096036276</v>
       </c>
       <c r="C79">
-        <v>-2292.665368101491</v>
+        <v>-2353.278125299149</v>
       </c>
       <c r="D79">
-        <v>1287.266631898509</v>
+        <v>1273.46987470085</v>
       </c>
       <c r="E79">
-        <v>3542.932</v>
+        <v>3589.748</v>
       </c>
       <c r="F79">
-        <v>3604.832</v>
+        <v>3651.648</v>
       </c>
       <c r="G79">
         <v>24.9</v>
@@ -7765,37 +7765,37 @@
         <v>326.5</v>
       </c>
       <c r="M79">
-        <v>850.0193856</v>
+        <v>861.0585983999999</v>
       </c>
       <c r="N79">
-        <v>-523.5193856</v>
+        <v>-534.5585983999999</v>
       </c>
       <c r="O79">
-        <v>-125.644652544</v>
+        <v>-128.294063616</v>
       </c>
       <c r="P79">
-        <v>-397.874733056</v>
+        <v>-406.2645347839999</v>
       </c>
       <c r="Q79">
-        <v>-248.674733056</v>
+        <v>-257.0645347839999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2037881608669121</v>
+        <v>0.2109694409063172</v>
       </c>
       <c r="T79">
-        <v>3.248402872844179</v>
+        <v>3.39605754888255</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.0921861328429449</v>
+        <v>0.09100425934495843</v>
       </c>
       <c r="W79">
-        <v>0.2140625098756336</v>
+        <v>0.2143411956464588</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3841088868456037</v>
+        <v>0.3791844139373268</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2135994096036276</v>
+        <v>0.2154994096036277</v>
       </c>
       <c r="C80">
-        <v>-2353.278125299149</v>
+        <v>-2413.598274910176</v>
       </c>
       <c r="D80">
-        <v>1273.46987470085</v>
+        <v>1259.965725089824</v>
       </c>
       <c r="E80">
-        <v>3589.748</v>
+        <v>3636.564</v>
       </c>
       <c r="F80">
-        <v>3651.648</v>
+        <v>3698.464</v>
       </c>
       <c r="G80">
         <v>24.9</v>
@@ -7847,37 +7847,37 @@
         <v>326.5</v>
       </c>
       <c r="M80">
-        <v>861.0585983999999</v>
+        <v>872.0978112</v>
       </c>
       <c r="N80">
-        <v>-534.5585983999999</v>
+        <v>-545.5978112</v>
       </c>
       <c r="O80">
-        <v>-128.294063616</v>
+        <v>-130.943474688</v>
       </c>
       <c r="P80">
-        <v>-406.2645347839999</v>
+        <v>-414.654336512</v>
       </c>
       <c r="Q80">
-        <v>-257.0645347839999</v>
+        <v>-265.454336512</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2109694409063172</v>
+        <v>0.2188346523780466</v>
       </c>
       <c r="T80">
-        <v>3.39605754888255</v>
+        <v>3.557774575019816</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.09100425934495843</v>
+        <v>0.08985230669502223</v>
       </c>
       <c r="W80">
-        <v>0.2143411956464588</v>
+        <v>0.2146128260813138</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3791844139373268</v>
+        <v>0.3743846112292594</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2154994096036277</v>
+        <v>0.2173994096036277</v>
       </c>
       <c r="C81">
-        <v>-2413.598274910176</v>
+        <v>-2473.63502788184</v>
       </c>
       <c r="D81">
-        <v>1259.965725089824</v>
+        <v>1246.74497211816</v>
       </c>
       <c r="E81">
-        <v>3636.564</v>
+        <v>3683.38</v>
       </c>
       <c r="F81">
-        <v>3698.464</v>
+        <v>3745.28</v>
       </c>
       <c r="G81">
         <v>24.9</v>
@@ -7929,37 +7929,37 @@
         <v>326.5</v>
       </c>
       <c r="M81">
-        <v>872.0978112</v>
+        <v>883.137024</v>
       </c>
       <c r="N81">
-        <v>-545.5978112</v>
+        <v>-556.637024</v>
       </c>
       <c r="O81">
-        <v>-130.943474688</v>
+        <v>-133.59288576</v>
       </c>
       <c r="P81">
-        <v>-414.654336512</v>
+        <v>-423.04413824</v>
       </c>
       <c r="Q81">
-        <v>-265.454336512</v>
+        <v>-273.84413824</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2188346523780466</v>
+        <v>0.227486384996949</v>
       </c>
       <c r="T81">
-        <v>3.557774575019816</v>
+        <v>3.735663303770806</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.08985230669502223</v>
+        <v>0.08872915286133445</v>
       </c>
       <c r="W81">
-        <v>0.2146128260813138</v>
+        <v>0.2148776657552973</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3743846112292594</v>
+        <v>0.3697048035888936</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2173994096036277</v>
+        <v>0.2192994096036276</v>
       </c>
       <c r="C82">
-        <v>-2473.63502788184</v>
+        <v>-2533.397212575959</v>
       </c>
       <c r="D82">
-        <v>1246.74497211816</v>
+        <v>1233.798787424041</v>
       </c>
       <c r="E82">
-        <v>3683.38</v>
+        <v>3730.196</v>
       </c>
       <c r="F82">
-        <v>3745.28</v>
+        <v>3792.096</v>
       </c>
       <c r="G82">
         <v>24.9</v>
@@ -8011,37 +8011,37 @@
         <v>326.5</v>
       </c>
       <c r="M82">
-        <v>883.137024</v>
+        <v>894.1762368000001</v>
       </c>
       <c r="N82">
-        <v>-556.637024</v>
+        <v>-567.6762368000001</v>
       </c>
       <c r="O82">
-        <v>-133.59288576</v>
+        <v>-136.242296832</v>
       </c>
       <c r="P82">
-        <v>-423.04413824</v>
+        <v>-431.4339399680001</v>
       </c>
       <c r="Q82">
-        <v>-273.84413824</v>
+        <v>-282.2339399680001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.227486384996949</v>
+        <v>0.2370488263125778</v>
       </c>
       <c r="T82">
-        <v>3.735663303770806</v>
+        <v>3.932277161864006</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.08872915286133445</v>
+        <v>0.08763373122107107</v>
       </c>
       <c r="W82">
-        <v>0.2148776657552973</v>
+        <v>0.2151359661780714</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3697048035888936</v>
+        <v>0.3651405467544627</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2192994096036276</v>
+        <v>0.2211994096036277</v>
       </c>
       <c r="C83">
-        <v>-2533.397212575959</v>
+        <v>-2592.893294428555</v>
       </c>
       <c r="D83">
-        <v>1233.798787424041</v>
+        <v>1221.118705571444</v>
       </c>
       <c r="E83">
-        <v>3730.196</v>
+        <v>3777.012</v>
       </c>
       <c r="F83">
-        <v>3792.096</v>
+        <v>3838.912</v>
       </c>
       <c r="G83">
         <v>24.9</v>
@@ -8093,37 +8093,37 @@
         <v>326.5</v>
       </c>
       <c r="M83">
-        <v>894.1762368000001</v>
+        <v>905.2154495999999</v>
       </c>
       <c r="N83">
-        <v>-567.6762368000001</v>
+        <v>-578.7154495999999</v>
       </c>
       <c r="O83">
-        <v>-136.242296832</v>
+        <v>-138.891707904</v>
       </c>
       <c r="P83">
-        <v>-431.4339399680001</v>
+        <v>-439.823741696</v>
       </c>
       <c r="Q83">
-        <v>-282.2339399680001</v>
+        <v>-290.623741696</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2370488263125778</v>
+        <v>0.2476737611077211</v>
       </c>
       <c r="T83">
-        <v>3.932277161864006</v>
+        <v>4.150737004189785</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.08763373122107107</v>
+        <v>0.08656502718178972</v>
       </c>
       <c r="W83">
-        <v>0.2151359661780714</v>
+        <v>0.215387966590534</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3651405467544627</v>
+        <v>0.3606876132574571</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2211994096036277</v>
+        <v>0.2230994096036277</v>
       </c>
       <c r="C84">
-        <v>-2592.893294428555</v>
+        <v>-2652.131394409575</v>
       </c>
       <c r="D84">
-        <v>1221.118705571444</v>
+        <v>1208.696605590424</v>
       </c>
       <c r="E84">
-        <v>3777.012</v>
+        <v>3823.828</v>
       </c>
       <c r="F84">
-        <v>3838.912</v>
+        <v>3885.728</v>
       </c>
       <c r="G84">
         <v>24.9</v>
@@ -8175,37 +8175,37 @@
         <v>326.5</v>
       </c>
       <c r="M84">
-        <v>905.2154495999999</v>
+        <v>916.2546624</v>
       </c>
       <c r="N84">
-        <v>-578.7154495999999</v>
+        <v>-589.7546624</v>
       </c>
       <c r="O84">
-        <v>-138.891707904</v>
+        <v>-141.541118976</v>
       </c>
       <c r="P84">
-        <v>-439.823741696</v>
+        <v>-448.213543424</v>
       </c>
       <c r="Q84">
-        <v>-290.623741696</v>
+        <v>-299.013543424</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2476737611077211</v>
+        <v>0.2595486882317046</v>
       </c>
       <c r="T84">
-        <v>4.150737004189785</v>
+        <v>4.394898004436243</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.08656502718178972</v>
+        <v>0.08552207504706935</v>
       </c>
       <c r="W84">
-        <v>0.215387966590534</v>
+        <v>0.2156338947039011</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3606876132574571</v>
+        <v>0.356341979362789</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2230994096036277</v>
+        <v>0.2249994096036277</v>
       </c>
       <c r="C85">
-        <v>-2652.131394409575</v>
+        <v>-2711.119306367234</v>
       </c>
       <c r="D85">
-        <v>1208.696605590424</v>
+        <v>1196.524693632766</v>
       </c>
       <c r="E85">
-        <v>3823.828</v>
+        <v>3870.644</v>
       </c>
       <c r="F85">
-        <v>3885.728</v>
+        <v>3932.544</v>
       </c>
       <c r="G85">
         <v>24.9</v>
@@ -8257,37 +8257,37 @@
         <v>326.5</v>
       </c>
       <c r="M85">
-        <v>916.2546624</v>
+        <v>927.2938752</v>
       </c>
       <c r="N85">
-        <v>-589.7546624</v>
+        <v>-600.7938752</v>
       </c>
       <c r="O85">
-        <v>-141.541118976</v>
+        <v>-144.190530048</v>
       </c>
       <c r="P85">
-        <v>-448.213543424</v>
+        <v>-456.603345152</v>
       </c>
       <c r="Q85">
-        <v>-299.013543424</v>
+        <v>-307.403345152</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2595486882317046</v>
+        <v>0.2729079812461863</v>
       </c>
       <c r="T85">
-        <v>4.394898004436243</v>
+        <v>4.669579129713509</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.08552207504706935</v>
+        <v>0.08450395510603281</v>
       </c>
       <c r="W85">
-        <v>0.2156338947039011</v>
+        <v>0.2158739673859975</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.356341979362789</v>
+        <v>0.3520998129418034</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2249994096036277</v>
+        <v>0.2268994096036277</v>
       </c>
       <c r="C86">
-        <v>-2711.119306367233</v>
+        <v>-2769.864513334835</v>
       </c>
       <c r="D86">
-        <v>1196.524693632767</v>
+        <v>1184.595486665164</v>
       </c>
       <c r="E86">
-        <v>3870.643999999999</v>
+        <v>3917.459999999999</v>
       </c>
       <c r="F86">
-        <v>3932.543999999999</v>
+        <v>3979.359999999999</v>
       </c>
       <c r="G86">
         <v>24.9</v>
@@ -8339,37 +8339,37 @@
         <v>326.5</v>
       </c>
       <c r="M86">
-        <v>927.2938751999999</v>
+        <v>938.3330879999999</v>
       </c>
       <c r="N86">
-        <v>-600.7938751999999</v>
+        <v>-611.8330879999999</v>
       </c>
       <c r="O86">
-        <v>-144.190530048</v>
+        <v>-146.83994112</v>
       </c>
       <c r="P86">
-        <v>-456.6033451519999</v>
+        <v>-464.9931468799999</v>
       </c>
       <c r="Q86">
-        <v>-307.4033451519999</v>
+        <v>-315.7931468799999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.272907981246186</v>
+        <v>0.2880485133292652</v>
       </c>
       <c r="T86">
-        <v>4.669579129713505</v>
+        <v>4.98088440502774</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.08450395510603283</v>
+        <v>0.0835097909283148</v>
       </c>
       <c r="W86">
-        <v>0.2158739673859975</v>
+        <v>0.2161083912991034</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3520998129418035</v>
+        <v>0.3479574622013116</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2268994096036277</v>
+        <v>0.2287994096036276</v>
       </c>
       <c r="C87">
-        <v>-2769.864513334835</v>
+        <v>-2828.37420287177</v>
       </c>
       <c r="D87">
-        <v>1184.595486665164</v>
+        <v>1172.90179712823</v>
       </c>
       <c r="E87">
-        <v>3917.459999999999</v>
+        <v>3964.275999999999</v>
       </c>
       <c r="F87">
-        <v>3979.359999999999</v>
+        <v>4026.175999999999</v>
       </c>
       <c r="G87">
         <v>24.9</v>
@@ -8421,37 +8421,37 @@
         <v>326.5</v>
       </c>
       <c r="M87">
-        <v>938.3330879999999</v>
+        <v>949.3723007999999</v>
       </c>
       <c r="N87">
-        <v>-611.8330879999999</v>
+        <v>-622.8723007999999</v>
       </c>
       <c r="O87">
-        <v>-146.83994112</v>
+        <v>-149.489352192</v>
       </c>
       <c r="P87">
-        <v>-464.9931468799999</v>
+        <v>-473.382948608</v>
       </c>
       <c r="Q87">
-        <v>-315.7931468799999</v>
+        <v>-324.182948608</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2880485133292652</v>
+        <v>0.3053519785670698</v>
       </c>
       <c r="T87">
-        <v>4.98088440502774</v>
+        <v>5.336661862529721</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.0835097909283148</v>
+        <v>0.08253874684775299</v>
       </c>
       <c r="W87">
-        <v>0.2161083912991034</v>
+        <v>0.2163373634932999</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3479574622013116</v>
+        <v>0.3439114451989708</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2287994096036276</v>
+        <v>0.2306994096036276</v>
       </c>
       <c r="C88">
-        <v>-2828.37420287177</v>
+        <v>-2886.655281504741</v>
       </c>
       <c r="D88">
-        <v>1172.90179712823</v>
+        <v>1161.436718495259</v>
       </c>
       <c r="E88">
-        <v>3964.275999999999</v>
+        <v>4011.091999999999</v>
       </c>
       <c r="F88">
-        <v>4026.175999999999</v>
+        <v>4072.991999999999</v>
       </c>
       <c r="G88">
         <v>24.9</v>
@@ -8503,37 +8503,37 @@
         <v>326.5</v>
       </c>
       <c r="M88">
-        <v>949.3723007999999</v>
+        <v>960.4115135999999</v>
       </c>
       <c r="N88">
-        <v>-622.8723007999999</v>
+        <v>-633.9115135999999</v>
       </c>
       <c r="O88">
-        <v>-149.489352192</v>
+        <v>-152.138763264</v>
       </c>
       <c r="P88">
-        <v>-473.382948608</v>
+        <v>-481.7727503359999</v>
       </c>
       <c r="Q88">
-        <v>-324.182948608</v>
+        <v>-332.572750336</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3053519785670698</v>
+        <v>0.3253175153799214</v>
       </c>
       <c r="T88">
-        <v>5.336661862529721</v>
+        <v>5.747174313493546</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.08253874684775299</v>
+        <v>0.0815900256196179</v>
       </c>
       <c r="W88">
-        <v>0.2163373634932999</v>
+        <v>0.2165610719588941</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3439114451989708</v>
+        <v>0.3399584400817413</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2306994096036276</v>
+        <v>0.2325994096036276</v>
       </c>
       <c r="C89">
-        <v>-2886.655281504741</v>
+        <v>-2944.714388330243</v>
       </c>
       <c r="D89">
-        <v>1161.436718495259</v>
+        <v>1150.193611669757</v>
       </c>
       <c r="E89">
-        <v>4011.091999999999</v>
+        <v>4057.908</v>
       </c>
       <c r="F89">
-        <v>4072.991999999999</v>
+        <v>4119.808</v>
       </c>
       <c r="G89">
         <v>24.9</v>
@@ -8585,37 +8585,37 @@
         <v>326.5</v>
       </c>
       <c r="M89">
-        <v>960.4115135999999</v>
+        <v>971.4507264</v>
       </c>
       <c r="N89">
-        <v>-633.9115135999999</v>
+        <v>-644.9507264</v>
       </c>
       <c r="O89">
-        <v>-152.138763264</v>
+        <v>-154.788174336</v>
       </c>
       <c r="P89">
-        <v>-481.7727503359999</v>
+        <v>-490.162552064</v>
       </c>
       <c r="Q89">
-        <v>-332.572750336</v>
+        <v>-340.962552064</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3253175153799214</v>
+        <v>0.3486106416615815</v>
       </c>
       <c r="T89">
-        <v>5.747174313493546</v>
+        <v>6.226105506284675</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.0815900256196179</v>
+        <v>0.08066286623757678</v>
       </c>
       <c r="W89">
-        <v>0.2165610719588941</v>
+        <v>0.2167796961411794</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3399584400817413</v>
+        <v>0.3360952759899033</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2325994096036276</v>
+        <v>0.2344994096036276</v>
       </c>
       <c r="C90">
-        <v>-2944.714388330243</v>
+        <v>-3002.557907834532</v>
       </c>
       <c r="D90">
-        <v>1150.193611669757</v>
+        <v>1139.166092165467</v>
       </c>
       <c r="E90">
-        <v>4057.908</v>
+        <v>4104.724</v>
       </c>
       <c r="F90">
-        <v>4119.808</v>
+        <v>4166.624</v>
       </c>
       <c r="G90">
         <v>24.9</v>
@@ -8667,37 +8667,37 @@
         <v>326.5</v>
       </c>
       <c r="M90">
-        <v>971.4507264</v>
+        <v>982.4899392</v>
       </c>
       <c r="N90">
-        <v>-644.9507264</v>
+        <v>-655.9899392</v>
       </c>
       <c r="O90">
-        <v>-154.788174336</v>
+        <v>-157.437585408</v>
       </c>
       <c r="P90">
-        <v>-490.162552064</v>
+        <v>-498.552353792</v>
       </c>
       <c r="Q90">
-        <v>-340.962552064</v>
+        <v>-349.352353792</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3486106416615815</v>
+        <v>0.3761388818126344</v>
       </c>
       <c r="T90">
-        <v>6.226105506284675</v>
+        <v>6.792115097765101</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.08066286623757678</v>
+        <v>0.07975654189782873</v>
       </c>
       <c r="W90">
-        <v>0.2167796961411794</v>
+        <v>0.216993407420492</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3360952759899033</v>
+        <v>0.3323189245742864</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2344994096036276</v>
+        <v>0.2363994096036277</v>
       </c>
       <c r="C91">
-        <v>-3002.557907834532</v>
+        <v>-3060.191981983148</v>
       </c>
       <c r="D91">
-        <v>1139.166092165467</v>
+        <v>1128.348018016852</v>
       </c>
       <c r="E91">
-        <v>4104.724</v>
+        <v>4151.54</v>
       </c>
       <c r="F91">
-        <v>4166.624</v>
+        <v>4213.44</v>
       </c>
       <c r="G91">
         <v>24.9</v>
@@ -8749,37 +8749,37 @@
         <v>326.5</v>
       </c>
       <c r="M91">
-        <v>982.4899392</v>
+        <v>993.529152</v>
       </c>
       <c r="N91">
-        <v>-655.9899392</v>
+        <v>-667.029152</v>
       </c>
       <c r="O91">
-        <v>-157.437585408</v>
+        <v>-160.08699648</v>
       </c>
       <c r="P91">
-        <v>-498.552353792</v>
+        <v>-506.94215552</v>
       </c>
       <c r="Q91">
-        <v>-349.352353792</v>
+        <v>-357.74215552</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3761388818126344</v>
+        <v>0.4091727699938978</v>
       </c>
       <c r="T91">
-        <v>6.792115097765101</v>
+        <v>7.471326607541611</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.07975654189782873</v>
+        <v>0.07887035809896396</v>
       </c>
       <c r="W91">
-        <v>0.216993407420492</v>
+        <v>0.2172023695602643</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3323189245742864</v>
+        <v>0.3286264920790165</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2363994096036277</v>
+        <v>0.2382994096036277</v>
       </c>
       <c r="C92">
-        <v>-3060.191981983148</v>
+        <v>-3117.62252162805</v>
       </c>
       <c r="D92">
-        <v>1128.348018016852</v>
+        <v>1117.73347837195</v>
       </c>
       <c r="E92">
-        <v>4151.54</v>
+        <v>4198.356</v>
       </c>
       <c r="F92">
-        <v>4213.44</v>
+        <v>4260.255999999999</v>
       </c>
       <c r="G92">
         <v>24.9</v>
@@ -8831,37 +8831,37 @@
         <v>326.5</v>
       </c>
       <c r="M92">
-        <v>993.529152</v>
+        <v>1004.5683648</v>
       </c>
       <c r="N92">
-        <v>-667.029152</v>
+        <v>-678.0683647999999</v>
       </c>
       <c r="O92">
-        <v>-160.08699648</v>
+        <v>-162.736407552</v>
       </c>
       <c r="P92">
-        <v>-506.94215552</v>
+        <v>-515.331957248</v>
       </c>
       <c r="Q92">
-        <v>-357.74215552</v>
+        <v>-366.131957248</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4091727699938978</v>
+        <v>0.4495475222154421</v>
       </c>
       <c r="T92">
-        <v>7.471326607541611</v>
+        <v>8.30147400837957</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.07887035809896396</v>
+        <v>0.07800365086710721</v>
       </c>
       <c r="W92">
-        <v>0.2172023695602643</v>
+        <v>0.2174067391255361</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3286264920790165</v>
+        <v>0.3250152119462801</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2382994096036277</v>
+        <v>0.2401994096036277</v>
       </c>
       <c r="C93">
-        <v>-3117.62252162805</v>
+        <v>-3174.855217276912</v>
       </c>
       <c r="D93">
-        <v>1117.73347837195</v>
+        <v>1107.316782723087</v>
       </c>
       <c r="E93">
-        <v>4198.356</v>
+        <v>4245.172</v>
       </c>
       <c r="F93">
-        <v>4260.255999999999</v>
+        <v>4307.072</v>
       </c>
       <c r="G93">
         <v>24.9</v>
@@ -8913,37 +8913,37 @@
         <v>326.5</v>
       </c>
       <c r="M93">
-        <v>1004.5683648</v>
+        <v>1015.6075776</v>
       </c>
       <c r="N93">
-        <v>-678.0683647999999</v>
+        <v>-689.1075776</v>
       </c>
       <c r="O93">
-        <v>-162.736407552</v>
+        <v>-165.385818624</v>
       </c>
       <c r="P93">
-        <v>-515.331957248</v>
+        <v>-523.721758976</v>
       </c>
       <c r="Q93">
-        <v>-366.131957248</v>
+        <v>-374.5217589760001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4495475222154421</v>
+        <v>0.5000159624923725</v>
       </c>
       <c r="T93">
-        <v>8.30147400837957</v>
+        <v>9.339158259427018</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.07800365086710721</v>
+        <v>0.07715578509681256</v>
       </c>
       <c r="W93">
-        <v>0.2174067391255361</v>
+        <v>0.2176066658741716</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3250152119462801</v>
+        <v>0.3214824379033857</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2401994096036277</v>
+        <v>0.2420994096036277</v>
       </c>
       <c r="C94">
-        <v>-3174.855217276912</v>
+        <v>-3231.895549265795</v>
       </c>
       <c r="D94">
-        <v>1107.316782723087</v>
+        <v>1097.092450734204</v>
       </c>
       <c r="E94">
-        <v>4245.172</v>
+        <v>4291.988</v>
       </c>
       <c r="F94">
-        <v>4307.072</v>
+        <v>4353.888</v>
       </c>
       <c r="G94">
         <v>24.9</v>
@@ -8995,37 +8995,37 @@
         <v>326.5</v>
       </c>
       <c r="M94">
-        <v>1015.6075776</v>
+        <v>1026.6467904</v>
       </c>
       <c r="N94">
-        <v>-689.1075776</v>
+        <v>-700.1467904000001</v>
       </c>
       <c r="O94">
-        <v>-165.385818624</v>
+        <v>-168.035229696</v>
       </c>
       <c r="P94">
-        <v>-523.721758976</v>
+        <v>-532.1115607040001</v>
       </c>
       <c r="Q94">
-        <v>-374.5217589760001</v>
+        <v>-382.9115607040001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5000159624923725</v>
+        <v>0.56490395713414</v>
       </c>
       <c r="T94">
-        <v>9.339158259427018</v>
+        <v>10.67332372505945</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.07715578509681256</v>
+        <v>0.07632615299899738</v>
       </c>
       <c r="W94">
-        <v>0.2176066658741716</v>
+        <v>0.2178022931228364</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3214824379033857</v>
+        <v>0.3180256374958224</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2420994096036277</v>
+        <v>0.2439994096036277</v>
       </c>
       <c r="C95">
-        <v>-3231.895549265795</v>
+        <v>-3288.748797373391</v>
       </c>
       <c r="D95">
-        <v>1097.092450734204</v>
+        <v>1087.055202626609</v>
       </c>
       <c r="E95">
-        <v>4291.988</v>
+        <v>4338.804</v>
       </c>
       <c r="F95">
-        <v>4353.888</v>
+        <v>4400.704</v>
       </c>
       <c r="G95">
         <v>24.9</v>
@@ -9077,37 +9077,37 @@
         <v>326.5</v>
       </c>
       <c r="M95">
-        <v>1026.6467904</v>
+        <v>1037.6860032</v>
       </c>
       <c r="N95">
-        <v>-700.1467904000001</v>
+        <v>-711.1860032</v>
       </c>
       <c r="O95">
-        <v>-168.035229696</v>
+        <v>-170.684640768</v>
       </c>
       <c r="P95">
-        <v>-532.1115607040001</v>
+        <v>-540.501362432</v>
       </c>
       <c r="Q95">
-        <v>-382.9115607040001</v>
+        <v>-391.301362432</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.56490395713414</v>
+        <v>0.6514212833231635</v>
       </c>
       <c r="T95">
-        <v>10.67332372505945</v>
+        <v>12.45221101256936</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.07632615299899738</v>
+        <v>0.07551417264794423</v>
       </c>
       <c r="W95">
-        <v>0.2178022931228364</v>
+        <v>0.2179937580896148</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3180256374958224</v>
+        <v>0.3146423860331009</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2439994096036277</v>
+        <v>0.2458994096036277</v>
       </c>
       <c r="C96">
-        <v>-3288.748797373391</v>
+        <v>-3345.420049912303</v>
       </c>
       <c r="D96">
-        <v>1087.055202626609</v>
+        <v>1077.199950087697</v>
       </c>
       <c r="E96">
-        <v>4338.804</v>
+        <v>4385.62</v>
       </c>
       <c r="F96">
-        <v>4400.704</v>
+        <v>4447.52</v>
       </c>
       <c r="G96">
         <v>24.9</v>
@@ -9159,37 +9159,37 @@
         <v>326.5</v>
       </c>
       <c r="M96">
-        <v>1037.6860032</v>
+        <v>1048.725216</v>
       </c>
       <c r="N96">
-        <v>-711.1860032</v>
+        <v>-722.2252159999998</v>
       </c>
       <c r="O96">
-        <v>-170.684640768</v>
+        <v>-173.3340518399999</v>
       </c>
       <c r="P96">
-        <v>-540.501362432</v>
+        <v>-548.8911641599999</v>
       </c>
       <c r="Q96">
-        <v>-391.301362432</v>
+        <v>-399.6911641599999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6514212833231635</v>
+        <v>0.7725455399877965</v>
       </c>
       <c r="T96">
-        <v>12.45221101256936</v>
+        <v>14.94265321508324</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.07551417264794423</v>
+        <v>0.07471928662007114</v>
       </c>
       <c r="W96">
-        <v>0.2179937580896148</v>
+        <v>0.2181811922149872</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3146423860331009</v>
+        <v>0.3113303609169631</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2458994096036277</v>
+        <v>0.2477994096036277</v>
       </c>
       <c r="C97">
-        <v>-3345.420049912303</v>
+        <v>-3401.914212330234</v>
       </c>
       <c r="D97">
-        <v>1077.199950087697</v>
+        <v>1067.521787669765</v>
       </c>
       <c r="E97">
-        <v>4385.62</v>
+        <v>4432.436000000001</v>
       </c>
       <c r="F97">
-        <v>4447.52</v>
+        <v>4494.336</v>
       </c>
       <c r="G97">
         <v>24.9</v>
@@ -9241,37 +9241,37 @@
         <v>326.5</v>
       </c>
       <c r="M97">
-        <v>1048.725216</v>
+        <v>1059.7644288</v>
       </c>
       <c r="N97">
-        <v>-722.2252159999998</v>
+        <v>-733.2644288000001</v>
       </c>
       <c r="O97">
-        <v>-173.3340518399999</v>
+        <v>-175.983462912</v>
       </c>
       <c r="P97">
-        <v>-548.8911641599999</v>
+        <v>-557.2809658880001</v>
       </c>
       <c r="Q97">
-        <v>-399.6911641599999</v>
+        <v>-408.0809658880001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7725455399877965</v>
+        <v>0.9542319249847461</v>
       </c>
       <c r="T97">
-        <v>14.94265321508324</v>
+        <v>18.67831651885406</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.07471928662007114</v>
+        <v>0.07394096071777871</v>
       </c>
       <c r="W97">
-        <v>0.2181811922149872</v>
+        <v>0.2183647214627478</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3113303609169631</v>
+        <v>0.3080873363240779</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2477994096036276</v>
+        <v>0.2496994096036277</v>
       </c>
       <c r="C98">
-        <v>-3401.914212330234</v>
+        <v>-3458.236015351631</v>
       </c>
       <c r="D98">
-        <v>1067.521787669766</v>
+        <v>1058.015984648368</v>
       </c>
       <c r="E98">
-        <v>4432.436</v>
+        <v>4479.251999999999</v>
       </c>
       <c r="F98">
-        <v>4494.335999999999</v>
+        <v>4541.151999999999</v>
       </c>
       <c r="G98">
         <v>24.9</v>
@@ -9323,37 +9323,37 @@
         <v>326.5</v>
       </c>
       <c r="M98">
-        <v>1059.7644288</v>
+        <v>1070.8036416</v>
       </c>
       <c r="N98">
-        <v>-733.2644287999999</v>
+        <v>-744.3036415999998</v>
       </c>
       <c r="O98">
-        <v>-175.983462912</v>
+        <v>-178.6328739839999</v>
       </c>
       <c r="P98">
-        <v>-557.280965888</v>
+        <v>-565.6707676159998</v>
       </c>
       <c r="Q98">
-        <v>-408.080965888</v>
+        <v>-416.4707676159998</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9542319249847435</v>
+        <v>1.257042566646325</v>
       </c>
       <c r="T98">
-        <v>18.67831651885401</v>
+        <v>24.90442202513868</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.07394096071777873</v>
+        <v>0.07317868277223462</v>
       </c>
       <c r="W98">
-        <v>0.2183647214627478</v>
+        <v>0.2185444666023071</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.308087336324078</v>
+        <v>0.3049111782176442</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2496994096036277</v>
+        <v>0.2515994096036276</v>
       </c>
       <c r="C99">
-        <v>-3458.236015351631</v>
+        <v>-3514.390022688197</v>
       </c>
       <c r="D99">
-        <v>1058.015984648368</v>
+        <v>1048.677977311801</v>
       </c>
       <c r="E99">
-        <v>4479.251999999999</v>
+        <v>4526.067999999999</v>
       </c>
       <c r="F99">
-        <v>4541.151999999999</v>
+        <v>4587.967999999999</v>
       </c>
       <c r="G99">
         <v>24.9</v>
@@ -9405,37 +9405,37 @@
         <v>326.5</v>
       </c>
       <c r="M99">
-        <v>1070.8036416</v>
+        <v>1081.8428544</v>
       </c>
       <c r="N99">
-        <v>-744.3036415999998</v>
+        <v>-755.3428543999999</v>
       </c>
       <c r="O99">
-        <v>-178.6328739839999</v>
+        <v>-181.2822850559999</v>
       </c>
       <c r="P99">
-        <v>-565.6707676159998</v>
+        <v>-574.0605693439999</v>
       </c>
       <c r="Q99">
-        <v>-416.4707676159998</v>
+        <v>-424.8605693439999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.257042566646325</v>
+        <v>1.862663849969487</v>
       </c>
       <c r="T99">
-        <v>24.90442202513868</v>
+        <v>37.35663303770801</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.07317868277223462</v>
+        <v>0.07243196151945672</v>
       </c>
       <c r="W99">
-        <v>0.2185444666023071</v>
+        <v>0.2187205434737121</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3049111782176442</v>
+        <v>0.3017998396644029</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2515994096036276</v>
+        <v>0.2534994096036277</v>
       </c>
       <c r="C100">
-        <v>-3514.390022688197</v>
+        <v>-3570.380638344642</v>
       </c>
       <c r="D100">
-        <v>1048.677977311801</v>
+        <v>1039.503361655358</v>
       </c>
       <c r="E100">
-        <v>4526.067999999999</v>
+        <v>4572.884</v>
       </c>
       <c r="F100">
-        <v>4587.967999999999</v>
+        <v>4634.784</v>
       </c>
       <c r="G100">
         <v>24.9</v>
@@ -9487,37 +9487,37 @@
         <v>326.5</v>
       </c>
       <c r="M100">
-        <v>1081.8428544</v>
+        <v>1092.8820672</v>
       </c>
       <c r="N100">
-        <v>-755.3428543999999</v>
+        <v>-766.3820671999999</v>
       </c>
       <c r="O100">
-        <v>-181.2822850559999</v>
+        <v>-183.931696128</v>
       </c>
       <c r="P100">
-        <v>-574.0605693439999</v>
+        <v>-582.4503710719999</v>
       </c>
       <c r="Q100">
-        <v>-424.8605693439999</v>
+        <v>-433.250371072</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.862663849969487</v>
+        <v>3.679527699938975</v>
       </c>
       <c r="T100">
-        <v>37.35663303770801</v>
+        <v>74.71326607541604</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.07243196151945672</v>
+        <v>0.07170032554451269</v>
       </c>
       <c r="W100">
-        <v>0.2187205434737121</v>
+        <v>0.2188930632366039</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3017998396644029</v>
+        <v>0.2987513564354696</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2534994096036277</v>
-      </c>
-      <c r="C101">
-        <v>-3570.380638344642</v>
-      </c>
-      <c r="D101">
-        <v>1039.503361655358</v>
-      </c>
-      <c r="E101">
-        <v>4572.884</v>
-      </c>
-      <c r="F101">
-        <v>4634.784</v>
-      </c>
-      <c r="G101">
-        <v>24.9</v>
-      </c>
-      <c r="H101">
-        <v>4619.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>475.7</v>
-      </c>
-      <c r="K101">
-        <v>149.2</v>
-      </c>
-      <c r="L101">
-        <v>326.5</v>
-      </c>
-      <c r="M101">
-        <v>1092.8820672</v>
-      </c>
-      <c r="N101">
-        <v>-766.3820671999999</v>
-      </c>
-      <c r="O101">
-        <v>-183.931696128</v>
-      </c>
-      <c r="P101">
-        <v>-582.4503710719999</v>
-      </c>
-      <c r="Q101">
-        <v>-433.250371072</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.679527699938975</v>
-      </c>
-      <c r="T101">
-        <v>74.71326607541604</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.07170032554451269</v>
-      </c>
-      <c r="W101">
-        <v>0.2188930632366039</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2987513564354696</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
